--- a/research/traditional_assets/database/data/netherlands/netherlands_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_auto_truck.xlsx
@@ -650,10 +650,10 @@
         <v>0.1701214837882308</v>
       </c>
       <c r="X2">
-        <v>0.1200601936675676</v>
+        <v>0.1200124509655526</v>
       </c>
       <c r="Y2">
-        <v>0.05006129012066327</v>
+        <v>0.05010903282267826</v>
       </c>
       <c r="Z2">
         <v>4.003286589863555</v>
@@ -662,10 +662,10 @@
         <v>0.3312550471031711</v>
       </c>
       <c r="AB2">
-        <v>0.08244066056938079</v>
+        <v>0.08241588201714535</v>
       </c>
       <c r="AC2">
-        <v>0.2488143865337903</v>
+        <v>0.2488391650860257</v>
       </c>
       <c r="AD2">
         <v>34566.6</v>
@@ -787,10 +787,10 @@
         <v>0.1701214837882308</v>
       </c>
       <c r="X3">
-        <v>0.1200601936675676</v>
+        <v>0.1200124509655526</v>
       </c>
       <c r="Y3">
-        <v>0.05006129012066327</v>
+        <v>0.05010903282267826</v>
       </c>
       <c r="Z3">
         <v>4.003286589863555</v>
@@ -799,10 +799,10 @@
         <v>0.3312550471031711</v>
       </c>
       <c r="AB3">
-        <v>0.08244066056938079</v>
+        <v>0.08241588201714535</v>
       </c>
       <c r="AC3">
-        <v>0.2488143865337903</v>
+        <v>0.2488391650860257</v>
       </c>
       <c r="AD3">
         <v>34566.6</v>
@@ -1139,7 +1139,7 @@
         <v>13.7229022924549</v>
       </c>
       <c r="F2">
-        <v>4.58950774390427</v>
+        <v>4.77545465065545</v>
       </c>
       <c r="G2">
         <v>1.47817143746251</v>
@@ -1157,13 +1157,13 @@
         <v>37395.8</v>
       </c>
       <c r="L2">
-        <v>9980.15855964653</v>
+        <v>12586.6787241039</v>
       </c>
       <c r="M2">
         <v>34710.5031570334</v>
       </c>
       <c r="N2">
-        <v>43970.1286851096</v>
+        <v>46576.648849567</v>
       </c>
       <c r="O2">
         <v>34657.5031570334</v>
@@ -1172,16 +1172,16 @@
         <v>71332.7701254631</v>
       </c>
       <c r="Q2">
-        <v>0.08244066056938081</v>
+        <v>0.08241588201714541</v>
       </c>
       <c r="R2">
-        <v>0.0747245404187316</v>
+        <v>0.0730874008703076</v>
       </c>
       <c r="S2">
         <v>0.0418488</v>
       </c>
       <c r="T2">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.120060193667568</v>
+        <v>0.120012450965553</v>
       </c>
       <c r="X2">
-        <v>3.32207704187315</v>
+        <v>3.31997068703076</v>
       </c>
       <c r="Y2">
         <v>1.7139134172183</v>
@@ -1236,7 +1236,7 @@
         <v>37395.8</v>
       </c>
       <c r="AK2">
-        <v>0.043327855959079</v>
+        <v>0.04329999999999998</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1424,13 +1424,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08980167936115874</v>
+        <v>0.08977339019354216</v>
       </c>
       <c r="C2">
-        <v>66246.60055566565</v>
+        <v>66245.63607335638</v>
       </c>
       <c r="D2">
-        <v>28903.80055566564</v>
+        <v>28902.83607335638</v>
       </c>
       <c r="E2">
         <v>-34657.50315703339</v>
@@ -1475,19 +1475,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08980167936115874</v>
+        <v>0.08977339019354216</v>
       </c>
       <c r="T2">
         <v>1.015551736571413</v>
       </c>
       <c r="U2">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V2">
         <v>0.258</v>
       </c>
       <c r="W2">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08961376902840694</v>
+        <v>0.08957516484684284</v>
       </c>
       <c r="C3">
-        <v>65650.03135785463</v>
+        <v>65655.98261063015</v>
       </c>
       <c r="D3">
-        <v>29027.76438942496</v>
+        <v>29033.71564220048</v>
       </c>
       <c r="E3">
         <v>-33936.97012546306</v>
@@ -1539,37 +1539,37 @@
         <v>18497.1</v>
       </c>
       <c r="M3">
-        <v>37.25155773218626</v>
+        <v>36.24281148798779</v>
       </c>
       <c r="N3">
-        <v>18459.84844226782</v>
+        <v>18460.85718851201</v>
       </c>
       <c r="O3">
-        <v>4762.640898105096</v>
+        <v>4762.9011546361</v>
       </c>
       <c r="P3">
-        <v>13697.20754416272</v>
+        <v>13697.95603387591</v>
       </c>
       <c r="Q3">
-        <v>18646.30754416272</v>
+        <v>18647.05603387591</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09013146972566358</v>
+        <v>0.09010296853216448</v>
       </c>
       <c r="T3">
         <v>1.023163245546524</v>
       </c>
       <c r="U3">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V3">
         <v>0.258</v>
       </c>
       <c r="W3">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>496.5456782500682</v>
+        <v>510.3660350999708</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08942585869565514</v>
+        <v>0.0893769395001435</v>
       </c>
       <c r="C4">
-        <v>65054.5300627026</v>
+        <v>65067.51985327278</v>
       </c>
       <c r="D4">
-        <v>29152.79612584327</v>
+        <v>29165.78591641345</v>
       </c>
       <c r="E4">
         <v>-33216.43709389272</v>
@@ -1621,37 +1621,37 @@
         <v>18497.1</v>
       </c>
       <c r="M4">
-        <v>74.50311546437253</v>
+        <v>72.48562297597559</v>
       </c>
       <c r="N4">
-        <v>18422.59688453563</v>
+        <v>18424.61437702403</v>
       </c>
       <c r="O4">
-        <v>4753.029996210193</v>
+        <v>4753.550509272199</v>
       </c>
       <c r="P4">
-        <v>13669.56688832544</v>
+        <v>13671.06386775183</v>
       </c>
       <c r="Q4">
-        <v>18618.66688832544</v>
+        <v>18620.16386775183</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09046799050577056</v>
+        <v>0.0904392729593301</v>
       </c>
       <c r="T4">
         <v>1.030930091439495</v>
       </c>
       <c r="U4">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V4">
         <v>0.258</v>
       </c>
       <c r="W4">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>248.2728391250341</v>
+        <v>255.1830175499854</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1670,13 +1670,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08923794836290336</v>
+        <v>0.08917871415344414</v>
       </c>
       <c r="C5">
-        <v>64460.11052928566</v>
+        <v>64480.2641245886</v>
       </c>
       <c r="D5">
-        <v>29278.90962399666</v>
+        <v>29299.0632192996</v>
       </c>
       <c r="E5">
         <v>-32495.90406232239</v>
@@ -1703,37 +1703,37 @@
         <v>18497.1</v>
       </c>
       <c r="M5">
-        <v>111.7546731965588</v>
+        <v>108.7284344639634</v>
       </c>
       <c r="N5">
-        <v>18385.34532680344</v>
+        <v>18388.37156553604</v>
       </c>
       <c r="O5">
-        <v>4743.419094315288</v>
+        <v>4744.199863908299</v>
       </c>
       <c r="P5">
-        <v>13641.92623248815</v>
+        <v>13644.17170162774</v>
       </c>
       <c r="Q5">
-        <v>18591.02623248816</v>
+        <v>18593.27170162774</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09081144985866325</v>
+        <v>0.09078251149839603</v>
       </c>
       <c r="T5">
         <v>1.038857078484897</v>
       </c>
       <c r="U5">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V5">
         <v>0.258</v>
       </c>
       <c r="W5">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>165.5152260833561</v>
+        <v>170.1220116999903</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1752,13 +1752,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08905003803015157</v>
+        <v>0.08898048880674482</v>
       </c>
       <c r="C6">
-        <v>63866.78685753645</v>
+        <v>63894.23204761848</v>
       </c>
       <c r="D6">
-        <v>29406.11898381778</v>
+        <v>29433.56417389981</v>
       </c>
       <c r="E6">
         <v>-31775.37103075205</v>
@@ -1785,37 +1785,37 @@
         <v>18497.1</v>
       </c>
       <c r="M6">
-        <v>149.0062309287451</v>
+        <v>144.9712459519512</v>
       </c>
       <c r="N6">
-        <v>18348.09376907126</v>
+        <v>18352.12875404805</v>
       </c>
       <c r="O6">
-        <v>4733.808192420384</v>
+        <v>4734.849218544397</v>
       </c>
       <c r="P6">
-        <v>13614.28557665087</v>
+        <v>13617.27953550365</v>
       </c>
       <c r="Q6">
-        <v>18563.38557665087</v>
+        <v>18566.37953550365</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09116206461474122</v>
+        <v>0.09113290084035919</v>
       </c>
       <c r="T6">
         <v>1.046949211093746</v>
       </c>
       <c r="U6">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V6">
         <v>0.258</v>
       </c>
       <c r="W6">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>124.136419562517</v>
+        <v>127.5915087749927</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1834,13 +1834,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08886212769739978</v>
+        <v>0.08878226346004547</v>
       </c>
       <c r="C7">
-        <v>63274.57339349927</v>
+        <v>63309.44055205154</v>
       </c>
       <c r="D7">
-        <v>29534.43855135094</v>
+        <v>29569.30570990319</v>
       </c>
       <c r="E7">
         <v>-31054.83799918172</v>
@@ -1867,37 +1867,37 @@
         <v>18497.1</v>
       </c>
       <c r="M7">
-        <v>186.2577886609314</v>
+        <v>181.214057439939</v>
       </c>
       <c r="N7">
-        <v>18310.84221133907</v>
+        <v>18315.88594256006</v>
       </c>
       <c r="O7">
-        <v>4724.19729052548</v>
+        <v>4725.498573180496</v>
       </c>
       <c r="P7">
-        <v>13586.64492081359</v>
+        <v>13590.38736937957</v>
       </c>
       <c r="Q7">
-        <v>18535.74492081359</v>
+        <v>18539.48736937957</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09152006073410504</v>
+        <v>0.09149066680004787</v>
       </c>
       <c r="T7">
         <v>1.055211704389097</v>
       </c>
       <c r="U7">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V7">
         <v>0.258</v>
       </c>
       <c r="W7">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>99.30913565001362</v>
+        <v>102.0732070199941</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.08867421736464798</v>
+        <v>0.08858403811334613</v>
       </c>
       <c r="C8">
-        <v>62683.48473472344</v>
+        <v>62725.90688132872</v>
       </c>
       <c r="D8">
-        <v>29663.88292414544</v>
+        <v>29706.30507075072</v>
       </c>
       <c r="E8">
         <v>-30334.30496761138</v>
@@ -1949,37 +1949,37 @@
         <v>18497.1</v>
       </c>
       <c r="M8">
-        <v>223.5093463931176</v>
+        <v>217.4568689279268</v>
       </c>
       <c r="N8">
-        <v>18273.59065360688</v>
+        <v>18279.64313107208</v>
       </c>
       <c r="O8">
-        <v>4714.586388630576</v>
+        <v>4716.147927816596</v>
       </c>
       <c r="P8">
-        <v>13559.00426497631</v>
+        <v>13563.49520325548</v>
       </c>
       <c r="Q8">
-        <v>18508.1042649763</v>
+        <v>18512.59520325548</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.09188567379217871</v>
+        <v>0.09185604480143206</v>
       </c>
       <c r="T8">
         <v>1.063649995414136</v>
       </c>
       <c r="U8">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V8">
         <v>0.258</v>
       </c>
       <c r="W8">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>82.75761304167803</v>
+        <v>85.06100584999513</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1998,13 +1998,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08848630703189619</v>
+        <v>0.08838581276664681</v>
       </c>
       <c r="C9">
-        <v>62093.535735799</v>
+        <v>62143.64859994507</v>
       </c>
       <c r="D9">
-        <v>29794.46695679134</v>
+        <v>29844.57982093741</v>
       </c>
       <c r="E9">
         <v>-29613.77193604105</v>
@@ -2031,37 +2031,37 @@
         <v>18497.1</v>
       </c>
       <c r="M9">
-        <v>260.7609041253039</v>
+        <v>253.6996804159146</v>
       </c>
       <c r="N9">
-        <v>18236.3390958747</v>
+        <v>18243.40031958409</v>
       </c>
       <c r="O9">
-        <v>4704.975486735672</v>
+        <v>4706.797282452695</v>
       </c>
       <c r="P9">
-        <v>13531.36360913903</v>
+        <v>13536.60303713139</v>
       </c>
       <c r="Q9">
-        <v>18480.46360913902</v>
+        <v>18485.70303713139</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09225914949666258</v>
+        <v>0.09222928039424388</v>
       </c>
       <c r="T9">
         <v>1.072269755063369</v>
       </c>
       <c r="U9">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V9">
         <v>0.258</v>
       </c>
       <c r="W9">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>70.93509689286687</v>
+        <v>72.9094335857101</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2080,13 +2080,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08829839669914442</v>
+        <v>0.08818758741994746</v>
       </c>
       <c r="C10">
-        <v>61504.74151403946</v>
+        <v>61562.68360095679</v>
       </c>
       <c r="D10">
-        <v>29926.20576660213</v>
+        <v>29984.14785351946</v>
       </c>
       <c r="E10">
         <v>-28893.23890447072</v>
@@ -2113,37 +2113,37 @@
         <v>18497.1</v>
       </c>
       <c r="M10">
-        <v>298.0124618574901</v>
+        <v>289.9424919039024</v>
       </c>
       <c r="N10">
-        <v>18199.08753814251</v>
+        <v>18207.1575080961</v>
       </c>
       <c r="O10">
-        <v>4695.364584840768</v>
+        <v>4697.446637088794</v>
       </c>
       <c r="P10">
-        <v>13503.72295330174</v>
+        <v>13509.71087100731</v>
       </c>
       <c r="Q10">
-        <v>18452.82295330174</v>
+        <v>18458.81087100731</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09264074423820044</v>
+        <v>0.09261062980429072</v>
       </c>
       <c r="T10">
         <v>1.081076900791934</v>
       </c>
       <c r="U10">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V10">
         <v>0.258</v>
       </c>
       <c r="W10">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>62.06820978125852</v>
+        <v>63.79575438749635</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2162,13 +2162,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08811048636639263</v>
+        <v>0.08798936207324812</v>
       </c>
       <c r="C11">
-        <v>60917.11745531582</v>
+        <v>60983.03011369976</v>
       </c>
       <c r="D11">
-        <v>30059.11473944882</v>
+        <v>30125.02739783276</v>
       </c>
       <c r="E11">
         <v>-28172.70587290038</v>
@@ -2195,37 +2195,37 @@
         <v>18497.1</v>
       </c>
       <c r="M11">
-        <v>335.2640195896764</v>
+        <v>326.1853033918902</v>
       </c>
       <c r="N11">
-        <v>18161.83598041033</v>
+        <v>18170.91469660811</v>
       </c>
       <c r="O11">
-        <v>4685.753682945865</v>
+        <v>4688.095991724894</v>
       </c>
       <c r="P11">
-        <v>13476.08229746446</v>
+        <v>13482.81870488322</v>
       </c>
       <c r="Q11">
-        <v>18425.18229746446</v>
+        <v>18431.91870488322</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.09303072567735453</v>
+        <v>0.09300036052005288</v>
       </c>
       <c r="T11">
         <v>1.090077610162884</v>
       </c>
       <c r="U11">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V11">
         <v>0.258</v>
       </c>
       <c r="W11">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>55.17174202778536</v>
+        <v>56.70733723333009</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2244,13 +2244,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08792257603364084</v>
+        <v>0.08779113672654879</v>
       </c>
       <c r="C12">
-        <v>60330.67922004672</v>
+        <v>60404.70671172698</v>
       </c>
       <c r="D12">
-        <v>30193.20953575004</v>
+        <v>30267.2370274303</v>
       </c>
       <c r="E12">
         <v>-27452.17284133005</v>
@@ -2277,37 +2277,37 @@
         <v>18497.1</v>
       </c>
       <c r="M12">
-        <v>372.5155773218627</v>
+        <v>362.428114879878</v>
       </c>
       <c r="N12">
-        <v>18124.58442267814</v>
+        <v>18134.67188512013</v>
       </c>
       <c r="O12">
-        <v>4676.14278105096</v>
+        <v>4678.745346360993</v>
       </c>
       <c r="P12">
-        <v>13448.44164162718</v>
+        <v>13455.92653875913</v>
       </c>
       <c r="Q12">
-        <v>18397.54164162718</v>
+        <v>18405.02653875913</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.09342937337071204</v>
+        <v>0.09339875191838753</v>
       </c>
       <c r="T12">
         <v>1.099278335297634</v>
       </c>
       <c r="U12">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V12">
         <v>0.258</v>
       </c>
       <c r="W12">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>49.65456782500681</v>
+        <v>51.03660350999707</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2326,13 +2326,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08773466570088904</v>
+        <v>0.08759291137984944</v>
       </c>
       <c r="C13">
-        <v>59745.4427493498</v>
+        <v>59827.73232097165</v>
       </c>
       <c r="D13">
-        <v>30328.50609662348</v>
+        <v>30410.79566824532</v>
       </c>
       <c r="E13">
         <v>-26731.63980975972</v>
@@ -2359,37 +2359,37 @@
         <v>18497.1</v>
       </c>
       <c r="M13">
-        <v>409.7671350540489</v>
+        <v>398.6709263678658</v>
       </c>
       <c r="N13">
-        <v>18087.33286494595</v>
+        <v>18098.42907363214</v>
       </c>
       <c r="O13">
-        <v>4666.531879156057</v>
+        <v>4669.394700997092</v>
       </c>
       <c r="P13">
-        <v>13420.8009857899</v>
+        <v>13429.03437263505</v>
       </c>
       <c r="Q13">
-        <v>18369.9009857899</v>
+        <v>18378.13437263505</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.09383697943920116</v>
+        <v>0.0938060959324151</v>
       </c>
       <c r="T13">
         <v>1.10868581830058</v>
       </c>
       <c r="U13">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V13">
         <v>0.258</v>
       </c>
       <c r="W13">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.14051620455166</v>
+        <v>46.39691228181552</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2408,13 +2408,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.08754675536813726</v>
+        <v>0.08739468603315009</v>
       </c>
       <c r="C14">
-        <v>59161.42427135914</v>
+        <v>59252.12622814385</v>
       </c>
       <c r="D14">
-        <v>30465.02065020315</v>
+        <v>30555.72260698785</v>
       </c>
       <c r="E14">
         <v>-26011.10677818938</v>
@@ -2441,37 +2441,37 @@
         <v>18497.1</v>
       </c>
       <c r="M14">
-        <v>447.0186927862352</v>
+        <v>434.9137378558535</v>
       </c>
       <c r="N14">
-        <v>18050.08130721377</v>
+        <v>18062.18626214415</v>
       </c>
       <c r="O14">
-        <v>4656.920977261152</v>
+        <v>4660.04405563319</v>
       </c>
       <c r="P14">
-        <v>13393.16032995262</v>
+        <v>13402.14220651096</v>
       </c>
       <c r="Q14">
-        <v>18342.26032995262</v>
+        <v>18351.24220651096</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.09425384928197417</v>
+        <v>0.0942226977649433</v>
       </c>
       <c r="T14">
         <v>1.118307107735412</v>
       </c>
       <c r="U14">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V14">
         <v>0.258</v>
       </c>
       <c r="W14">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>41.37880652083902</v>
+        <v>42.53050292499756</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2490,13 +2490,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08735884503538548</v>
+        <v>0.08719646068645077</v>
       </c>
       <c r="C15">
-        <v>58578.64030771396</v>
+        <v>58677.90808936822</v>
       </c>
       <c r="D15">
-        <v>30602.76971812829</v>
+        <v>30702.03749978256</v>
       </c>
       <c r="E15">
         <v>-25290.57374661905</v>
@@ -2523,37 +2523,37 @@
         <v>18497.1</v>
       </c>
       <c r="M15">
-        <v>484.2702505184216</v>
+        <v>471.1565493438414</v>
       </c>
       <c r="N15">
-        <v>18012.82974948158</v>
+        <v>18025.94345065616</v>
       </c>
       <c r="O15">
-        <v>4647.310075366248</v>
+        <v>4650.693410269289</v>
       </c>
       <c r="P15">
-        <v>13365.51967411533</v>
+        <v>13375.25004038687</v>
       </c>
       <c r="Q15">
-        <v>18314.61967411533</v>
+        <v>18324.35004038687</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.09468030233952353</v>
+        <v>0.09464887665109284</v>
       </c>
       <c r="T15">
         <v>1.12814957623771</v>
       </c>
       <c r="U15">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V15">
         <v>0.258</v>
       </c>
       <c r="W15">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.1958214038514</v>
+        <v>39.25892577692082</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2572,13 +2572,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08717093470263368</v>
+        <v>0.08699823533975143</v>
       </c>
       <c r="C16">
-        <v>57997.10768022426</v>
+        <v>58105.09793907135</v>
       </c>
       <c r="D16">
-        <v>30741.77012220894</v>
+        <v>30849.76038105603</v>
       </c>
       <c r="E16">
         <v>-24570.04071504871</v>
@@ -2605,37 +2605,37 @@
         <v>18497.1</v>
       </c>
       <c r="M16">
-        <v>521.5218082506078</v>
+        <v>507.3993608318292</v>
       </c>
       <c r="N16">
-        <v>17975.5781917494</v>
+        <v>17989.70063916817</v>
       </c>
       <c r="O16">
-        <v>4637.699173471344</v>
+        <v>4641.342764905388</v>
       </c>
       <c r="P16">
-        <v>13337.87901827805</v>
+        <v>13348.35787426278</v>
       </c>
       <c r="Q16">
-        <v>18286.97901827805</v>
+        <v>18297.45787426278</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.09511667291003915</v>
+        <v>0.09508496667412956</v>
       </c>
       <c r="T16">
         <v>1.138220939356341</v>
       </c>
       <c r="U16">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V16">
         <v>0.258</v>
       </c>
       <c r="W16">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>35.46754844643344</v>
+        <v>36.45471679285505</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2654,13 +2654,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.0869830243698819</v>
+        <v>0.08680000999305208</v>
       </c>
       <c r="C17">
-        <v>57416.84351771901</v>
+        <v>57533.71619912663</v>
       </c>
       <c r="D17">
-        <v>30882.03899127402</v>
+        <v>30998.91167268164</v>
       </c>
       <c r="E17">
         <v>-23849.50768347838</v>
@@ -2687,37 +2687,37 @@
         <v>18497.1</v>
       </c>
       <c r="M17">
-        <v>558.773365982794</v>
+        <v>543.642172319817</v>
       </c>
       <c r="N17">
-        <v>17938.32663401721</v>
+        <v>17953.45782768018</v>
       </c>
       <c r="O17">
-        <v>4628.08827157644</v>
+        <v>4631.992119541487</v>
       </c>
       <c r="P17">
-        <v>13310.23836244077</v>
+        <v>13321.4657081387</v>
       </c>
       <c r="Q17">
-        <v>18259.33836244077</v>
+        <v>18270.5657081387</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09556331102339047</v>
+        <v>0.09553131763888481</v>
       </c>
       <c r="T17">
         <v>1.148529275724823</v>
       </c>
       <c r="U17">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V17">
         <v>0.258</v>
       </c>
       <c r="W17">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.10304521667122</v>
+        <v>34.02440233999805</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2736,13 +2736,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.0867951140371301</v>
+        <v>0.08660178464635275</v>
       </c>
       <c r="C18">
-        <v>56837.86526308255</v>
+        <v>56963.78368826583</v>
       </c>
       <c r="D18">
-        <v>31023.59376820789</v>
+        <v>31149.51219339118</v>
       </c>
       <c r="E18">
         <v>-23128.97465190804</v>
@@ -2769,37 +2769,37 @@
         <v>18497.1</v>
       </c>
       <c r="M18">
-        <v>596.0249237149802</v>
+        <v>579.8849838078047</v>
       </c>
       <c r="N18">
-        <v>17901.07507628502</v>
+        <v>17917.2150161922</v>
       </c>
       <c r="O18">
-        <v>4618.477369681535</v>
+        <v>4622.641474177587</v>
       </c>
       <c r="P18">
-        <v>13282.59770660349</v>
+        <v>13294.57354201461</v>
       </c>
       <c r="Q18">
-        <v>18231.69770660349</v>
+        <v>18243.67354201461</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09602058337753583</v>
+        <v>0.0959882960075628</v>
       </c>
       <c r="T18">
         <v>1.159083048673506</v>
       </c>
       <c r="U18">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V18">
         <v>0.258</v>
       </c>
       <c r="W18">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.03410489062927</v>
+        <v>31.89787719374817</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2818,13 +2818,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.0866072037043783</v>
+        <v>0.0864035592996534</v>
       </c>
       <c r="C19">
-        <v>56260.19068048541</v>
+        <v>56395.32163176648</v>
       </c>
       <c r="D19">
-        <v>31166.45221718108</v>
+        <v>31301.58316846216</v>
       </c>
       <c r="E19">
         <v>-22408.44162033771</v>
@@ -2851,37 +2851,37 @@
         <v>18497.1</v>
       </c>
       <c r="M19">
-        <v>633.2764814471666</v>
+        <v>616.1277952957927</v>
       </c>
       <c r="N19">
-        <v>17863.82351855284</v>
+        <v>17880.97220470421</v>
       </c>
       <c r="O19">
-        <v>4608.866467786632</v>
+        <v>4613.290828813686</v>
       </c>
       <c r="P19">
-        <v>13254.9570507662</v>
+        <v>13267.68137589052</v>
       </c>
       <c r="Q19">
-        <v>18204.0570507662</v>
+        <v>18216.78137589052</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09648887434262446</v>
+        <v>0.09645628590319688</v>
       </c>
       <c r="T19">
         <v>1.169891129404085</v>
       </c>
       <c r="U19">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V19">
         <v>0.258</v>
       </c>
       <c r="W19">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.20856930882754</v>
+        <v>30.02153147646886</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2900,13 +2900,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08641929337162652</v>
+        <v>0.08620533395295407</v>
       </c>
       <c r="C20">
-        <v>55683.83786281594</v>
+        <v>55828.3516714241</v>
       </c>
       <c r="D20">
-        <v>31310.63243108194</v>
+        <v>31455.1462396901</v>
       </c>
       <c r="E20">
         <v>-21687.90858876738</v>
@@ -2933,37 +2933,37 @@
         <v>18497.1</v>
       </c>
       <c r="M20">
-        <v>670.5280391793528</v>
+        <v>652.3706067837803</v>
       </c>
       <c r="N20">
-        <v>17826.57196082065</v>
+        <v>17844.72939321622</v>
       </c>
       <c r="O20">
-        <v>4599.255565891727</v>
+        <v>4603.940183449785</v>
       </c>
       <c r="P20">
-        <v>13227.31639492892</v>
+        <v>13240.78920976644</v>
       </c>
       <c r="Q20">
-        <v>18176.41639492892</v>
+        <v>18189.88920976644</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.09696858703856892</v>
+        <v>0.09693569018652935</v>
       </c>
       <c r="T20">
         <v>1.180962821859801</v>
       </c>
       <c r="U20">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V20">
         <v>0.258</v>
       </c>
       <c r="W20">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>27.58587101389267</v>
+        <v>28.35366861666504</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2982,13 +2982,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08623138303887473</v>
+        <v>0.08600710860625474</v>
       </c>
       <c r="C21">
-        <v>55108.82523931911</v>
+        <v>55262.89587581971</v>
       </c>
       <c r="D21">
-        <v>31456.15283915545</v>
+        <v>31610.22347565605</v>
       </c>
       <c r="E21">
         <v>-20967.37555719704</v>
@@ -3015,37 +3015,37 @@
         <v>18497.1</v>
       </c>
       <c r="M21">
-        <v>707.7795969115391</v>
+        <v>688.6134182717682</v>
       </c>
       <c r="N21">
-        <v>17789.32040308846</v>
+        <v>17808.48658172823</v>
       </c>
       <c r="O21">
-        <v>4589.644663996824</v>
+        <v>4594.589538085885</v>
       </c>
       <c r="P21">
-        <v>13199.67573909164</v>
+        <v>13213.89704364235</v>
       </c>
       <c r="Q21">
-        <v>18148.77573909164</v>
+        <v>18162.99704364235</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09746014449243794</v>
+        <v>0.09742693161266017</v>
       </c>
       <c r="T21">
         <v>1.19230788943788</v>
       </c>
       <c r="U21">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V21">
         <v>0.258</v>
       </c>
       <c r="W21">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.13398306579306</v>
+        <v>26.86137026841951</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3064,13 +3064,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.08604347270612295</v>
+        <v>0.08580888325955541</v>
       </c>
       <c r="C22">
-        <v>54535.17158344932</v>
+        <v>54698.97675089243</v>
       </c>
       <c r="D22">
-        <v>31603.03221485599</v>
+        <v>31766.83738229912</v>
       </c>
       <c r="E22">
         <v>-20246.84252562671</v>
@@ -3097,37 +3097,37 @@
         <v>18497.1</v>
       </c>
       <c r="M22">
-        <v>745.0311546437255</v>
+        <v>724.856229759756</v>
       </c>
       <c r="N22">
-        <v>17752.06884535628</v>
+        <v>17772.24377024025</v>
       </c>
       <c r="O22">
-        <v>4580.03376210192</v>
+        <v>4585.238892721984</v>
       </c>
       <c r="P22">
-        <v>13172.03508325436</v>
+        <v>13187.00487751826</v>
       </c>
       <c r="Q22">
-        <v>18121.13508325435</v>
+        <v>18136.10487751826</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09796399088265367</v>
+        <v>0.09793045407444424</v>
       </c>
       <c r="T22">
         <v>1.20393658370541</v>
       </c>
       <c r="U22">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V22">
         <v>0.258</v>
       </c>
       <c r="W22">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>24.8272839125034</v>
+        <v>25.51830175499853</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3146,13 +3146,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08585556237337116</v>
+        <v>0.08561065791285605</v>
       </c>
       <c r="C23">
-        <v>53962.89602094416</v>
+        <v>54136.61725082798</v>
       </c>
       <c r="D23">
-        <v>31751.28968392118</v>
+        <v>31925.01091380498</v>
       </c>
       <c r="E23">
         <v>-19526.30949405638</v>
@@ -3179,37 +3179,37 @@
         <v>18497.1</v>
       </c>
       <c r="M23">
-        <v>782.2827123759116</v>
+        <v>761.0990412477437</v>
       </c>
       <c r="N23">
-        <v>17714.81728762409</v>
+        <v>17736.00095875226</v>
       </c>
       <c r="O23">
-        <v>4570.422860207015</v>
+        <v>4575.888247358082</v>
       </c>
       <c r="P23">
-        <v>13144.39442741708</v>
+        <v>13160.11271139418</v>
       </c>
       <c r="Q23">
-        <v>18093.49442741707</v>
+        <v>18109.21271139418</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.098480592877685</v>
+        <v>0.09844672394032411</v>
       </c>
       <c r="T23">
         <v>1.215859675296169</v>
       </c>
       <c r="U23">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V23">
         <v>0.258</v>
       </c>
       <c r="W23">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>23.64503229762229</v>
+        <v>24.30314452857004</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3228,13 +3228,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08566765204061937</v>
+        <v>0.08541243256615672</v>
       </c>
       <c r="C24">
-        <v>53392.01803812678</v>
+        <v>53575.84078927388</v>
       </c>
       <c r="D24">
-        <v>31900.94473267412</v>
+        <v>32084.76748382123</v>
       </c>
       <c r="E24">
         <v>-18805.77646248604</v>
@@ -3261,37 +3261,37 @@
         <v>18497.1</v>
       </c>
       <c r="M24">
-        <v>819.5342701080979</v>
+        <v>797.3418527357315</v>
       </c>
       <c r="N24">
-        <v>17677.5657298919</v>
+        <v>17699.75814726427</v>
       </c>
       <c r="O24">
-        <v>4560.811958312112</v>
+        <v>4566.537601994182</v>
       </c>
       <c r="P24">
-        <v>13116.75377157979</v>
+        <v>13133.22054527009</v>
       </c>
       <c r="Q24">
-        <v>18065.85377157979</v>
+        <v>18082.32054527009</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09901044107771713</v>
+        <v>0.09897623149507272</v>
       </c>
       <c r="T24">
         <v>1.228088487184128</v>
       </c>
       <c r="U24">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V24">
         <v>0.258</v>
       </c>
       <c r="W24">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.57025810227583</v>
+        <v>23.19845614090776</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3310,13 +3310,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.08547974170786757</v>
+        <v>0.08521420721945738</v>
       </c>
       <c r="C25">
-        <v>52822.55749044372</v>
+        <v>53016.67125089359</v>
       </c>
       <c r="D25">
-        <v>32052.01721656141</v>
+        <v>32246.13097701127</v>
       </c>
       <c r="E25">
         <v>-18085.24343091571</v>
@@ -3343,37 +3343,37 @@
         <v>18497.1</v>
       </c>
       <c r="M25">
-        <v>856.7858278402842</v>
+        <v>833.5846642237193</v>
       </c>
       <c r="N25">
-        <v>17640.31417215972</v>
+        <v>17663.51533577628</v>
       </c>
       <c r="O25">
-        <v>4551.201056417207</v>
+        <v>4557.186956630281</v>
       </c>
       <c r="P25">
-        <v>13089.11311574251</v>
+        <v>13106.328379146</v>
       </c>
       <c r="Q25">
-        <v>18038.21311574251</v>
+        <v>18055.428379146</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09955405156865918</v>
+        <v>0.09951949249280179</v>
       </c>
       <c r="T25">
         <v>1.240634930549695</v>
       </c>
       <c r="U25">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V25">
         <v>0.258</v>
       </c>
       <c r="W25">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.58894253261166</v>
+        <v>22.1898276130422</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3392,13 +3392,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08529183137511578</v>
+        <v>0.08501598187275805</v>
       </c>
       <c r="C26">
-        <v>52254.53461124696</v>
+        <v>52459.13300327053</v>
       </c>
       <c r="D26">
-        <v>32204.52736893497</v>
+        <v>32409.12576095854</v>
       </c>
       <c r="E26">
         <v>-17364.71039934537</v>
@@ -3425,37 +3425,37 @@
         <v>18497.1</v>
       </c>
       <c r="M26">
-        <v>894.0373855724704</v>
+        <v>869.8274757117071</v>
       </c>
       <c r="N26">
-        <v>17603.06261442753</v>
+        <v>17627.2725242883</v>
       </c>
       <c r="O26">
-        <v>4541.590154522303</v>
+        <v>4547.83631126638</v>
       </c>
       <c r="P26">
-        <v>13061.47245990523</v>
+        <v>13079.43621302192</v>
       </c>
       <c r="Q26">
-        <v>18010.57245990523</v>
+        <v>18028.53621302191</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1001119675988366</v>
+        <v>0.1000770498325764</v>
       </c>
       <c r="T26">
         <v>1.253511543477515</v>
       </c>
       <c r="U26">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V26">
         <v>0.258</v>
       </c>
       <c r="W26">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>20.68940326041951</v>
+        <v>21.26525146249878</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3474,13 +3474,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.085103921042364</v>
+        <v>0.08481775652605869</v>
       </c>
       <c r="C27">
-        <v>51687.97002082752</v>
+        <v>51903.25090917526</v>
       </c>
       <c r="D27">
-        <v>32358.49581008586</v>
+        <v>32573.7766984336</v>
       </c>
       <c r="E27">
         <v>-16644.17736777504</v>
@@ -3507,37 +3507,37 @@
         <v>18497.1</v>
       </c>
       <c r="M27">
-        <v>931.2889433046568</v>
+        <v>906.0702871996949</v>
       </c>
       <c r="N27">
-        <v>17565.81105669534</v>
+        <v>17591.02971280031</v>
       </c>
       <c r="O27">
-        <v>4531.979252627399</v>
+        <v>4538.48566590248</v>
       </c>
       <c r="P27">
-        <v>13033.83180406794</v>
+        <v>13052.54404689783</v>
       </c>
       <c r="Q27">
-        <v>17982.93180406794</v>
+        <v>18001.64404689783</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1006847613898187</v>
+        <v>0.1006494753680783</v>
       </c>
       <c r="T27">
         <v>1.266731532750076</v>
       </c>
       <c r="U27">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V27">
         <v>0.258</v>
       </c>
       <c r="W27">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>19.86182713000272</v>
+        <v>20.41464140399883</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3556,13 +3556,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.0849160107096122</v>
+        <v>0.08461953117935936</v>
       </c>
       <c r="C28">
-        <v>51122.88473570968</v>
+        <v>51349.05033920835</v>
       </c>
       <c r="D28">
-        <v>32513.94355653836</v>
+        <v>32740.10916003702</v>
       </c>
       <c r="E28">
         <v>-15923.6443362047</v>
@@ -3589,37 +3589,37 @@
         <v>18497.1</v>
       </c>
       <c r="M28">
-        <v>968.5405010368431</v>
+        <v>942.3130986876828</v>
       </c>
       <c r="N28">
-        <v>17528.55949896316</v>
+        <v>17554.78690131232</v>
       </c>
       <c r="O28">
-        <v>4522.368350732495</v>
+        <v>4529.135020538579</v>
       </c>
       <c r="P28">
-        <v>13006.19114823066</v>
+        <v>13025.65188077374</v>
       </c>
       <c r="Q28">
-        <v>17955.29114823066</v>
+        <v>17974.75188077374</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1012730360940705</v>
+        <v>0.1012373718639991</v>
       </c>
       <c r="T28">
         <v>1.280308819030004</v>
       </c>
       <c r="U28">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V28">
         <v>0.258</v>
       </c>
       <c r="W28">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.0979107019257</v>
+        <v>19.62946288846041</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3638,13 +3638,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08472810037686043</v>
+        <v>0.08442130583266003</v>
       </c>
       <c r="C29">
-        <v>50559.30017821421</v>
+        <v>50796.55718483278</v>
       </c>
       <c r="D29">
-        <v>32670.89203061322</v>
+        <v>32908.1490372318</v>
       </c>
       <c r="E29">
         <v>-15203.11130463437</v>
@@ -3671,37 +3671,37 @@
         <v>18497.1</v>
       </c>
       <c r="M29">
-        <v>1005.792058769029</v>
+        <v>978.5559101756705</v>
       </c>
       <c r="N29">
-        <v>17491.30794123097</v>
+        <v>17518.54408982433</v>
       </c>
       <c r="O29">
-        <v>4512.757448837591</v>
+        <v>4519.784375174678</v>
       </c>
       <c r="P29">
-        <v>12978.55049239338</v>
+        <v>12998.75971464966</v>
       </c>
       <c r="Q29">
-        <v>17927.65049239338</v>
+        <v>17947.85971464965</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1018774279135074</v>
+        <v>0.1018413751132329</v>
       </c>
       <c r="T29">
         <v>1.294258085755957</v>
       </c>
       <c r="U29">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V29">
         <v>0.258</v>
       </c>
       <c r="W29">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.39058067592845</v>
+        <v>18.90244574444336</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3720,13 +3720,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.08454019004410862</v>
+        <v>0.08422308048596068</v>
       </c>
       <c r="C30">
-        <v>49997.23818630013</v>
+        <v>50245.79787180963</v>
       </c>
       <c r="D30">
-        <v>32829.36307026949</v>
+        <v>33077.92275577898</v>
       </c>
       <c r="E30">
         <v>-14482.57827306403</v>
@@ -3753,37 +3753,37 @@
         <v>18497.1</v>
       </c>
       <c r="M30">
-        <v>1043.043616501216</v>
+        <v>1014.798721663658</v>
       </c>
       <c r="N30">
-        <v>17454.05638349879</v>
+        <v>17482.30127833634</v>
       </c>
       <c r="O30">
-        <v>4503.146546942688</v>
+        <v>4510.433729810777</v>
       </c>
       <c r="P30">
-        <v>12950.9098365561</v>
+        <v>12971.86754852557</v>
       </c>
       <c r="Q30">
-        <v>17900.0098365561</v>
+        <v>17920.96754852556</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1024986083945953</v>
+        <v>0.102462156230501</v>
       </c>
       <c r="T30">
         <v>1.308594832113186</v>
       </c>
       <c r="U30">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V30">
         <v>0.258</v>
       </c>
       <c r="W30">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>17.73377422321672</v>
+        <v>18.22735839642753</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3802,13 +3802,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08435227971135682</v>
+        <v>0.08402485513926135</v>
       </c>
       <c r="C31">
-        <v>49436.72102369401</v>
+        <v>49696.79937405165</v>
       </c>
       <c r="D31">
-        <v>32989.37893923369</v>
+        <v>33249.45728959134</v>
       </c>
       <c r="E31">
         <v>-13762.0452414937</v>
@@ -3835,37 +3835,37 @@
         <v>18497.1</v>
       </c>
       <c r="M31">
-        <v>1080.295174233402</v>
+        <v>1051.041533151646</v>
       </c>
       <c r="N31">
-        <v>17416.8048257666</v>
+        <v>17446.05846684836</v>
       </c>
       <c r="O31">
-        <v>4493.535645047783</v>
+        <v>4501.083084446876</v>
       </c>
       <c r="P31">
-        <v>12923.26918071882</v>
+        <v>12944.97538240148</v>
       </c>
       <c r="Q31">
-        <v>17872.36918071882</v>
+        <v>17894.07538240148</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.103137286917404</v>
+        <v>0.1031004241398047</v>
       </c>
       <c r="T31">
         <v>1.323335430480479</v>
       </c>
       <c r="U31">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V31">
         <v>0.258</v>
       </c>
       <c r="W31">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.12226476724373</v>
+        <v>17.59882879655071</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3884,13 +3884,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08416436937860504</v>
+        <v>0.08382662979256202</v>
       </c>
       <c r="C32">
-        <v>48877.77139031719</v>
+        <v>49149.5892279105</v>
       </c>
       <c r="D32">
-        <v>33150.9623374272</v>
+        <v>33422.78017502051</v>
       </c>
       <c r="E32">
         <v>-13041.51220992337</v>
@@ -3917,37 +3917,37 @@
         <v>18497.1</v>
       </c>
       <c r="M32">
-        <v>1117.546731965588</v>
+        <v>1087.284344639634</v>
       </c>
       <c r="N32">
-        <v>17379.55326803441</v>
+        <v>17409.81565536037</v>
       </c>
       <c r="O32">
-        <v>4483.924743152879</v>
+        <v>4491.732439082975</v>
       </c>
       <c r="P32">
-        <v>12895.62852488154</v>
+        <v>12918.08321627739</v>
       </c>
       <c r="Q32">
-        <v>17844.72852488154</v>
+        <v>17867.18321627739</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1037942133980072</v>
+        <v>0.1037569282750886</v>
       </c>
       <c r="T32">
         <v>1.338497188801123</v>
       </c>
       <c r="U32">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V32">
         <v>0.258</v>
       </c>
       <c r="W32">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.55152260833561</v>
+        <v>17.01220116999902</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3966,13 +3966,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08397645904585324</v>
+        <v>0.08362840444586267</v>
       </c>
       <c r="C33">
-        <v>48320.4124330209</v>
+        <v>48604.19554691284</v>
       </c>
       <c r="D33">
-        <v>33314.13641170125</v>
+        <v>33597.9195255932</v>
       </c>
       <c r="E33">
         <v>-12320.97917835303</v>
@@ -3999,37 +3999,37 @@
         <v>18497.1</v>
       </c>
       <c r="M33">
-        <v>1154.798289697774</v>
+        <v>1123.527156127622</v>
       </c>
       <c r="N33">
-        <v>17342.30171030223</v>
+        <v>17373.57284387238</v>
       </c>
       <c r="O33">
-        <v>4474.313841257975</v>
+        <v>4482.381793719074</v>
       </c>
       <c r="P33">
-        <v>12867.98786904425</v>
+        <v>12891.19105015331</v>
       </c>
       <c r="Q33">
-        <v>17817.08786904425</v>
+        <v>17840.2910501533</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1044701812258743</v>
+        <v>0.104432461515743</v>
       </c>
       <c r="T33">
         <v>1.354098418377437</v>
       </c>
       <c r="U33">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V33">
         <v>0.258</v>
       </c>
       <c r="W33">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.01760252419574</v>
+        <v>16.46342048709583</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4048,13 +4048,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08378854871310147</v>
+        <v>0.08343017909916332</v>
       </c>
       <c r="C34">
-        <v>47764.66775663986</v>
+        <v>48060.64703696244</v>
       </c>
       <c r="D34">
-        <v>33478.92476689055</v>
+        <v>33774.90404721312</v>
       </c>
       <c r="E34">
         <v>-11600.4461467827</v>
@@ -4081,37 +4081,37 @@
         <v>18497.1</v>
       </c>
       <c r="M34">
-        <v>1192.04984742996</v>
+        <v>1159.769967615609</v>
       </c>
       <c r="N34">
-        <v>17305.05015257004</v>
+        <v>17337.33003238439</v>
       </c>
       <c r="O34">
-        <v>4464.702939363071</v>
+        <v>4473.031148355174</v>
       </c>
       <c r="P34">
-        <v>12840.34721320697</v>
+        <v>12864.29888402922</v>
       </c>
       <c r="Q34">
-        <v>17789.44721320697</v>
+        <v>17813.39888402922</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1051660304604433</v>
+        <v>0.1051278633811225</v>
       </c>
       <c r="T34">
         <v>1.370158507647173</v>
       </c>
       <c r="U34">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V34">
         <v>0.258</v>
       </c>
       <c r="W34">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.51705244531463</v>
+        <v>15.94893859687409</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4130,13 +4130,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08360063838034967</v>
+        <v>0.08323195375246398</v>
       </c>
       <c r="C35">
-        <v>47210.56143537581</v>
+        <v>47518.97301202505</v>
       </c>
       <c r="D35">
-        <v>33645.35147719683</v>
+        <v>33953.76305384607</v>
       </c>
       <c r="E35">
         <v>-10879.91311521237</v>
@@ -4163,37 +4163,37 @@
         <v>18497.1</v>
       </c>
       <c r="M35">
-        <v>1229.301405162147</v>
+        <v>1196.012779103597</v>
       </c>
       <c r="N35">
-        <v>17267.79859483786</v>
+        <v>17301.08722089641</v>
       </c>
       <c r="O35">
-        <v>4455.092037468167</v>
+        <v>4463.680502991273</v>
       </c>
       <c r="P35">
-        <v>12812.70655736969</v>
+        <v>12837.40671790513</v>
       </c>
       <c r="Q35">
-        <v>17761.80655736969</v>
+        <v>17786.50671790513</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1058826513139547</v>
+        <v>0.1058440235111403</v>
       </c>
       <c r="T35">
         <v>1.386698002566751</v>
       </c>
       <c r="U35">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V35">
         <v>0.258</v>
       </c>
       <c r="W35">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.04683873485055</v>
+        <v>15.46563742727184</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4212,13 +4212,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08341272804759789</v>
+        <v>0.08303372840576465</v>
       </c>
       <c r="C36">
-        <v>46658.11802452191</v>
+        <v>46979.20341031454</v>
       </c>
       <c r="D36">
-        <v>33813.44109791326</v>
+        <v>34134.5264837059</v>
       </c>
       <c r="E36">
         <v>-10159.38008364203</v>
@@ -4245,37 +4245,37 @@
         <v>18497.1</v>
       </c>
       <c r="M36">
-        <v>1266.552962894333</v>
+        <v>1232.255590591585</v>
       </c>
       <c r="N36">
-        <v>17230.54703710567</v>
+        <v>17264.84440940842</v>
       </c>
       <c r="O36">
-        <v>4445.481135573263</v>
+        <v>4454.329857627371</v>
       </c>
       <c r="P36">
-        <v>12785.06590153241</v>
+        <v>12810.51455178105</v>
       </c>
       <c r="Q36">
-        <v>17734.1659015324</v>
+        <v>17759.61455178104</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1066209879509059</v>
+        <v>0.1065818854632798</v>
       </c>
       <c r="T36">
         <v>1.403738694302074</v>
       </c>
       <c r="U36">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V36">
         <v>0.258</v>
       </c>
       <c r="W36">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.60428465441377</v>
+        <v>15.01076573823443</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4294,13 +4294,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08322481771484609</v>
+        <v>0.0828355030590653</v>
       </c>
       <c r="C37">
-        <v>46107.36257254073</v>
+        <v>46441.36881099879</v>
       </c>
       <c r="D37">
-        <v>33983.21867750242</v>
+        <v>34317.22491596048</v>
       </c>
       <c r="E37">
         <v>-9438.847052071698</v>
@@ -4327,37 +4327,37 @@
         <v>18497.1</v>
       </c>
       <c r="M37">
-        <v>1303.804520626519</v>
+        <v>1268.498402079573</v>
       </c>
       <c r="N37">
-        <v>17193.29547937348</v>
+        <v>17228.60159792043</v>
       </c>
       <c r="O37">
-        <v>4435.870233678359</v>
+        <v>4444.979212263471</v>
       </c>
       <c r="P37">
-        <v>12757.42524569512</v>
+        <v>12783.62238565696</v>
       </c>
       <c r="Q37">
-        <v>17706.52524569512</v>
+        <v>17732.72238565695</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1073820426382248</v>
+        <v>0.1073424508601005</v>
       </c>
       <c r="T37">
         <v>1.421303715013869</v>
       </c>
       <c r="U37">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V37">
         <v>0.258</v>
       </c>
       <c r="W37">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.18701937857338</v>
+        <v>14.58188671714202</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4376,13 +4376,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08303690738209431</v>
+        <v>0.08263727771236598</v>
       </c>
       <c r="C38">
-        <v>45558.32063350771</v>
+        <v>45905.50045144468</v>
       </c>
       <c r="D38">
-        <v>34154.70977003973</v>
+        <v>34501.8895879767</v>
       </c>
       <c r="E38">
         <v>-8718.314020501366</v>
@@ -4409,37 +4409,37 @@
         <v>18497.1</v>
       </c>
       <c r="M38">
-        <v>1341.056078358706</v>
+        <v>1304.741213567561</v>
       </c>
       <c r="N38">
-        <v>17156.0439216413</v>
+        <v>17192.35878643244</v>
       </c>
       <c r="O38">
-        <v>4426.259331783454</v>
+        <v>4435.62856689957</v>
       </c>
       <c r="P38">
-        <v>12729.78458985784</v>
+        <v>12756.73021953287</v>
       </c>
       <c r="Q38">
-        <v>17678.88458985784</v>
+        <v>17705.83021953287</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1081668802845224</v>
+        <v>0.1081267839255718</v>
       </c>
       <c r="T38">
         <v>1.439417642622907</v>
       </c>
       <c r="U38">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V38">
         <v>0.258</v>
       </c>
       <c r="W38">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>13.79293550694634</v>
+        <v>14.17683430833252</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4458,13 +4458,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.08284899704934251</v>
+        <v>0.08243905236566662</v>
       </c>
       <c r="C39">
-        <v>45011.01827993338</v>
+        <v>45371.63024502341</v>
       </c>
       <c r="D39">
-        <v>34327.94044803573</v>
+        <v>34688.55241312576</v>
       </c>
       <c r="E39">
         <v>-7997.78098893103</v>
@@ -4491,37 +4491,37 @@
         <v>18497.1</v>
       </c>
       <c r="M39">
-        <v>1378.307636090892</v>
+        <v>1340.984025055548</v>
       </c>
       <c r="N39">
-        <v>17118.79236390911</v>
+        <v>17156.11597494445</v>
       </c>
       <c r="O39">
-        <v>4416.648429888551</v>
+        <v>4426.277921535669</v>
       </c>
       <c r="P39">
-        <v>12702.14393402056</v>
+        <v>12729.83805340878</v>
       </c>
       <c r="Q39">
-        <v>17651.24393402056</v>
+        <v>17678.93805340878</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1089766334116548</v>
+        <v>0.1089360164534391</v>
       </c>
       <c r="T39">
         <v>1.458106615552867</v>
       </c>
       <c r="U39">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V39">
         <v>0.258</v>
       </c>
       <c r="W39">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.42015346621806</v>
+        <v>13.79367662432353</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4540,13 +4540,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08266108671659073</v>
+        <v>0.08224082701896729</v>
       </c>
       <c r="C40">
-        <v>44465.48211597764</v>
+        <v>44839.79079949631</v>
       </c>
       <c r="D40">
-        <v>34502.93731565034</v>
+        <v>34877.24599916899</v>
       </c>
       <c r="E40">
         <v>-7277.247957360698</v>
@@ -4573,37 +4573,37 @@
         <v>18497.1</v>
       </c>
       <c r="M40">
-        <v>1415.559193823078</v>
+        <v>1377.226836543536</v>
       </c>
       <c r="N40">
-        <v>17081.54080617692</v>
+        <v>17119.87316345646</v>
       </c>
       <c r="O40">
-        <v>4407.037527993646</v>
+        <v>4416.927276171768</v>
       </c>
       <c r="P40">
-        <v>12674.50327818328</v>
+        <v>12702.9458872847</v>
       </c>
       <c r="Q40">
-        <v>17623.60327818328</v>
+        <v>17652.04588728469</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1098125076074044</v>
+        <v>0.1097713532563989</v>
       </c>
       <c r="T40">
         <v>1.477398458577341</v>
       </c>
       <c r="U40">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V40">
         <v>0.258</v>
       </c>
       <c r="W40">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.06699153289653</v>
+        <v>13.43068513420975</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4622,13 +4622,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08247317638383894</v>
+        <v>0.08204260167226796</v>
       </c>
       <c r="C41">
-        <v>43921.73929107058</v>
+        <v>44310.01543600456</v>
       </c>
       <c r="D41">
-        <v>34679.72752231362</v>
+        <v>35068.00366724758</v>
       </c>
       <c r="E41">
         <v>-6556.714925790362</v>
@@ -4655,37 +4655,37 @@
         <v>18497.1</v>
       </c>
       <c r="M41">
-        <v>1452.810751555264</v>
+        <v>1413.469648031524</v>
       </c>
       <c r="N41">
-        <v>17044.28924844474</v>
+        <v>17083.63035196848</v>
       </c>
       <c r="O41">
-        <v>4397.426626098742</v>
+        <v>4407.576630807867</v>
       </c>
       <c r="P41">
-        <v>12646.86262234599</v>
+        <v>12676.05372116061</v>
       </c>
       <c r="Q41">
-        <v>17595.96262234599</v>
+        <v>17625.15372116061</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1106757875144901</v>
+        <v>0.1106340781512589</v>
       </c>
       <c r="T41">
         <v>1.497322821045242</v>
       </c>
       <c r="U41">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V41">
         <v>0.258</v>
       </c>
       <c r="W41">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>12.73194046795047</v>
+        <v>13.08630859230694</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4704,13 +4704,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.08228526605108716</v>
+        <v>0.08184437632556862</v>
       </c>
       <c r="C42">
-        <v>43379.81751395388</v>
+        <v>43782.33820868524</v>
       </c>
       <c r="D42">
-        <v>34858.33877676725</v>
+        <v>35260.8594714986</v>
       </c>
       <c r="E42">
         <v>-5836.181894220026</v>
@@ -4737,37 +4737,37 @@
         <v>18497.1</v>
       </c>
       <c r="M42">
-        <v>1490.062309287451</v>
+        <v>1449.712459519512</v>
       </c>
       <c r="N42">
-        <v>17007.03769071255</v>
+        <v>17047.38754048049</v>
       </c>
       <c r="O42">
-        <v>4387.815724203838</v>
+        <v>4398.225985443966</v>
       </c>
       <c r="P42">
-        <v>12619.22196650871</v>
+        <v>12649.16155503652</v>
       </c>
       <c r="Q42">
-        <v>17568.32196650871</v>
+        <v>17598.26155503652</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1115678434184786</v>
+        <v>0.1115255605426144</v>
       </c>
       <c r="T42">
         <v>1.517911328928739</v>
       </c>
       <c r="U42">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V42">
         <v>0.258</v>
       </c>
       <c r="W42">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.4136419562517</v>
+        <v>12.75915087749927</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4786,13 +4786,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.08209735571833535</v>
+        <v>0.08164615097886926</v>
       </c>
       <c r="C43">
-        <v>42839.74506715857</v>
+        <v>43256.79392493822</v>
       </c>
       <c r="D43">
-        <v>35038.79936154227</v>
+        <v>35455.84821932191</v>
       </c>
       <c r="E43">
         <v>-5115.648862649694</v>
@@ -4819,37 +4819,37 @@
         <v>18497.1</v>
       </c>
       <c r="M43">
-        <v>1527.313867019637</v>
+        <v>1485.9552710075</v>
       </c>
       <c r="N43">
-        <v>16969.78613298036</v>
+        <v>17011.1447289925</v>
       </c>
       <c r="O43">
-        <v>4378.204822308934</v>
+        <v>4388.875340080065</v>
       </c>
       <c r="P43">
-        <v>12591.58131067143</v>
+        <v>12622.26938891244</v>
       </c>
       <c r="Q43">
-        <v>17540.68131067143</v>
+        <v>17571.36938891243</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1124901385056531</v>
+        <v>0.1124472626760496</v>
       </c>
       <c r="T43">
         <v>1.53919775233371</v>
       </c>
       <c r="U43">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V43">
         <v>0.258</v>
       </c>
       <c r="W43">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>12.11087020122117</v>
+        <v>12.44795207560904</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4868,13 +4868,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.08190944538558358</v>
+        <v>0.08144792563216996</v>
       </c>
       <c r="C44">
-        <v>42301.55082193467</v>
+        <v>42733.41816636921</v>
       </c>
       <c r="D44">
-        <v>35221.13814788869</v>
+        <v>35653.00549232324</v>
       </c>
       <c r="E44">
         <v>-4395.115831079362</v>
@@ -4901,37 +4901,37 @@
         <v>18497.1</v>
       </c>
       <c r="M44">
-        <v>1564.565424751823</v>
+        <v>1522.198082495487</v>
       </c>
       <c r="N44">
-        <v>16932.53457524818</v>
+        <v>16974.90191750451</v>
       </c>
       <c r="O44">
-        <v>4368.59392041403</v>
+        <v>4379.524694716165</v>
       </c>
       <c r="P44">
-        <v>12563.94065483415</v>
+        <v>12595.37722278835</v>
       </c>
       <c r="Q44">
-        <v>17513.04065483415</v>
+        <v>17544.47722278835</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1134442368716958</v>
+        <v>0.1134007476416723</v>
       </c>
       <c r="T44">
         <v>1.561218190338853</v>
       </c>
       <c r="U44">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V44">
         <v>0.258</v>
       </c>
       <c r="W44">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.82251614881115</v>
+        <v>12.15157226428502</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4950,13 +4950,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.08172153505283179</v>
+        <v>0.0812497002854706</v>
       </c>
       <c r="C45">
-        <v>41765.26425364972</v>
+        <v>42212.24731043587</v>
       </c>
       <c r="D45">
-        <v>35405.38461117408</v>
+        <v>35852.36766796021</v>
       </c>
       <c r="E45">
         <v>-3674.582799509026</v>
@@ -4983,37 +4983,37 @@
         <v>18497.1</v>
       </c>
       <c r="M45">
-        <v>1601.81698248401</v>
+        <v>1558.440893983475</v>
       </c>
       <c r="N45">
-        <v>16895.28301751599</v>
+        <v>16938.65910601653</v>
       </c>
       <c r="O45">
-        <v>4358.983018519126</v>
+        <v>4370.174049352264</v>
       </c>
       <c r="P45">
-        <v>12536.29999899686</v>
+        <v>12568.48505666426</v>
       </c>
       <c r="Q45">
-        <v>17485.39999899687</v>
+        <v>17517.58505666426</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1144318123733891</v>
+        <v>0.1143876882201239</v>
       </c>
       <c r="T45">
         <v>1.584011275291545</v>
       </c>
       <c r="U45">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V45">
         <v>0.258</v>
       </c>
       <c r="W45">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.54757391279228</v>
+        <v>11.86897756046443</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5032,13 +5032,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.08153362472007999</v>
+        <v>0.08105147493877127</v>
       </c>
       <c r="C46">
-        <v>41230.91545767283</v>
+        <v>41693.31855282334</v>
       </c>
       <c r="D46">
-        <v>35591.56884676752</v>
+        <v>36053.97194191803</v>
       </c>
       <c r="E46">
         <v>-2954.049767938694</v>
@@ -5065,37 +5065,37 @@
         <v>18497.1</v>
       </c>
       <c r="M46">
-        <v>1639.068540216196</v>
+        <v>1594.683705471463</v>
       </c>
       <c r="N46">
-        <v>16858.03145978381</v>
+        <v>16902.41629452854</v>
       </c>
       <c r="O46">
-        <v>4349.372116624222</v>
+        <v>4360.823403988363</v>
       </c>
       <c r="P46">
-        <v>12508.65934315959</v>
+        <v>12541.59289054018</v>
       </c>
       <c r="Q46">
-        <v>17457.75934315959</v>
+        <v>17490.69289054017</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1154546584287143</v>
+        <v>0.1154098766763773</v>
       </c>
       <c r="T46">
         <v>1.607618398992547</v>
       </c>
       <c r="U46">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V46">
         <v>0.258</v>
       </c>
       <c r="W46">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.28512905113791</v>
+        <v>11.59922807045388</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5114,13 +5114,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.0813457143873282</v>
+        <v>0.08085324959207192</v>
       </c>
       <c r="C47">
-        <v>40698.5351657627</v>
+        <v>41176.66993058011</v>
       </c>
       <c r="D47">
-        <v>35779.72158642772</v>
+        <v>36257.85635124514</v>
       </c>
       <c r="E47">
         <v>-2233.516736368358</v>
@@ -5147,37 +5147,37 @@
         <v>18497.1</v>
       </c>
       <c r="M47">
-        <v>1676.320097948382</v>
+        <v>1630.926516959451</v>
       </c>
       <c r="N47">
-        <v>16820.77990205162</v>
+        <v>16866.17348304055</v>
       </c>
       <c r="O47">
-        <v>4339.761214729318</v>
+        <v>4351.472758624463</v>
       </c>
       <c r="P47">
-        <v>12481.0186873223</v>
+        <v>12514.70072441609</v>
       </c>
       <c r="Q47">
-        <v>17430.1186873223</v>
+        <v>17463.80072441609</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1165146988860513</v>
+        <v>0.1164692356219489</v>
       </c>
       <c r="T47">
         <v>1.632083963555404</v>
       </c>
       <c r="U47">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V47">
         <v>0.258</v>
       </c>
       <c r="W47">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.03434840555707</v>
+        <v>11.34146744666602</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5196,13 +5196,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.08115780405457643</v>
+        <v>0.08065502424537259</v>
       </c>
       <c r="C48">
-        <v>40168.15476297818</v>
+        <v>40662.34034604237</v>
       </c>
       <c r="D48">
-        <v>35969.87421521353</v>
+        <v>36464.05979827773</v>
       </c>
       <c r="E48">
         <v>-1512.983704798025</v>
@@ -5229,37 +5229,37 @@
         <v>18497.1</v>
       </c>
       <c r="M48">
-        <v>1713.571655680568</v>
+        <v>1667.169328447439</v>
       </c>
       <c r="N48">
-        <v>16783.52834431943</v>
+        <v>16829.93067155256</v>
       </c>
       <c r="O48">
-        <v>4330.150312834414</v>
+        <v>4342.122113260561</v>
       </c>
       <c r="P48">
-        <v>12453.37803148502</v>
+        <v>12487.808558292</v>
       </c>
       <c r="Q48">
-        <v>17402.47803148502</v>
+        <v>17436.908558292</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1176140001010674</v>
+        <v>0.1175678300840233</v>
       </c>
       <c r="T48">
         <v>1.657455660139107</v>
       </c>
       <c r="U48">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V48">
         <v>0.258</v>
       </c>
       <c r="W48">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.79447126630583</v>
+        <v>11.0949138065211</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5278,13 +5278,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.08096989372182462</v>
+        <v>0.08045679889867324</v>
       </c>
       <c r="C49">
-        <v>39639.8063051311</v>
+        <v>40150.36959157996</v>
       </c>
       <c r="D49">
-        <v>36162.0587889368</v>
+        <v>36672.62207538567</v>
       </c>
       <c r="E49">
         <v>-792.4506732276859</v>
@@ -5311,37 +5311,37 @@
         <v>18497.1</v>
       </c>
       <c r="M49">
-        <v>1750.823213412755</v>
+        <v>1703.412139935427</v>
       </c>
       <c r="N49">
-        <v>16746.27678658725</v>
+        <v>16793.68786006458</v>
       </c>
       <c r="O49">
-        <v>4320.53941093951</v>
+        <v>4332.77146789666</v>
       </c>
       <c r="P49">
-        <v>12425.73737564774</v>
+        <v>12460.91639216792</v>
       </c>
       <c r="Q49">
-        <v>17374.83737564774</v>
+        <v>17410.01639216791</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1187547843808012</v>
+        <v>0.1187078809408929</v>
       </c>
       <c r="T49">
         <v>1.683784779235403</v>
       </c>
       <c r="U49">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V49">
         <v>0.258</v>
       </c>
       <c r="W49">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.56480166489507</v>
+        <v>10.85885181063767</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5360,13 +5360,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.08078198338907283</v>
+        <v>0.08025857355197391</v>
       </c>
       <c r="C50">
-        <v>39113.52253680127</v>
+        <v>39640.79837519628</v>
       </c>
       <c r="D50">
-        <v>36356.3080521773</v>
+        <v>36883.58389057231</v>
       </c>
       <c r="E50">
         <v>-71.91764165736095</v>
@@ -5393,37 +5393,37 @@
         <v>18497.1</v>
       </c>
       <c r="M50">
-        <v>1788.074771144941</v>
+        <v>1739.654951423414</v>
       </c>
       <c r="N50">
-        <v>16709.02522885506</v>
+        <v>16757.44504857659</v>
       </c>
       <c r="O50">
-        <v>4310.928509044606</v>
+        <v>4323.42082253276</v>
       </c>
       <c r="P50">
-        <v>12398.09671981046</v>
+        <v>12434.02422604383</v>
       </c>
       <c r="Q50">
-        <v>17347.19671981045</v>
+        <v>17383.12422604383</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1199394449789862</v>
+        <v>0.1198917799076421</v>
       </c>
       <c r="T50">
         <v>1.711126556758479</v>
       </c>
       <c r="U50">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V50">
         <v>0.258</v>
       </c>
       <c r="W50">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.34470163020976</v>
+        <v>10.63262573124939</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5442,13 +5442,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.08059407305632105</v>
+        <v>0.08006034820527456</v>
       </c>
       <c r="C51">
-        <v>38589.33690993553</v>
+        <v>39133.66834701684</v>
       </c>
       <c r="D51">
-        <v>36552.6554568819</v>
+        <v>37096.9868939632</v>
       </c>
       <c r="E51">
         <v>648.6153899129786</v>
@@ -5475,37 +5475,37 @@
         <v>18497.1</v>
       </c>
       <c r="M51">
-        <v>1825.326328877127</v>
+        <v>1775.897762911402</v>
       </c>
       <c r="N51">
-        <v>16671.77367112288</v>
+        <v>16721.2022370886</v>
       </c>
       <c r="O51">
-        <v>4301.317607149702</v>
+        <v>4314.070177168859</v>
       </c>
       <c r="P51">
-        <v>12370.45606397317</v>
+        <v>12407.13205991974</v>
       </c>
       <c r="Q51">
-        <v>17319.55606397317</v>
+        <v>17356.23205991974</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1211705628555315</v>
+        <v>0.1211221062848521</v>
       </c>
       <c r="T51">
         <v>1.739540560851088</v>
       </c>
       <c r="U51">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V51">
         <v>0.258</v>
       </c>
       <c r="W51">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.13358527040955</v>
+        <v>10.41563336938716</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5524,13 +5524,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.08040616272356926</v>
+        <v>0.07986212285857522</v>
       </c>
       <c r="C52">
-        <v>38067.28360305268</v>
+        <v>38629.02212670277</v>
       </c>
       <c r="D52">
-        <v>36751.13518156938</v>
+        <v>37312.87370521946</v>
       </c>
       <c r="E52">
         <v>1369.148421483311</v>
@@ -5557,37 +5557,37 @@
         <v>18497.1</v>
       </c>
       <c r="M52">
-        <v>1862.577886609314</v>
+        <v>1812.14057439939</v>
       </c>
       <c r="N52">
-        <v>16634.52211339069</v>
+        <v>16684.95942560061</v>
       </c>
       <c r="O52">
-        <v>4291.706705254798</v>
+        <v>4304.719531804958</v>
       </c>
       <c r="P52">
-        <v>12342.81540813589</v>
+        <v>12380.23989379566</v>
       </c>
       <c r="Q52">
-        <v>17291.91540813589</v>
+        <v>17329.33989379565</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1224509254471385</v>
+        <v>0.1224016457171505</v>
       </c>
       <c r="T52">
         <v>1.769091125107402</v>
       </c>
       <c r="U52">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V52">
         <v>0.258</v>
       </c>
       <c r="W52">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.930913565001363</v>
+        <v>10.20732070199941</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5606,13 +5606,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.08021825239081747</v>
+        <v>0.07966389751187589</v>
       </c>
       <c r="C53">
-        <v>37547.39754107739</v>
+        <v>38126.90333182718</v>
       </c>
       <c r="D53">
-        <v>36951.78215116442</v>
+        <v>37531.28794191421</v>
       </c>
       <c r="E53">
         <v>2089.681453053643</v>
@@ -5639,37 +5639,37 @@
         <v>18497.1</v>
       </c>
       <c r="M53">
-        <v>1899.8294443415</v>
+        <v>1848.383385887378</v>
       </c>
       <c r="N53">
-        <v>16597.2705556585</v>
+        <v>16648.71661411263</v>
       </c>
       <c r="O53">
-        <v>4282.095803359894</v>
+        <v>4295.368886441058</v>
       </c>
       <c r="P53">
-        <v>12315.17475229861</v>
+        <v>12353.34772767157</v>
       </c>
       <c r="Q53">
-        <v>17264.27475229861</v>
+        <v>17302.44772767157</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1237835477363622</v>
+        <v>0.1237334112487263</v>
       </c>
       <c r="T53">
         <v>1.799847834843564</v>
       </c>
       <c r="U53">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V53">
         <v>0.258</v>
       </c>
       <c r="W53">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.736189769609181</v>
+        <v>10.00717715882296</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5688,13 +5688,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.08003034205806568</v>
+        <v>0.07946567216517655</v>
       </c>
       <c r="C54">
-        <v>37029.71441582754</v>
+        <v>37627.35660725398</v>
       </c>
       <c r="D54">
-        <v>37154.63205748491</v>
+        <v>37752.27424891134</v>
       </c>
       <c r="E54">
         <v>2810.214484623983</v>
@@ -5721,37 +5721,37 @@
         <v>18497.1</v>
       </c>
       <c r="M54">
-        <v>1937.081002073686</v>
+        <v>1884.626197375366</v>
       </c>
       <c r="N54">
-        <v>16560.01899792632</v>
+        <v>16612.47380262464</v>
       </c>
       <c r="O54">
-        <v>4272.48490146499</v>
+        <v>4286.018241077157</v>
       </c>
       <c r="P54">
-        <v>12287.53409646133</v>
+        <v>12326.45556154748</v>
       </c>
       <c r="Q54">
-        <v>17236.63409646133</v>
+        <v>17275.55556154748</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1251716959543035</v>
+        <v>0.1251206670107845</v>
       </c>
       <c r="T54">
         <v>1.831886074152067</v>
       </c>
       <c r="U54">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V54">
         <v>0.258</v>
       </c>
       <c r="W54">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.548955350962848</v>
+        <v>9.814731444230206</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5770,13 +5770,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.07984243172531388</v>
+        <v>0.07926744681847721</v>
       </c>
       <c r="C55">
-        <v>36514.27070718008</v>
+        <v>37130.42765556067</v>
       </c>
       <c r="D55">
-        <v>37359.72138040778</v>
+        <v>37975.87832878837</v>
       </c>
       <c r="E55">
         <v>3530.747516194315</v>
@@ -5803,37 +5803,37 @@
         <v>18497.1</v>
       </c>
       <c r="M55">
-        <v>1974.332559805872</v>
+        <v>1920.869008863353</v>
       </c>
       <c r="N55">
-        <v>16522.76744019413</v>
+        <v>16576.23099113665</v>
       </c>
       <c r="O55">
-        <v>4262.873999570085</v>
+        <v>4276.667595713256</v>
       </c>
       <c r="P55">
-        <v>12259.89344062404</v>
+        <v>12299.56339542339</v>
       </c>
       <c r="Q55">
-        <v>17208.99344062404</v>
+        <v>17248.66339542339</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1266189143091785</v>
+        <v>0.1265669549329302</v>
       </c>
       <c r="T55">
         <v>1.865287642792847</v>
       </c>
       <c r="U55">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V55">
         <v>0.258</v>
       </c>
       <c r="W55">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.368786382076758</v>
+        <v>9.62954783207492</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5852,13 +5852,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.0796545213925621</v>
+        <v>0.07906922147177788</v>
       </c>
       <c r="C56">
-        <v>36001.10370494161</v>
+        <v>36636.16326854884</v>
       </c>
       <c r="D56">
-        <v>37567.08740973964</v>
+        <v>38202.14697334688</v>
       </c>
       <c r="E56">
         <v>4251.280547764647</v>
@@ -5885,37 +5885,37 @@
         <v>18497.1</v>
       </c>
       <c r="M56">
-        <v>2011.584117538059</v>
+        <v>1957.111820351341</v>
       </c>
       <c r="N56">
-        <v>16485.51588246194</v>
+        <v>16539.98817964866</v>
       </c>
       <c r="O56">
-        <v>4253.263097675182</v>
+        <v>4267.316950349355</v>
       </c>
       <c r="P56">
-        <v>12232.25278478676</v>
+        <v>12272.67122929931</v>
       </c>
       <c r="Q56">
-        <v>17181.35278478676</v>
+        <v>17221.77122929931</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1281290552012219</v>
+        <v>0.1280761249386476</v>
       </c>
       <c r="T56">
         <v>1.900141453548443</v>
       </c>
       <c r="U56">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V56">
         <v>0.258</v>
       </c>
       <c r="W56">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>9.195290337964225</v>
+        <v>9.451222872221681</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5934,13 +5934,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.0794666110598103</v>
+        <v>0.07887099612507853</v>
       </c>
       <c r="C57">
-        <v>35490.25153145168</v>
+        <v>36144.61135988784</v>
       </c>
       <c r="D57">
-        <v>37776.76826782004</v>
+        <v>38431.12809625622</v>
       </c>
       <c r="E57">
         <v>4971.813579334987</v>
@@ -5967,37 +5967,37 @@
         <v>18497.1</v>
       </c>
       <c r="M57">
-        <v>2048.835675270245</v>
+        <v>1993.354631839329</v>
       </c>
       <c r="N57">
-        <v>16448.26432472976</v>
+        <v>16503.74536816067</v>
       </c>
       <c r="O57">
-        <v>4243.652195780277</v>
+        <v>4257.966304985453</v>
       </c>
       <c r="P57">
-        <v>12204.61212894948</v>
+        <v>12245.77906317522</v>
       </c>
       <c r="Q57">
-        <v>17153.71212894948</v>
+        <v>17194.87906317522</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1297063134662451</v>
+        <v>0.1296523691668412</v>
       </c>
       <c r="T57">
         <v>1.936544322559844</v>
       </c>
       <c r="U57">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V57">
         <v>0.258</v>
       </c>
       <c r="W57">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.028103240910328</v>
+        <v>9.279382456363102</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6016,13 +6016,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07927870072705852</v>
+        <v>0.0786727707783792</v>
       </c>
       <c r="C58">
-        <v>34981.75316494693</v>
+        <v>35655.82099893953</v>
       </c>
       <c r="D58">
-        <v>37988.80293288563</v>
+        <v>38662.87076687824</v>
       </c>
       <c r="E58">
         <v>5692.346610905319</v>
@@ -6049,37 +6049,37 @@
         <v>18497.1</v>
       </c>
       <c r="M58">
-        <v>2086.087233002431</v>
+        <v>2029.597443327317</v>
       </c>
       <c r="N58">
-        <v>16411.01276699757</v>
+        <v>16467.50255667268</v>
       </c>
       <c r="O58">
-        <v>4234.041293885373</v>
+        <v>4248.615659621552</v>
       </c>
       <c r="P58">
-        <v>12176.9714731122</v>
+        <v>12218.88689705113</v>
       </c>
       <c r="Q58">
-        <v>17126.0714731122</v>
+        <v>17167.98689705113</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1313552652887694</v>
+        <v>0.1313002608599527</v>
       </c>
       <c r="T58">
         <v>1.974601867435399</v>
       </c>
       <c r="U58">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V58">
         <v>0.258</v>
       </c>
       <c r="W58">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.86688711160836</v>
+        <v>9.113679198213761</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6098,13 +6098,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07909079039430672</v>
+        <v>0.07847454543167985</v>
       </c>
       <c r="C59">
-        <v>34475.64846371693</v>
+        <v>35169.84244581424</v>
       </c>
       <c r="D59">
-        <v>38203.23126322596</v>
+        <v>38897.42524532328</v>
       </c>
       <c r="E59">
         <v>6412.879642475651</v>
@@ -6131,37 +6131,37 @@
         <v>18497.1</v>
       </c>
       <c r="M59">
-        <v>2123.338790734617</v>
+        <v>2065.840254815304</v>
       </c>
       <c r="N59">
-        <v>16373.76120926539</v>
+        <v>16431.2597451847</v>
       </c>
       <c r="O59">
-        <v>4224.43039199047</v>
+        <v>4239.265014257651</v>
       </c>
       <c r="P59">
-        <v>12149.33081727492</v>
+        <v>12191.99473092704</v>
       </c>
       <c r="Q59">
-        <v>17098.43081727492</v>
+        <v>17141.09473092704</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1330809125448994</v>
+        <v>0.1330247986783253</v>
       </c>
       <c r="T59">
         <v>2.014429530677258</v>
       </c>
       <c r="U59">
-        <v>0.0517</v>
+        <v>0.0503</v>
       </c>
       <c r="V59">
         <v>0.258</v>
       </c>
       <c r="W59">
-        <v>0.0383614</v>
+        <v>0.0373226</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.711327688597688</v>
+        <v>8.95379008947317</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6180,13 +6180,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.07937627606155494</v>
+        <v>0.07827632008498052</v>
       </c>
       <c r="C60">
-        <v>33430.28861251283</v>
+        <v>34686.72718771054</v>
       </c>
       <c r="D60">
-        <v>37878.4044435922</v>
+        <v>39134.8430187899</v>
       </c>
       <c r="E60">
         <v>7133.412674045983</v>
@@ -6213,45 +6213,45 @@
         <v>18497.1</v>
       </c>
       <c r="M60">
-        <v>2206.560355880991</v>
+        <v>2102.083066303293</v>
       </c>
       <c r="N60">
-        <v>16290.53964411901</v>
+        <v>16395.01693369671</v>
       </c>
       <c r="O60">
-        <v>4202.959228182705</v>
+        <v>4229.914368893751</v>
       </c>
       <c r="P60">
-        <v>12087.58041593631</v>
+        <v>12165.10256480296</v>
       </c>
       <c r="Q60">
-        <v>17036.68041593631</v>
+        <v>17114.20256480296</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1348887334798927</v>
+        <v>0.1348314573451917</v>
       </c>
       <c r="T60">
         <v>2.056153749311588</v>
       </c>
       <c r="U60">
-        <v>0.0528</v>
+        <v>0.0503</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0391776</v>
+        <v>0.0373226</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y60">
-        <v>8.382775458963078</v>
+        <v>8.799414398275356</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6262,13 +6262,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.07919652772880315</v>
+        <v>0.07873476473828117</v>
       </c>
       <c r="C61">
-        <v>32913.62647738188</v>
+        <v>33421.44578212583</v>
       </c>
       <c r="D61">
-        <v>38082.27534003159</v>
+        <v>38590.09464477553</v>
       </c>
       <c r="E61">
         <v>7853.945705616316</v>
@@ -6295,37 +6295,37 @@
         <v>18497.1</v>
       </c>
       <c r="M61">
-        <v>2244.604499947905</v>
+        <v>2202.093051085255</v>
       </c>
       <c r="N61">
-        <v>16252.4955000521</v>
+        <v>16295.00694891475</v>
       </c>
       <c r="O61">
-        <v>4193.143839013441</v>
+        <v>4204.111792820006</v>
       </c>
       <c r="P61">
-        <v>12059.35166103866</v>
+        <v>12090.89515609474</v>
       </c>
       <c r="Q61">
-        <v>17008.45166103866</v>
+        <v>17039.99515609474</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1367847408019589</v>
+        <v>0.1367262457031248</v>
       </c>
       <c r="T61">
         <v>2.099913295684177</v>
       </c>
       <c r="U61">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V61">
         <v>0.258</v>
       </c>
       <c r="W61">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.24069451898065</v>
+        <v>8.39978128575634</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6344,13 +6344,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.07901677939605135</v>
+        <v>0.07854766939158184</v>
       </c>
       <c r="C62">
-        <v>32399.17078456098</v>
+        <v>32921.38728418994</v>
       </c>
       <c r="D62">
-        <v>38288.35267878102</v>
+        <v>38810.56917840998</v>
       </c>
       <c r="E62">
         <v>8574.478737186648</v>
@@ -6377,37 +6377,37 @@
         <v>18497.1</v>
       </c>
       <c r="M62">
-        <v>2282.648644014818</v>
+        <v>2239.416662120598</v>
       </c>
       <c r="N62">
-        <v>16214.45135598518</v>
+        <v>16257.6833378794</v>
       </c>
       <c r="O62">
-        <v>4183.328449844177</v>
+        <v>4194.482301172886</v>
       </c>
       <c r="P62">
-        <v>12031.12290614101</v>
+        <v>12063.20103670652</v>
       </c>
       <c r="Q62">
-        <v>16980.222906141</v>
+        <v>17012.30103670651</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1387755484901284</v>
+        <v>0.1387157734789546</v>
       </c>
       <c r="T62">
         <v>2.145860819375395</v>
       </c>
       <c r="U62">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V62">
         <v>0.258</v>
       </c>
       <c r="W62">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.103349610330975</v>
+        <v>8.259784930993735</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.07883703106329956</v>
+        <v>0.0783605740448825</v>
       </c>
       <c r="C63">
-        <v>31886.95754857509</v>
+        <v>32423.86251058288</v>
       </c>
       <c r="D63">
-        <v>38496.67247436546</v>
+        <v>39033.57743637325</v>
       </c>
       <c r="E63">
         <v>9295.011768756987</v>
@@ -6459,37 +6459,37 @@
         <v>18497.1</v>
       </c>
       <c r="M63">
-        <v>2320.692788081732</v>
+        <v>2276.740273155941</v>
       </c>
       <c r="N63">
-        <v>16176.40721191827</v>
+        <v>16220.35972684406</v>
       </c>
       <c r="O63">
-        <v>4173.513060674914</v>
+        <v>4184.852809525768</v>
       </c>
       <c r="P63">
-        <v>12002.89415124336</v>
+        <v>12035.50691731829</v>
       </c>
       <c r="Q63">
-        <v>16951.99415124335</v>
+        <v>16984.60691731829</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1408684488802553</v>
+        <v>0.1408073283202115</v>
       </c>
       <c r="T63">
         <v>2.194164626332831</v>
       </c>
       <c r="U63">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V63">
         <v>0.258</v>
       </c>
       <c r="W63">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.970507813440301</v>
+        <v>8.124378620649575</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.07865728273054778</v>
+        <v>0.07817347869818317</v>
       </c>
       <c r="C64">
-        <v>31377.02357203024</v>
+        <v>31928.91539059958</v>
       </c>
       <c r="D64">
-        <v>38707.27152939094</v>
+        <v>39259.1633479603</v>
       </c>
       <c r="E64">
         <v>10015.54480032732</v>
@@ -6541,37 +6541,37 @@
         <v>18497.1</v>
       </c>
       <c r="M64">
-        <v>2358.736932148645</v>
+        <v>2314.063884191285</v>
       </c>
       <c r="N64">
-        <v>16138.36306785136</v>
+        <v>16183.03611580872</v>
       </c>
       <c r="O64">
-        <v>4163.69767150565</v>
+        <v>4175.223317878649</v>
       </c>
       <c r="P64">
-        <v>11974.66539634571</v>
+        <v>12007.81279793007</v>
       </c>
       <c r="Q64">
-        <v>16923.76539634571</v>
+        <v>16956.91279793007</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1430715019224942</v>
+        <v>0.1430089649952188</v>
       </c>
       <c r="T64">
         <v>2.245010738919605</v>
       </c>
       <c r="U64">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V64">
         <v>0.258</v>
       </c>
       <c r="W64">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.841951235804168</v>
+        <v>7.993340255800388</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6590,13 +6590,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.07847753439779599</v>
+        <v>0.07798638335148383</v>
       </c>
       <c r="C65">
-        <v>30869.40646728846</v>
+        <v>31436.59087495665</v>
       </c>
       <c r="D65">
-        <v>38920.18745621951</v>
+        <v>39487.37186388769</v>
       </c>
       <c r="E65">
         <v>10736.07783189765</v>
@@ -6623,37 +6623,37 @@
         <v>18497.1</v>
       </c>
       <c r="M65">
-        <v>2396.781076215559</v>
+        <v>2351.387495226628</v>
       </c>
       <c r="N65">
-        <v>16100.31892378444</v>
+        <v>16145.71250477338</v>
       </c>
       <c r="O65">
-        <v>4153.882282336386</v>
+        <v>4165.593826231531</v>
       </c>
       <c r="P65">
-        <v>11946.43664144806</v>
+        <v>11980.11867854184</v>
       </c>
       <c r="Q65">
-        <v>16895.53664144806</v>
+        <v>16929.21867854184</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1453936389129621</v>
+        <v>0.1453296090580644</v>
       </c>
       <c r="T65">
         <v>2.298605290024583</v>
       </c>
       <c r="U65">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V65">
         <v>0.258</v>
       </c>
       <c r="W65">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.717475819362832</v>
+        <v>7.866461839041652</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6672,13 +6672,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.07829778606504419</v>
+        <v>0.07779928800478449</v>
       </c>
       <c r="C66">
-        <v>30364.14467886193</v>
+        <v>30946.93496565277</v>
       </c>
       <c r="D66">
-        <v>39135.45869936331</v>
+        <v>39718.24898615415</v>
       </c>
       <c r="E66">
         <v>11456.61086346798</v>
@@ -6705,37 +6705,37 @@
         <v>18497.1</v>
       </c>
       <c r="M66">
-        <v>2434.825220282472</v>
+        <v>2388.711106261971</v>
       </c>
       <c r="N66">
-        <v>16062.27477971753</v>
+        <v>16108.38889373803</v>
       </c>
       <c r="O66">
-        <v>4144.066893167123</v>
+        <v>4155.964334584412</v>
       </c>
       <c r="P66">
-        <v>11918.20788655041</v>
+        <v>11952.42455915362</v>
       </c>
       <c r="Q66">
-        <v>16867.30788655041</v>
+        <v>16901.52455915361</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1478447835140116</v>
+        <v>0.147779177791068</v>
       </c>
       <c r="T66">
         <v>2.355177316190948</v>
       </c>
       <c r="U66">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V66">
         <v>0.258</v>
       </c>
       <c r="W66">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.596890259685289</v>
+        <v>7.743548372806626</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6754,13 +6754,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.07811803773229241</v>
+        <v>0.07761219265808514</v>
       </c>
       <c r="C67">
-        <v>29861.27750655438</v>
+        <v>30459.99474688301</v>
       </c>
       <c r="D67">
-        <v>39353.12455862609</v>
+        <v>39951.84179895472</v>
       </c>
       <c r="E67">
         <v>12177.14389503832</v>
@@ -6787,37 +6787,37 @@
         <v>18497.1</v>
       </c>
       <c r="M67">
-        <v>2472.869364349386</v>
+        <v>2426.034717297315</v>
       </c>
       <c r="N67">
-        <v>16024.23063565062</v>
+        <v>16071.06528270269</v>
       </c>
       <c r="O67">
-        <v>4134.251503997859</v>
+        <v>4146.334842937294</v>
       </c>
       <c r="P67">
-        <v>11889.97913165276</v>
+        <v>11924.73043976539</v>
       </c>
       <c r="Q67">
-        <v>16839.07913165275</v>
+        <v>16873.83043976539</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1504359935208354</v>
+        <v>0.1503687218802433</v>
       </c>
       <c r="T67">
         <v>2.41498202956682</v>
       </c>
       <c r="U67">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V67">
         <v>0.258</v>
       </c>
       <c r="W67">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.480015024920899</v>
+        <v>7.624416859378831</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6836,13 +6836,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.07793828939954062</v>
+        <v>0.0774250973113858</v>
       </c>
       <c r="C68">
-        <v>29360.84512937942</v>
+        <v>29975.81841705035</v>
       </c>
       <c r="D68">
-        <v>39573.22521302146</v>
+        <v>40188.19850069239</v>
       </c>
       <c r="E68">
         <v>12897.67692660866</v>
@@ -6869,37 +6869,37 @@
         <v>18497.1</v>
       </c>
       <c r="M68">
-        <v>2510.9135084163</v>
+        <v>2463.358328332658</v>
       </c>
       <c r="N68">
-        <v>15986.1864915837</v>
+        <v>16033.74167166734</v>
       </c>
       <c r="O68">
-        <v>4124.436114828595</v>
+        <v>4136.705351290175</v>
       </c>
       <c r="P68">
-        <v>11861.75037675511</v>
+        <v>11897.03632037717</v>
       </c>
       <c r="Q68">
-        <v>16810.85037675511</v>
+        <v>16846.13632037717</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1531796276457077</v>
+        <v>0.1531105920923112</v>
       </c>
       <c r="T68">
         <v>2.47830466725892</v>
       </c>
       <c r="U68">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V68">
         <v>0.258</v>
       </c>
       <c r="W68">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.366681463937249</v>
+        <v>7.508895391812485</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6918,13 +6918,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.07775854106678884</v>
+        <v>0.07723800196468647</v>
       </c>
       <c r="C69">
-        <v>28862.88863028551</v>
+        <v>29494.45532192047</v>
       </c>
       <c r="D69">
-        <v>39795.80174549788</v>
+        <v>40427.36843713283</v>
       </c>
       <c r="E69">
         <v>13618.20995817899</v>
@@ -6951,37 +6951,37 @@
         <v>18497.1</v>
       </c>
       <c r="M69">
-        <v>2548.957652483214</v>
+        <v>2500.681939368001</v>
       </c>
       <c r="N69">
-        <v>15948.14234751679</v>
+        <v>15996.418060632</v>
       </c>
       <c r="O69">
-        <v>4114.620725659332</v>
+        <v>4127.075859643056</v>
       </c>
       <c r="P69">
-        <v>11833.52162185746</v>
+        <v>11869.34220098894</v>
       </c>
       <c r="Q69">
-        <v>16782.62162185746</v>
+        <v>16818.44220098894</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1560895426266329</v>
+        <v>0.1560186362566257</v>
       </c>
       <c r="T69">
         <v>2.545465040568724</v>
       </c>
       <c r="U69">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V69">
         <v>0.258</v>
       </c>
       <c r="W69">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.256730994326245</v>
+        <v>7.396822326263045</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7000,13 +7000,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.07757879273403703</v>
+        <v>0.07705090661798714</v>
       </c>
       <c r="C70">
-        <v>28367.45002172051</v>
+        <v>29015.95598896717</v>
       </c>
       <c r="D70">
-        <v>40020.89616850323</v>
+        <v>40669.40213574988</v>
       </c>
       <c r="E70">
         <v>14338.74298974933</v>
@@ -7033,37 +7033,37 @@
         <v>18497.1</v>
       </c>
       <c r="M70">
-        <v>2587.001796550127</v>
+        <v>2538.005550403345</v>
       </c>
       <c r="N70">
-        <v>15910.09820344987</v>
+        <v>15959.09444959666</v>
       </c>
       <c r="O70">
-        <v>4104.805336490068</v>
+        <v>4117.446367995938</v>
       </c>
       <c r="P70">
-        <v>11805.29286695981</v>
+        <v>11841.64808160072</v>
       </c>
       <c r="Q70">
-        <v>16754.3928669598</v>
+        <v>16790.74808160072</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1591813272938658</v>
+        <v>0.1591084331812098</v>
       </c>
       <c r="T70">
         <v>2.616822937210389</v>
       </c>
       <c r="U70">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V70">
         <v>0.258</v>
       </c>
       <c r="W70">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.150014362056741</v>
+        <v>7.288045527347411</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7082,13 +7082,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07739904440128526</v>
+        <v>0.0768638112712878</v>
       </c>
       <c r="C71">
-        <v>27874.57227206839</v>
+        <v>28540.37216295925</v>
       </c>
       <c r="D71">
-        <v>40248.55145042144</v>
+        <v>40914.3513413123</v>
       </c>
       <c r="E71">
         <v>15059.27602131966</v>
@@ -7115,37 +7115,37 @@
         <v>18497.1</v>
       </c>
       <c r="M71">
-        <v>2625.045940617041</v>
+        <v>2575.329161438688</v>
       </c>
       <c r="N71">
-        <v>15872.05405938296</v>
+        <v>15921.77083856132</v>
       </c>
       <c r="O71">
-        <v>4094.989947320804</v>
+        <v>4107.816876348819</v>
       </c>
       <c r="P71">
-        <v>11777.06411206216</v>
+        <v>11813.9539622125</v>
       </c>
       <c r="Q71">
-        <v>16726.16411206216</v>
+        <v>16763.05396221249</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.1624725819396299</v>
+        <v>0.1623975718428639</v>
       </c>
       <c r="T71">
         <v>2.692784569119259</v>
       </c>
       <c r="U71">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V71">
         <v>0.258</v>
       </c>
       <c r="W71">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.046390965505195</v>
+        <v>7.182421679124985</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7164,13 +7164,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07721929606853345</v>
+        <v>0.07667671592458845</v>
       </c>
       <c r="C72">
-        <v>27384.29933299371</v>
+        <v>28067.75684284107</v>
       </c>
       <c r="D72">
-        <v>40478.81154291708</v>
+        <v>41162.26905276444</v>
       </c>
       <c r="E72">
         <v>15779.80905288999</v>
@@ -7197,37 +7197,37 @@
         <v>18497.1</v>
       </c>
       <c r="M72">
-        <v>2663.090084683955</v>
+        <v>2612.652772474031</v>
       </c>
       <c r="N72">
-        <v>15834.00991531605</v>
+        <v>15884.44722752597</v>
       </c>
       <c r="O72">
-        <v>4085.174558151541</v>
+        <v>4098.1873847017</v>
       </c>
       <c r="P72">
-        <v>11748.83535716451</v>
+        <v>11786.25984282427</v>
       </c>
       <c r="Q72">
-        <v>16697.9353571645</v>
+        <v>16735.35984282427</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1659832535617782</v>
+        <v>0.1659059864152949</v>
       </c>
       <c r="T72">
         <v>2.773810309822053</v>
       </c>
       <c r="U72">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V72">
         <v>0.258</v>
       </c>
       <c r="W72">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.945728237426549</v>
+        <v>7.079815655137486</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7246,13 +7246,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.07703954773578167</v>
+        <v>0.07648962057788912</v>
       </c>
       <c r="C73">
-        <v>26896.67616772975</v>
+        <v>27598.16431996201</v>
       </c>
       <c r="D73">
-        <v>40711.72140922346</v>
+        <v>41413.20956145573</v>
       </c>
       <c r="E73">
         <v>16500.34208446032</v>
@@ -7279,37 +7279,37 @@
         <v>18497.1</v>
       </c>
       <c r="M73">
-        <v>2701.134228750868</v>
+        <v>2649.976383509374</v>
       </c>
       <c r="N73">
-        <v>15795.96577124914</v>
+        <v>15847.12361649063</v>
       </c>
       <c r="O73">
-        <v>4075.359168982277</v>
+        <v>4088.557893054582</v>
       </c>
       <c r="P73">
-        <v>11720.60660226686</v>
+        <v>11758.56572343605</v>
       </c>
       <c r="Q73">
-        <v>16669.70660226686</v>
+        <v>16707.66572343605</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1697360404682127</v>
+        <v>0.1696563606134107</v>
       </c>
       <c r="T73">
         <v>2.860424032642281</v>
       </c>
       <c r="U73">
-        <v>0.0528</v>
+        <v>0.0518</v>
       </c>
       <c r="V73">
         <v>0.258</v>
       </c>
       <c r="W73">
-        <v>0.0391776</v>
+        <v>0.0384356</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.847901079152937</v>
+        <v>6.980099941684847</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7328,13 +7328,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.07803512740302988</v>
+        <v>0.07630252523118977</v>
       </c>
       <c r="C74">
-        <v>24918.76445274567</v>
+        <v>27131.65021771333</v>
       </c>
       <c r="D74">
-        <v>39454.3427258097</v>
+        <v>41667.22849077737</v>
       </c>
       <c r="E74">
         <v>17220.87511603066</v>
@@ -7361,45 +7361,45 @@
         <v>18497.1</v>
       </c>
       <c r="M74">
-        <v>2853.310805018522</v>
+        <v>2687.299994544717</v>
       </c>
       <c r="N74">
-        <v>15643.78919498148</v>
+        <v>15809.80000545528</v>
       </c>
       <c r="O74">
-        <v>4036.097612305222</v>
+        <v>4078.928401407464</v>
       </c>
       <c r="P74">
-        <v>11607.69158267626</v>
+        <v>11730.87160404782</v>
       </c>
       <c r="Q74">
-        <v>16556.79158267625</v>
+        <v>16679.97160404782</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1737568835822496</v>
+        <v>0.1736746186828206</v>
       </c>
       <c r="T74">
         <v>2.953224449949669</v>
       </c>
       <c r="U74">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V74">
         <v>0.258</v>
       </c>
       <c r="W74">
-        <v>0.04081</v>
+        <v>0.0384356</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y74">
-        <v>6.482679688264779</v>
+        <v>6.883154109161446</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7410,13 +7410,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.0778717030702781</v>
+        <v>0.07611542988449044</v>
       </c>
       <c r="C75">
-        <v>24399.2746779053</v>
+        <v>26668.2715326321</v>
       </c>
       <c r="D75">
-        <v>39655.38598253968</v>
+        <v>41924.38283726647</v>
       </c>
       <c r="E75">
         <v>17941.40814760099</v>
@@ -7443,45 +7443,45 @@
         <v>18497.1</v>
       </c>
       <c r="M75">
-        <v>2892.940121754891</v>
+        <v>2724.62360558006</v>
       </c>
       <c r="N75">
-        <v>15604.15987824511</v>
+        <v>15772.47639441994</v>
       </c>
       <c r="O75">
-        <v>4025.873248587239</v>
+        <v>4069.298909760345</v>
       </c>
       <c r="P75">
-        <v>11578.28662965787</v>
+        <v>11703.1774846596</v>
       </c>
       <c r="Q75">
-        <v>16527.38662965787</v>
+        <v>16652.27748465959</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1780755669269559</v>
+        <v>0.1779905254981127</v>
       </c>
       <c r="T75">
         <v>3.052898972242789</v>
       </c>
       <c r="U75">
-        <v>0.055</v>
+        <v>0.0518</v>
       </c>
       <c r="V75">
         <v>0.258</v>
       </c>
       <c r="W75">
-        <v>0.04081</v>
+        <v>0.0384356</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y75">
-        <v>6.393875856918687</v>
+        <v>6.788864326844166</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7492,13 +7492,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.0777082787375263</v>
+        <v>0.07686177053779109</v>
       </c>
       <c r="C76">
-        <v>23881.8442658</v>
+        <v>24940.39504528795</v>
       </c>
       <c r="D76">
-        <v>39858.48860200471</v>
+        <v>40917.03938149266</v>
       </c>
       <c r="E76">
         <v>18661.94117917133</v>
@@ -7525,37 +7525,37 @@
         <v>18497.1</v>
       </c>
       <c r="M76">
-        <v>2932.569438491259</v>
+        <v>2852.590271986952</v>
       </c>
       <c r="N76">
-        <v>15564.53056150874</v>
+        <v>15644.50972801305</v>
       </c>
       <c r="O76">
-        <v>4015.648884869256</v>
+        <v>4036.283509827367</v>
       </c>
       <c r="P76">
-        <v>11548.88167663949</v>
+        <v>11608.22621818568</v>
       </c>
       <c r="Q76">
-        <v>16497.98167663949</v>
+        <v>16557.32621818568</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1827264566827935</v>
+        <v>0.1826384251453504</v>
       </c>
       <c r="T76">
         <v>3.160240765481534</v>
       </c>
       <c r="U76">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V76">
         <v>0.258</v>
       </c>
       <c r="W76">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.307472129122488</v>
+        <v>6.484317142088539</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7574,13 +7574,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.07754485440477452</v>
+        <v>0.07668728919109176</v>
       </c>
       <c r="C77">
-        <v>23366.5050215824</v>
+        <v>24451.00111077671</v>
       </c>
       <c r="D77">
-        <v>40063.68238935745</v>
+        <v>41148.17847855174</v>
       </c>
       <c r="E77">
         <v>19382.47421074166</v>
@@ -7607,37 +7607,37 @@
         <v>18497.1</v>
       </c>
       <c r="M77">
-        <v>2972.198755227628</v>
+        <v>2891.138789175965</v>
       </c>
       <c r="N77">
-        <v>15524.90124477237</v>
+        <v>15605.96121082404</v>
       </c>
       <c r="O77">
-        <v>4005.424521151273</v>
+        <v>4026.337992392601</v>
       </c>
       <c r="P77">
-        <v>11519.4767236211</v>
+        <v>11579.62321843144</v>
       </c>
       <c r="Q77">
-        <v>16468.5767236211</v>
+        <v>16528.72321843143</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1877494176190981</v>
+        <v>0.1876581567643671</v>
       </c>
       <c r="T77">
         <v>3.276169902179379</v>
       </c>
       <c r="U77">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V77">
         <v>0.258</v>
       </c>
       <c r="W77">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.223372500734188</v>
+        <v>6.397859580194025</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7656,13 +7656,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.07738143007202272</v>
+        <v>0.07651280784439242</v>
       </c>
       <c r="C78">
-        <v>22853.28940873341</v>
+        <v>23964.23340706366</v>
       </c>
       <c r="D78">
-        <v>40270.9998080788</v>
+        <v>41381.94380640904</v>
       </c>
       <c r="E78">
         <v>20103.00724231199</v>
@@ -7689,37 +7689,37 @@
         <v>18497.1</v>
       </c>
       <c r="M78">
-        <v>3011.828071963996</v>
+        <v>2929.687306364978</v>
       </c>
       <c r="N78">
-        <v>15485.27192803601</v>
+        <v>15567.41269363502</v>
       </c>
       <c r="O78">
-        <v>3995.20015743329</v>
+        <v>4016.392474957836</v>
       </c>
       <c r="P78">
-        <v>11490.07177060272</v>
+        <v>11551.02021867719</v>
       </c>
       <c r="Q78">
-        <v>16439.17177060272</v>
+        <v>16500.12021867718</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.193190958633428</v>
+        <v>0.1930961993516351</v>
       </c>
       <c r="T78">
         <v>3.40175980026871</v>
       </c>
       <c r="U78">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V78">
         <v>0.258</v>
       </c>
       <c r="W78">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.14148602046137</v>
+        <v>6.313677217296735</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7738,13 +7738,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.07721800573927093</v>
+        <v>0.07633832649769308</v>
       </c>
       <c r="C79">
-        <v>22342.23056618383</v>
+        <v>23480.1369492173</v>
       </c>
       <c r="D79">
-        <v>40480.47399709954</v>
+        <v>41618.38038013302</v>
       </c>
       <c r="E79">
         <v>20823.54027388233</v>
@@ -7771,37 +7771,37 @@
         <v>18497.1</v>
       </c>
       <c r="M79">
-        <v>3051.457388700365</v>
+        <v>2968.235823553991</v>
       </c>
       <c r="N79">
-        <v>15445.64261129964</v>
+        <v>15528.86417644601</v>
       </c>
       <c r="O79">
-        <v>3984.975793715307</v>
+        <v>4006.446957523071</v>
       </c>
       <c r="P79">
-        <v>11460.66681758433</v>
+        <v>11522.41721892294</v>
       </c>
       <c r="Q79">
-        <v>16409.76681758433</v>
+        <v>16471.51721892294</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1991056771272649</v>
+        <v>0.1990071152073612</v>
       </c>
       <c r="T79">
         <v>3.538270559061461</v>
       </c>
       <c r="U79">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V79">
         <v>0.258</v>
       </c>
       <c r="W79">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.061726461754079</v>
+        <v>6.231681409279894</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7820,13 +7820,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.07705458140651913</v>
+        <v>0.07616384515099374</v>
       </c>
       <c r="C80">
-        <v>21833.36232597341</v>
+        <v>22998.75778699588</v>
       </c>
       <c r="D80">
-        <v>40692.13878845946</v>
+        <v>41857.53424948193</v>
       </c>
       <c r="E80">
         <v>21544.07330545266</v>
@@ -7853,37 +7853,37 @@
         <v>18497.1</v>
       </c>
       <c r="M80">
-        <v>3091.086705436733</v>
+        <v>3006.784340743004</v>
       </c>
       <c r="N80">
-        <v>15406.01329456327</v>
+        <v>15490.315659257</v>
       </c>
       <c r="O80">
-        <v>3974.751429997324</v>
+        <v>3996.501440088306</v>
       </c>
       <c r="P80">
-        <v>11431.26186456595</v>
+        <v>11493.81421916869</v>
       </c>
       <c r="Q80">
-        <v>16380.36186456594</v>
+        <v>16442.91421916869</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2055580973023598</v>
+        <v>0.2054553870499716</v>
       </c>
       <c r="T80">
         <v>3.687191386835373</v>
       </c>
       <c r="U80">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V80">
         <v>0.258</v>
       </c>
       <c r="W80">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.984012019936719</v>
+        <v>6.15178805787887</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7902,13 +7902,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.07689115707376737</v>
+        <v>0.07598936380429441</v>
       </c>
       <c r="C81">
-        <v>21326.71923146678</v>
+        <v>22520.14303474761</v>
       </c>
       <c r="D81">
-        <v>40906.02872552317</v>
+        <v>42099.45252880399</v>
       </c>
       <c r="E81">
         <v>22264.606337023</v>
@@ -7935,37 +7935,37 @@
         <v>18497.1</v>
       </c>
       <c r="M81">
-        <v>3130.716022173101</v>
+        <v>3045.332857932016</v>
       </c>
       <c r="N81">
-        <v>15366.3839778269</v>
+        <v>15451.76714206799</v>
       </c>
       <c r="O81">
-        <v>3964.52706627934</v>
+        <v>3986.55592265354</v>
       </c>
       <c r="P81">
-        <v>11401.85691154756</v>
+        <v>11465.21121941444</v>
       </c>
       <c r="Q81">
-        <v>16350.95691154756</v>
+        <v>16414.31121941444</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2126250336846065</v>
+        <v>0.2125177800204496</v>
       </c>
       <c r="T81">
         <v>3.850295150587752</v>
       </c>
       <c r="U81">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V81">
         <v>0.258</v>
       </c>
       <c r="W81">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.908265032342584</v>
+        <v>6.073917322969011</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7984,13 +7984,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.07672773274101558</v>
+        <v>0.07581488245759507</v>
       </c>
       <c r="C82">
-        <v>20822.33655614706</v>
+        <v>22044.34090235399</v>
       </c>
       <c r="D82">
-        <v>41122.17908177379</v>
+        <v>42344.18342798071</v>
       </c>
       <c r="E82">
         <v>22985.13936859334</v>
@@ -8017,37 +8017,37 @@
         <v>18497.1</v>
       </c>
       <c r="M82">
-        <v>3170.34533890947</v>
+        <v>3083.88137512103</v>
       </c>
       <c r="N82">
-        <v>15326.75466109053</v>
+        <v>15413.21862487897</v>
       </c>
       <c r="O82">
-        <v>3954.302702561357</v>
+        <v>3976.610405218775</v>
       </c>
       <c r="P82">
-        <v>11372.45195852917</v>
+        <v>11436.6082196602</v>
       </c>
       <c r="Q82">
-        <v>16321.55195852917</v>
+        <v>16385.7082196602</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2203986637050779</v>
+        <v>0.2202864122879754</v>
       </c>
       <c r="T82">
         <v>4.029709290715368</v>
       </c>
       <c r="U82">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V82">
         <v>0.258</v>
       </c>
       <c r="W82">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.8344117194383</v>
+        <v>5.997993356431898</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8066,13 +8066,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07656430840826378</v>
+        <v>0.07564040111089573</v>
       </c>
       <c r="C83">
-        <v>20320.25032300803</v>
+        <v>21571.40072725837</v>
       </c>
       <c r="D83">
-        <v>41340.62588020509</v>
+        <v>42591.77628445542</v>
       </c>
       <c r="E83">
         <v>23705.67240016367</v>
@@ -8099,37 +8099,37 @@
         <v>18497.1</v>
       </c>
       <c r="M83">
-        <v>3209.974655645838</v>
+        <v>3122.429892310042</v>
       </c>
       <c r="N83">
-        <v>15287.12534435416</v>
+        <v>15374.67010768996</v>
       </c>
       <c r="O83">
-        <v>3944.078338843375</v>
+        <v>3966.664887784009</v>
       </c>
       <c r="P83">
-        <v>11343.04700551079</v>
+        <v>11408.00521990595</v>
       </c>
       <c r="Q83">
-        <v>16292.14700551079</v>
+        <v>16357.10521990595</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2289905705698094</v>
+        <v>0.2288727953205039</v>
       </c>
       <c r="T83">
         <v>4.228009129803787</v>
       </c>
       <c r="U83">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V83">
         <v>0.258</v>
       </c>
       <c r="W83">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.762381945124248</v>
+        <v>5.923944055735208</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8148,13 +8148,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07640088407551199</v>
+        <v>0.07546591976419638</v>
       </c>
       <c r="C84">
-        <v>19820.49732456822</v>
+        <v>21101.37300762508</v>
       </c>
       <c r="D84">
-        <v>41561.4059133356</v>
+        <v>42842.28159639246</v>
       </c>
       <c r="E84">
         <v>24426.205431734</v>
@@ -8181,37 +8181,37 @@
         <v>18497.1</v>
       </c>
       <c r="M84">
-        <v>3249.603972382206</v>
+        <v>3160.978409499055</v>
       </c>
       <c r="N84">
-        <v>15247.4960276178</v>
+        <v>15336.12159050095</v>
       </c>
       <c r="O84">
-        <v>3933.853975125391</v>
+        <v>3956.719370349244</v>
       </c>
       <c r="P84">
-        <v>11313.6420524924</v>
+        <v>11379.4022201517</v>
       </c>
       <c r="Q84">
-        <v>16262.7420524924</v>
+        <v>16328.5022201517</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2385371337528444</v>
+        <v>0.2384132209122022</v>
       </c>
       <c r="T84">
         <v>4.448342284346473</v>
       </c>
       <c r="U84">
-        <v>0.055</v>
+        <v>0.0535</v>
       </c>
       <c r="V84">
         <v>0.258</v>
       </c>
       <c r="W84">
-        <v>0.04081</v>
+        <v>0.039697</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.692108994573952</v>
+        <v>5.851700835543315</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8230,13 +8230,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.0771612497427602</v>
+        <v>0.07529143841749705</v>
       </c>
       <c r="C85">
-        <v>18092.29188203591</v>
+        <v>20634.3094366754</v>
       </c>
       <c r="D85">
-        <v>40553.73350237365</v>
+        <v>43095.75105701313</v>
       </c>
       <c r="E85">
         <v>25146.73846330434</v>
@@ -8263,45 +8263,45 @@
         <v>18497.1</v>
       </c>
       <c r="M85">
-        <v>3378.939651549082</v>
+        <v>3199.526926688068</v>
       </c>
       <c r="N85">
-        <v>15118.16034845092</v>
+        <v>15297.57307331193</v>
       </c>
       <c r="O85">
-        <v>3900.485369900338</v>
+        <v>3946.773852914479</v>
       </c>
       <c r="P85">
-        <v>11217.67497855058</v>
+        <v>11350.79922039746</v>
       </c>
       <c r="Q85">
-        <v>16166.77497855058</v>
+        <v>16299.89922039745</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2492068220162365</v>
+        <v>0.2490760495146886</v>
       </c>
       <c r="T85">
         <v>4.694596986482417</v>
       </c>
       <c r="U85">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V85">
         <v>0.258</v>
       </c>
       <c r="W85">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>5.474232128271356</v>
+        <v>5.781198415837975</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8312,13 +8312,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.07700895541000841</v>
+        <v>0.07511695707079771</v>
       </c>
       <c r="C86">
-        <v>17569.65409249466</v>
+        <v>20170.26293824999</v>
       </c>
       <c r="D86">
-        <v>40751.62874440271</v>
+        <v>43352.23759015804</v>
       </c>
       <c r="E86">
         <v>25867.27149487467</v>
@@ -8345,45 +8345,45 @@
         <v>18497.1</v>
       </c>
       <c r="M86">
-        <v>3419.649767832805</v>
+        <v>3238.075443877081</v>
       </c>
       <c r="N86">
-        <v>15077.4502321672</v>
+        <v>15259.02455612292</v>
       </c>
       <c r="O86">
-        <v>3889.982159899137</v>
+        <v>3936.828335479714</v>
       </c>
       <c r="P86">
-        <v>11187.46807226806</v>
+        <v>11322.19622064321</v>
       </c>
       <c r="Q86">
-        <v>16136.56807226806</v>
+        <v>16271.29622064321</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2612102213125525</v>
+        <v>0.2610717316924857</v>
       </c>
       <c r="T86">
         <v>4.971633526385352</v>
       </c>
       <c r="U86">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V86">
         <v>0.258</v>
       </c>
       <c r="W86">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y86">
-        <v>5.409062698172888</v>
+        <v>5.712374625173236</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8394,13 +8394,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.07685666107725662</v>
+        <v>0.07494247572409837</v>
       </c>
       <c r="C87">
-        <v>17048.9571634834</v>
+        <v>19709.28770364834</v>
       </c>
       <c r="D87">
-        <v>40951.46484696178</v>
+        <v>43611.79538712672</v>
       </c>
       <c r="E87">
         <v>26587.804526445</v>
@@ -8427,45 +8427,45 @@
         <v>18497.1</v>
       </c>
       <c r="M87">
-        <v>3460.359884116529</v>
+        <v>3276.623961066094</v>
       </c>
       <c r="N87">
-        <v>15036.74011588347</v>
+        <v>15220.47603893391</v>
       </c>
       <c r="O87">
-        <v>3879.478949897936</v>
+        <v>3926.882818044948</v>
       </c>
       <c r="P87">
-        <v>11157.26116598554</v>
+        <v>11293.59322088896</v>
       </c>
       <c r="Q87">
-        <v>16106.36116598553</v>
+        <v>16242.69322088896</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2748140738483775</v>
+        <v>0.2746668381606558</v>
       </c>
       <c r="T87">
         <v>5.285608271608681</v>
       </c>
       <c r="U87">
-        <v>0.0565</v>
+        <v>0.0535</v>
       </c>
       <c r="V87">
         <v>0.258</v>
       </c>
       <c r="W87">
-        <v>0.041923</v>
+        <v>0.039697</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y87">
-        <v>5.345426666429677</v>
+        <v>5.645170217818258</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8476,13 +8476,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.07670436674450483</v>
+        <v>0.07527849037739903</v>
       </c>
       <c r="C88">
-        <v>16530.22978823462</v>
+        <v>18491.63958513787</v>
       </c>
       <c r="D88">
-        <v>41153.27050328334</v>
+        <v>43114.68030018659</v>
       </c>
       <c r="E88">
         <v>27308.33755801534</v>
@@ -8509,37 +8509,37 @@
         <v>18497.1</v>
       </c>
       <c r="M88">
-        <v>3501.070000400253</v>
+        <v>3364.745150827146</v>
       </c>
       <c r="N88">
-        <v>14996.02999959975</v>
+        <v>15132.35484917286</v>
       </c>
       <c r="O88">
-        <v>3868.975739896735</v>
+        <v>3904.147551086597</v>
       </c>
       <c r="P88">
-        <v>11127.05425970301</v>
+        <v>11228.20729808626</v>
       </c>
       <c r="Q88">
-        <v>16076.15425970301</v>
+        <v>16177.30729808626</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2903613338893202</v>
+        <v>0.2902041026957073</v>
       </c>
       <c r="T88">
         <v>5.644436551863913</v>
       </c>
       <c r="U88">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V88">
         <v>0.258</v>
       </c>
       <c r="W88">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.283270542401425</v>
+        <v>5.49732570249872</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8558,13 +8558,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.07655207241175305</v>
+        <v>0.0751099450306997</v>
       </c>
       <c r="C89">
-        <v>16013.50122837383</v>
+        <v>18019.03532762065</v>
       </c>
       <c r="D89">
-        <v>41357.07497499288</v>
+        <v>43362.60907423971</v>
       </c>
       <c r="E89">
         <v>28028.87058958567</v>
@@ -8591,37 +8591,37 @@
         <v>18497.1</v>
       </c>
       <c r="M89">
-        <v>3541.780116683977</v>
+        <v>3403.870094441415</v>
       </c>
       <c r="N89">
-        <v>14955.31988331603</v>
+        <v>15093.22990555859</v>
       </c>
       <c r="O89">
-        <v>3858.472529895535</v>
+        <v>3894.053315634115</v>
       </c>
       <c r="P89">
-        <v>11096.84735342049</v>
+        <v>11199.17658992447</v>
       </c>
       <c r="Q89">
-        <v>16045.94735342049</v>
+        <v>16148.27658992447</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.308300480090408</v>
+        <v>0.3081317156207669</v>
       </c>
       <c r="T89">
         <v>6.058469182927643</v>
       </c>
       <c r="U89">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V89">
         <v>0.258</v>
       </c>
       <c r="W89">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.222543294787616</v>
+        <v>5.434138050745862</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8640,13 +8640,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.07639977807900125</v>
+        <v>0.07494139968400035</v>
       </c>
       <c r="C90">
-        <v>15498.80132806417</v>
+        <v>17549.29896537499</v>
       </c>
       <c r="D90">
-        <v>41562.90810625356</v>
+        <v>43613.40574356438</v>
       </c>
       <c r="E90">
         <v>28749.403621156</v>
@@ -8673,37 +8673,37 @@
         <v>18497.1</v>
       </c>
       <c r="M90">
-        <v>3582.490232967701</v>
+        <v>3442.995038055684</v>
       </c>
       <c r="N90">
-        <v>14914.6097670323</v>
+        <v>15054.10496194432</v>
       </c>
       <c r="O90">
-        <v>3847.969319894334</v>
+        <v>3883.959080181634</v>
       </c>
       <c r="P90">
-        <v>11066.64044713797</v>
+        <v>11170.14588176268</v>
       </c>
       <c r="Q90">
-        <v>16015.74044713797</v>
+        <v>16119.24588176268</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3292294839916771</v>
+        <v>0.3290472640333363</v>
       </c>
       <c r="T90">
         <v>6.541507252501995</v>
       </c>
       <c r="U90">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V90">
         <v>0.258</v>
       </c>
       <c r="W90">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.163196211892302</v>
+        <v>5.372386481987387</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8722,13 +8722,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.07624748374624946</v>
+        <v>0.07477285433730102</v>
       </c>
       <c r="C91">
-        <v>14986.16052857511</v>
+        <v>17082.48054908589</v>
       </c>
       <c r="D91">
-        <v>41770.80033833483</v>
+        <v>43867.12035884561</v>
       </c>
       <c r="E91">
         <v>29469.93665272633</v>
@@ -8755,37 +8755,37 @@
         <v>18497.1</v>
       </c>
       <c r="M91">
-        <v>3623.200349251425</v>
+        <v>3482.119981669953</v>
       </c>
       <c r="N91">
-        <v>14873.89965074858</v>
+        <v>15014.98001833005</v>
       </c>
       <c r="O91">
-        <v>3837.466109893133</v>
+        <v>3873.864844729153</v>
       </c>
       <c r="P91">
-        <v>11036.43354085544</v>
+        <v>11141.1151736009</v>
       </c>
       <c r="Q91">
-        <v>15985.53354085544</v>
+        <v>16090.21517360089</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3539637613295405</v>
+        <v>0.3537656394300093</v>
       </c>
       <c r="T91">
         <v>7.11237042563532</v>
       </c>
       <c r="U91">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V91">
         <v>0.258</v>
       </c>
       <c r="W91">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.105182771309242</v>
+        <v>5.312022588931348</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8804,13 +8804,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.07609518941349767</v>
+        <v>0.07460430899060168</v>
       </c>
       <c r="C92">
-        <v>14475.60988329085</v>
+        <v>16618.63130090352</v>
       </c>
       <c r="D92">
-        <v>41980.7827246209</v>
+        <v>44123.80414223357</v>
       </c>
       <c r="E92">
         <v>30190.46968429667</v>
@@ -8837,37 +8837,37 @@
         <v>18497.1</v>
       </c>
       <c r="M92">
-        <v>3663.910465535148</v>
+        <v>3521.244925284223</v>
       </c>
       <c r="N92">
-        <v>14833.18953446485</v>
+        <v>14975.85507471578</v>
       </c>
       <c r="O92">
-        <v>3826.962899891932</v>
+        <v>3863.770609276671</v>
       </c>
       <c r="P92">
-        <v>11006.22663457292</v>
+        <v>11112.08446543911</v>
       </c>
       <c r="Q92">
-        <v>15955.32663457292</v>
+        <v>16061.18446543911</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3836448941349768</v>
+        <v>0.3834276899060168</v>
       </c>
       <c r="T92">
         <v>7.797406233395311</v>
       </c>
       <c r="U92">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V92">
         <v>0.258</v>
       </c>
       <c r="W92">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.048458518294695</v>
+        <v>5.253000115720999</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8886,13 +8886,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.07594289508074588</v>
+        <v>0.07443576364390234</v>
       </c>
       <c r="C93">
-        <v>13967.18107317362</v>
+        <v>16157.8036489182</v>
       </c>
       <c r="D93">
-        <v>42192.886946074</v>
+        <v>44383.5095218186</v>
       </c>
       <c r="E93">
         <v>30911.00271586701</v>
@@ -8919,37 +8919,37 @@
         <v>18497.1</v>
       </c>
       <c r="M93">
-        <v>3704.620581818872</v>
+        <v>3560.369868898491</v>
       </c>
       <c r="N93">
-        <v>14792.47941818113</v>
+        <v>14936.73013110151</v>
       </c>
       <c r="O93">
-        <v>3816.459689890732</v>
+        <v>3853.67637382419</v>
       </c>
       <c r="P93">
-        <v>10976.0197282904</v>
+        <v>11083.05375727732</v>
       </c>
       <c r="Q93">
-        <v>15925.1197282904</v>
+        <v>16032.15375727732</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4199218342305099</v>
+        <v>0.4196813071544706</v>
       </c>
       <c r="T93">
         <v>8.634672220657521</v>
       </c>
       <c r="U93">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V93">
         <v>0.258</v>
       </c>
       <c r="W93">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>4.992980952159589</v>
+        <v>5.195274839724066</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8968,13 +8968,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.0757906007479941</v>
+        <v>0.07426721829720301</v>
       </c>
       <c r="C94">
-        <v>13460.90642269801</v>
+        <v>15700.05126286049</v>
       </c>
       <c r="D94">
-        <v>42407.14532716874</v>
+        <v>44646.29016733122</v>
       </c>
       <c r="E94">
         <v>31631.53574743734</v>
@@ -9001,37 +9001,37 @@
         <v>18497.1</v>
       </c>
       <c r="M94">
-        <v>3745.330698102596</v>
+        <v>3599.49481251276</v>
       </c>
       <c r="N94">
-        <v>14751.76930189741</v>
+        <v>14897.60518748724</v>
       </c>
       <c r="O94">
-        <v>3805.956479889531</v>
+        <v>3843.582138371709</v>
       </c>
       <c r="P94">
-        <v>10945.81282200788</v>
+        <v>11054.02304911553</v>
       </c>
       <c r="Q94">
-        <v>15894.91282200787</v>
+        <v>16003.12304911553</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4652680093499264</v>
+        <v>0.4649983287150378</v>
       </c>
       <c r="T94">
         <v>9.681254704735286</v>
       </c>
       <c r="U94">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V94">
         <v>0.258</v>
       </c>
       <c r="W94">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.938709420070897</v>
+        <v>5.138804461031413</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9050,13 +9050,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.0756383064152423</v>
+        <v>0.07409867295050365</v>
       </c>
       <c r="C95">
-        <v>12956.81891627351</v>
+        <v>15245.42909107692</v>
       </c>
       <c r="D95">
-        <v>42623.59085231457</v>
+        <v>44912.20102711798</v>
       </c>
       <c r="E95">
         <v>32352.06877900767</v>
@@ -9083,37 +9083,37 @@
         <v>18497.1</v>
       </c>
       <c r="M95">
-        <v>3786.04081438632</v>
+        <v>3638.61975612703</v>
       </c>
       <c r="N95">
-        <v>14711.05918561368</v>
+        <v>14858.48024387297</v>
       </c>
       <c r="O95">
-        <v>3795.45326988833</v>
+        <v>3833.487902919227</v>
       </c>
       <c r="P95">
-        <v>10915.60591572535</v>
+        <v>11024.99234095375</v>
       </c>
       <c r="Q95">
-        <v>15864.70591572535</v>
+        <v>15974.09234095374</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5235702345034619</v>
+        <v>0.5232630707214811</v>
       </c>
       <c r="T95">
         <v>11.02686075569241</v>
       </c>
       <c r="U95">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V95">
         <v>0.258</v>
       </c>
       <c r="W95">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.885605017704544</v>
+        <v>5.083548499084839</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9132,13 +9132,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07548601208249051</v>
+        <v>0.07393012760380432</v>
       </c>
       <c r="C96">
-        <v>12454.95221517225</v>
+        <v>14793.99339883475</v>
       </c>
       <c r="D96">
-        <v>42842.25718278365</v>
+        <v>45181.29836644614</v>
       </c>
       <c r="E96">
         <v>33072.60181057802</v>
@@ -9165,37 +9165,37 @@
         <v>18497.1</v>
       </c>
       <c r="M96">
-        <v>3826.750930670044</v>
+        <v>3677.744699741299</v>
       </c>
       <c r="N96">
-        <v>14670.34906932996</v>
+        <v>14819.3553002587</v>
       </c>
       <c r="O96">
-        <v>3784.950059887129</v>
+        <v>3823.393667466746</v>
       </c>
       <c r="P96">
-        <v>10885.39900944283</v>
+        <v>10995.96163279196</v>
       </c>
       <c r="Q96">
-        <v>15834.49900944283</v>
+        <v>15945.06163279196</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.6013065347081757</v>
+        <v>0.6009493933967393</v>
       </c>
       <c r="T96">
         <v>12.82100215696858</v>
       </c>
       <c r="U96">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V96">
         <v>0.258</v>
       </c>
       <c r="W96">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.833630496239601</v>
+        <v>5.029468195903084</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9214,13 +9214,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07533371774973871</v>
+        <v>0.07376158225710497</v>
       </c>
       <c r="C97">
-        <v>11955.34067498072</v>
+        <v>14345.80180801263</v>
       </c>
       <c r="D97">
-        <v>43063.17867416245</v>
+        <v>45453.63980719436</v>
       </c>
       <c r="E97">
         <v>33793.13484214835</v>
@@ -9247,37 +9247,37 @@
         <v>18497.1</v>
       </c>
       <c r="M97">
-        <v>3867.461046953768</v>
+        <v>3716.869643355568</v>
       </c>
       <c r="N97">
-        <v>14629.63895304623</v>
+        <v>14780.23035664443</v>
       </c>
       <c r="O97">
-        <v>3774.446849885928</v>
+        <v>3813.299432014264</v>
       </c>
       <c r="P97">
-        <v>10855.19210316031</v>
+        <v>10966.93092463017</v>
       </c>
       <c r="Q97">
-        <v>15804.2921031603</v>
+        <v>15916.03092463017</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7101373549947753</v>
+        <v>0.7097102451421005</v>
       </c>
       <c r="T97">
         <v>15.33280011875521</v>
       </c>
       <c r="U97">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V97">
         <v>0.258</v>
       </c>
       <c r="W97">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.782750175226552</v>
+        <v>4.976526425419894</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9296,13 +9296,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.07518142341698694</v>
+        <v>0.07359303691040564</v>
       </c>
       <c r="C98">
-        <v>11458.01936359411</v>
+        <v>13900.91333823475</v>
       </c>
       <c r="D98">
-        <v>43286.39039434616</v>
+        <v>45729.28436898681</v>
       </c>
       <c r="E98">
         <v>34513.66787371867</v>
@@ -9329,37 +9329,37 @@
         <v>18497.1</v>
       </c>
       <c r="M98">
-        <v>3908.171163237491</v>
+        <v>3755.994586969837</v>
       </c>
       <c r="N98">
-        <v>14588.92883676251</v>
+        <v>14741.10541303017</v>
       </c>
       <c r="O98">
-        <v>3763.943639884728</v>
+        <v>3803.205196561783</v>
       </c>
       <c r="P98">
-        <v>10824.98519687778</v>
+        <v>10937.90021646838</v>
       </c>
       <c r="Q98">
-        <v>15774.08519687778</v>
+        <v>15887.00021646838</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.8733835854246726</v>
+        <v>0.8728515227601403</v>
       </c>
       <c r="T98">
         <v>19.10049706143512</v>
       </c>
       <c r="U98">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V98">
         <v>0.258</v>
       </c>
       <c r="W98">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.732929860901277</v>
+        <v>4.924687608488437</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.07502912908423515</v>
+        <v>0.07342449156370631</v>
       </c>
       <c r="C99">
-        <v>10963.02407977336</v>
+        <v>13459.38844951143</v>
       </c>
       <c r="D99">
-        <v>43511.92814209576</v>
+        <v>46008.29251183383</v>
       </c>
       <c r="E99">
         <v>35234.20090528901</v>
@@ -9411,37 +9411,37 @@
         <v>18497.1</v>
       </c>
       <c r="M99">
-        <v>3948.881279521216</v>
+        <v>3795.119530584107</v>
       </c>
       <c r="N99">
-        <v>14548.21872047879</v>
+        <v>14701.9804694159</v>
       </c>
       <c r="O99">
-        <v>3753.440429883527</v>
+        <v>3793.110961109301</v>
       </c>
       <c r="P99">
-        <v>10794.77829059526</v>
+        <v>10908.86950830659</v>
       </c>
       <c r="Q99">
-        <v>15743.87829059526</v>
+        <v>15857.96950830659</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.145460636141171</v>
+        <v>1.144753652123543</v>
       </c>
       <c r="T99">
         <v>25.37999196590169</v>
       </c>
       <c r="U99">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V99">
         <v>0.258</v>
       </c>
       <c r="W99">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.684136769551779</v>
+        <v>4.873917633143195</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9460,13 +9460,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.07487683475148335</v>
+        <v>0.07325594621700697</v>
       </c>
       <c r="C100">
-        <v>10470.39137228513</v>
+        <v>13021.28908644998</v>
       </c>
       <c r="D100">
-        <v>43739.82846617786</v>
+        <v>46290.72618034271</v>
       </c>
       <c r="E100">
         <v>35954.73393685935</v>
@@ -9493,37 +9493,37 @@
         <v>18497.1</v>
       </c>
       <c r="M100">
-        <v>3989.59139580494</v>
+        <v>3834.244474198375</v>
       </c>
       <c r="N100">
-        <v>14507.50860419506</v>
+        <v>14662.85552580163</v>
       </c>
       <c r="O100">
-        <v>3742.937219882327</v>
+        <v>3783.01672565682</v>
       </c>
       <c r="P100">
-        <v>10764.57138431274</v>
+        <v>10879.83880014481</v>
       </c>
       <c r="Q100">
-        <v>15713.67138431274</v>
+        <v>15828.93880014481</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.689614737574166</v>
+        <v>1.688557910850347</v>
       </c>
       <c r="T100">
         <v>37.93898177483482</v>
       </c>
       <c r="U100">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V100">
         <v>0.258</v>
       </c>
       <c r="W100">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9531,7 +9531,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.636339455576761</v>
+        <v>4.824183779743775</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9542,13 +9542,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.07472454041873157</v>
+        <v>0.07308740087030763</v>
       </c>
       <c r="C101">
-        <v>9980.15855964653</v>
+        <v>12586.67872410388</v>
       </c>
       <c r="D101">
-        <v>43970.1286851096</v>
+        <v>46576.64884956695</v>
       </c>
       <c r="E101">
         <v>36675.26696842968</v>
@@ -9575,37 +9575,37 @@
         <v>18497.1</v>
       </c>
       <c r="M101">
-        <v>4030.301512088663</v>
+        <v>3873.369417812645</v>
       </c>
       <c r="N101">
-        <v>14466.79848791134</v>
+        <v>14623.73058218736</v>
       </c>
       <c r="O101">
-        <v>3732.434009881126</v>
+        <v>3772.922490204338</v>
       </c>
       <c r="P101">
-        <v>10734.36447803021</v>
+        <v>10850.80809198302</v>
       </c>
       <c r="Q101">
-        <v>15683.46447803021</v>
+        <v>15799.90809198302</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.322077041873154</v>
+        <v>3.31997068703076</v>
       </c>
       <c r="T101">
         <v>75.61595120163422</v>
       </c>
       <c r="U101">
-        <v>0.0565</v>
+        <v>0.0543</v>
       </c>
       <c r="V101">
         <v>0.258</v>
       </c>
       <c r="W101">
-        <v>0.041923</v>
+        <v>0.0402906</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>4.589507743904268</v>
+        <v>4.775454650655454</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/netherlands/netherlands_auto_truck.xlsx
+++ b/research/traditional_assets/database/data/netherlands/netherlands_auto_truck.xlsx
@@ -1284,7 +1284,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1421,22 +1421,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08977339019354216</v>
+        <v>0.08957516484684284</v>
       </c>
       <c r="C2">
-        <v>66245.63607335638</v>
+        <v>65655.98261063015</v>
       </c>
       <c r="D2">
-        <v>28902.83607335638</v>
+        <v>29033.71564220048</v>
       </c>
       <c r="E2">
-        <v>-34657.50315703339</v>
+        <v>-33936.97012546306</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>720.5330315703339</v>
       </c>
       <c r="G2">
         <v>37342.8</v>
@@ -1457,28 +1457,28 @@
         <v>18497.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>36.24281148798779</v>
       </c>
       <c r="N2">
-        <v>18497.1</v>
+        <v>18460.85718851201</v>
       </c>
       <c r="O2">
-        <v>4772.251800000001</v>
+        <v>4762.9011546361</v>
       </c>
       <c r="P2">
-        <v>13724.8482</v>
+        <v>13697.95603387591</v>
       </c>
       <c r="Q2">
-        <v>18673.9482</v>
+        <v>18647.05603387591</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08977339019354216</v>
+        <v>0.09010296853216448</v>
       </c>
       <c r="T2">
-        <v>1.015551736571413</v>
+        <v>1.023163245546524</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>510.3660350999708</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1503,22 +1503,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08957516484684284</v>
+        <v>0.0893769395001435</v>
       </c>
       <c r="C3">
-        <v>65655.98261063015</v>
+        <v>65067.51985327278</v>
       </c>
       <c r="D3">
-        <v>29033.71564220048</v>
+        <v>29165.78591641345</v>
       </c>
       <c r="E3">
-        <v>-33936.97012546306</v>
+        <v>-33216.43709389272</v>
       </c>
       <c r="F3">
-        <v>720.5330315703339</v>
+        <v>1441.066063140668</v>
       </c>
       <c r="G3">
         <v>37342.8</v>
@@ -1539,28 +1539,28 @@
         <v>18497.1</v>
       </c>
       <c r="M3">
-        <v>36.24281148798779</v>
+        <v>72.48562297597559</v>
       </c>
       <c r="N3">
-        <v>18460.85718851201</v>
+        <v>18424.61437702403</v>
       </c>
       <c r="O3">
-        <v>4762.9011546361</v>
+        <v>4753.550509272199</v>
       </c>
       <c r="P3">
-        <v>13697.95603387591</v>
+        <v>13671.06386775183</v>
       </c>
       <c r="Q3">
-        <v>18647.05603387591</v>
+        <v>18620.16386775183</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09010296853216448</v>
+        <v>0.0904392729593301</v>
       </c>
       <c r="T3">
-        <v>1.023163245546524</v>
+        <v>1.030930091439495</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1577,7 +1577,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>510.3660350999708</v>
+        <v>255.1830175499854</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,22 +1585,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0893769395001435</v>
+        <v>0.08917871415344414</v>
       </c>
       <c r="C4">
-        <v>65067.51985327278</v>
+        <v>64480.2641245886</v>
       </c>
       <c r="D4">
-        <v>29165.78591641345</v>
+        <v>29299.0632192996</v>
       </c>
       <c r="E4">
-        <v>-33216.43709389272</v>
+        <v>-32495.90406232239</v>
       </c>
       <c r="F4">
-        <v>1441.066063140668</v>
+        <v>2161.599094711002</v>
       </c>
       <c r="G4">
         <v>37342.8</v>
@@ -1621,28 +1621,28 @@
         <v>18497.1</v>
       </c>
       <c r="M4">
-        <v>72.48562297597559</v>
+        <v>108.7284344639634</v>
       </c>
       <c r="N4">
-        <v>18424.61437702403</v>
+        <v>18388.37156553604</v>
       </c>
       <c r="O4">
-        <v>4753.550509272199</v>
+        <v>4744.199863908299</v>
       </c>
       <c r="P4">
-        <v>13671.06386775183</v>
+        <v>13644.17170162774</v>
       </c>
       <c r="Q4">
-        <v>18620.16386775183</v>
+        <v>18593.27170162774</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0904392729593301</v>
+        <v>0.09078251149839603</v>
       </c>
       <c r="T4">
-        <v>1.030930091439495</v>
+        <v>1.038857078484897</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1659,7 +1659,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>255.1830175499854</v>
+        <v>170.1220116999903</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,22 +1667,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08917871415344414</v>
+        <v>0.08898048880674482</v>
       </c>
       <c r="C5">
-        <v>64480.2641245886</v>
+        <v>63894.23204761848</v>
       </c>
       <c r="D5">
-        <v>29299.0632192996</v>
+        <v>29433.56417389981</v>
       </c>
       <c r="E5">
-        <v>-32495.90406232239</v>
+        <v>-31775.37103075205</v>
       </c>
       <c r="F5">
-        <v>2161.599094711002</v>
+        <v>2882.132126281336</v>
       </c>
       <c r="G5">
         <v>37342.8</v>
@@ -1703,28 +1703,28 @@
         <v>18497.1</v>
       </c>
       <c r="M5">
-        <v>108.7284344639634</v>
+        <v>144.9712459519512</v>
       </c>
       <c r="N5">
-        <v>18388.37156553604</v>
+        <v>18352.12875404805</v>
       </c>
       <c r="O5">
-        <v>4744.199863908299</v>
+        <v>4734.849218544397</v>
       </c>
       <c r="P5">
-        <v>13644.17170162774</v>
+        <v>13617.27953550365</v>
       </c>
       <c r="Q5">
-        <v>18593.27170162774</v>
+        <v>18566.37953550365</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09078251149839603</v>
+        <v>0.09113290084035919</v>
       </c>
       <c r="T5">
-        <v>1.038857078484897</v>
+        <v>1.046949211093746</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1741,7 +1741,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>170.1220116999903</v>
+        <v>127.5915087749927</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,22 +1749,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08898048880674482</v>
+        <v>0.08878226346004547</v>
       </c>
       <c r="C6">
-        <v>63894.23204761848</v>
+        <v>63309.44055205154</v>
       </c>
       <c r="D6">
-        <v>29433.56417389981</v>
+        <v>29569.30570990319</v>
       </c>
       <c r="E6">
-        <v>-31775.37103075205</v>
+        <v>-31054.83799918172</v>
       </c>
       <c r="F6">
-        <v>2882.132126281336</v>
+        <v>3602.66515785167</v>
       </c>
       <c r="G6">
         <v>37342.8</v>
@@ -1785,28 +1785,28 @@
         <v>18497.1</v>
       </c>
       <c r="M6">
-        <v>144.9712459519512</v>
+        <v>181.214057439939</v>
       </c>
       <c r="N6">
-        <v>18352.12875404805</v>
+        <v>18315.88594256006</v>
       </c>
       <c r="O6">
-        <v>4734.849218544397</v>
+        <v>4725.498573180496</v>
       </c>
       <c r="P6">
-        <v>13617.27953550365</v>
+        <v>13590.38736937957</v>
       </c>
       <c r="Q6">
-        <v>18566.37953550365</v>
+        <v>18539.48736937957</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09113290084035919</v>
+        <v>0.09149066680004787</v>
       </c>
       <c r="T6">
-        <v>1.046949211093746</v>
+        <v>1.055211704389097</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1823,7 +1823,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>127.5915087749927</v>
+        <v>102.0732070199941</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,22 +1831,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08878226346004547</v>
+        <v>0.08858403811334613</v>
       </c>
       <c r="C7">
-        <v>63309.44055205154</v>
+        <v>62725.90688132872</v>
       </c>
       <c r="D7">
-        <v>29569.30570990319</v>
+        <v>29706.30507075072</v>
       </c>
       <c r="E7">
-        <v>-31054.83799918172</v>
+        <v>-30334.30496761138</v>
       </c>
       <c r="F7">
-        <v>3602.66515785167</v>
+        <v>4323.198189422004</v>
       </c>
       <c r="G7">
         <v>37342.8</v>
@@ -1867,28 +1867,28 @@
         <v>18497.1</v>
       </c>
       <c r="M7">
-        <v>181.214057439939</v>
+        <v>217.4568689279268</v>
       </c>
       <c r="N7">
-        <v>18315.88594256006</v>
+        <v>18279.64313107208</v>
       </c>
       <c r="O7">
-        <v>4725.498573180496</v>
+        <v>4716.147927816596</v>
       </c>
       <c r="P7">
-        <v>13590.38736937957</v>
+        <v>13563.49520325548</v>
       </c>
       <c r="Q7">
-        <v>18539.48736937957</v>
+        <v>18512.59520325548</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09149066680004787</v>
+        <v>0.09185604480143206</v>
       </c>
       <c r="T7">
-        <v>1.055211704389097</v>
+        <v>1.063649995414136</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>102.0732070199941</v>
+        <v>85.06100584999511</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,22 +1913,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08858403811334613</v>
+        <v>0.08838581276664682</v>
       </c>
       <c r="C8">
-        <v>62725.90688132872</v>
+        <v>62143.64859994507</v>
       </c>
       <c r="D8">
-        <v>29706.30507075072</v>
+        <v>29844.5798209374</v>
       </c>
       <c r="E8">
-        <v>-30334.30496761138</v>
+        <v>-29613.77193604105</v>
       </c>
       <c r="F8">
-        <v>4323.198189422003</v>
+        <v>5043.731220992338</v>
       </c>
       <c r="G8">
         <v>37342.8</v>
@@ -1949,28 +1949,28 @@
         <v>18497.1</v>
       </c>
       <c r="M8">
-        <v>217.4568689279268</v>
+        <v>253.6996804159146</v>
       </c>
       <c r="N8">
-        <v>18279.64313107208</v>
+        <v>18243.40031958409</v>
       </c>
       <c r="O8">
-        <v>4716.147927816596</v>
+        <v>4706.797282452695</v>
       </c>
       <c r="P8">
-        <v>13563.49520325548</v>
+        <v>13536.60303713139</v>
       </c>
       <c r="Q8">
-        <v>18512.59520325548</v>
+        <v>18485.70303713139</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09185604480143206</v>
+        <v>0.09222928039424388</v>
       </c>
       <c r="T8">
-        <v>1.063649995414136</v>
+        <v>1.072269755063369</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>85.06100584999513</v>
+        <v>72.9094335857101</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,22 +1995,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08838581276664681</v>
+        <v>0.08818758741994746</v>
       </c>
       <c r="C9">
-        <v>62143.64859994507</v>
+        <v>61562.68360095679</v>
       </c>
       <c r="D9">
-        <v>29844.57982093741</v>
+        <v>29984.14785351946</v>
       </c>
       <c r="E9">
-        <v>-29613.77193604105</v>
+        <v>-28893.23890447072</v>
       </c>
       <c r="F9">
-        <v>5043.731220992338</v>
+        <v>5764.264252562672</v>
       </c>
       <c r="G9">
         <v>37342.8</v>
@@ -2031,28 +2031,28 @@
         <v>18497.1</v>
       </c>
       <c r="M9">
-        <v>253.6996804159146</v>
+        <v>289.9424919039024</v>
       </c>
       <c r="N9">
-        <v>18243.40031958409</v>
+        <v>18207.1575080961</v>
       </c>
       <c r="O9">
-        <v>4706.797282452695</v>
+        <v>4697.446637088794</v>
       </c>
       <c r="P9">
-        <v>13536.60303713139</v>
+        <v>13509.71087100731</v>
       </c>
       <c r="Q9">
-        <v>18485.70303713139</v>
+        <v>18458.81087100731</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09222928039424388</v>
+        <v>0.09261062980429072</v>
       </c>
       <c r="T9">
-        <v>1.072269755063369</v>
+        <v>1.081076900791934</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>72.9094335857101</v>
+        <v>63.79575438749635</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,22 +2077,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08818758741994746</v>
+        <v>0.08798936207324812</v>
       </c>
       <c r="C10">
-        <v>61562.68360095679</v>
+        <v>60983.03011369976</v>
       </c>
       <c r="D10">
-        <v>29984.14785351946</v>
+        <v>30125.02739783276</v>
       </c>
       <c r="E10">
-        <v>-28893.23890447072</v>
+        <v>-28172.70587290038</v>
       </c>
       <c r="F10">
-        <v>5764.264252562672</v>
+        <v>6484.797284133006</v>
       </c>
       <c r="G10">
         <v>37342.8</v>
@@ -2113,28 +2113,28 @@
         <v>18497.1</v>
       </c>
       <c r="M10">
-        <v>289.9424919039024</v>
+        <v>326.1853033918902</v>
       </c>
       <c r="N10">
-        <v>18207.1575080961</v>
+        <v>18170.91469660811</v>
       </c>
       <c r="O10">
-        <v>4697.446637088794</v>
+        <v>4688.095991724894</v>
       </c>
       <c r="P10">
-        <v>13509.71087100731</v>
+        <v>13482.81870488322</v>
       </c>
       <c r="Q10">
-        <v>18458.81087100731</v>
+        <v>18431.91870488322</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09261062980429072</v>
+        <v>0.09300036052005288</v>
       </c>
       <c r="T10">
-        <v>1.081076900791934</v>
+        <v>1.090077610162884</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>63.79575438749635</v>
+        <v>56.70733723333009</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08798936207324812</v>
+        <v>0.08779113672654879</v>
       </c>
       <c r="C11">
-        <v>60983.03011369976</v>
+        <v>60404.70671172698</v>
       </c>
       <c r="D11">
-        <v>30125.02739783276</v>
+        <v>30267.2370274303</v>
       </c>
       <c r="E11">
-        <v>-28172.70587290038</v>
+        <v>-27452.17284133005</v>
       </c>
       <c r="F11">
-        <v>6484.797284133006</v>
+        <v>7205.33031570334</v>
       </c>
       <c r="G11">
         <v>37342.8</v>
@@ -2195,28 +2195,28 @@
         <v>18497.1</v>
       </c>
       <c r="M11">
-        <v>326.1853033918902</v>
+        <v>362.428114879878</v>
       </c>
       <c r="N11">
-        <v>18170.91469660811</v>
+        <v>18134.67188512013</v>
       </c>
       <c r="O11">
-        <v>4688.095991724894</v>
+        <v>4678.745346360993</v>
       </c>
       <c r="P11">
-        <v>13482.81870488322</v>
+        <v>13455.92653875913</v>
       </c>
       <c r="Q11">
-        <v>18431.91870488322</v>
+        <v>18405.02653875913</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09300036052005288</v>
+        <v>0.09339875191838753</v>
       </c>
       <c r="T11">
-        <v>1.090077610162884</v>
+        <v>1.099278335297634</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2233,7 +2233,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>56.70733723333009</v>
+        <v>51.03660350999708</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,22 +2241,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08779113672654879</v>
+        <v>0.08759291137984944</v>
       </c>
       <c r="C12">
-        <v>60404.70671172698</v>
+        <v>59827.73232097165</v>
       </c>
       <c r="D12">
-        <v>30267.2370274303</v>
+        <v>30410.79566824532</v>
       </c>
       <c r="E12">
-        <v>-27452.17284133005</v>
+        <v>-26731.63980975972</v>
       </c>
       <c r="F12">
-        <v>7205.330315703341</v>
+        <v>7925.863347273674</v>
       </c>
       <c r="G12">
         <v>37342.8</v>
@@ -2277,28 +2277,28 @@
         <v>18497.1</v>
       </c>
       <c r="M12">
-        <v>362.428114879878</v>
+        <v>398.6709263678658</v>
       </c>
       <c r="N12">
-        <v>18134.67188512013</v>
+        <v>18098.42907363214</v>
       </c>
       <c r="O12">
-        <v>4678.745346360993</v>
+        <v>4669.394700997092</v>
       </c>
       <c r="P12">
-        <v>13455.92653875913</v>
+        <v>13429.03437263505</v>
       </c>
       <c r="Q12">
-        <v>18405.02653875913</v>
+        <v>18378.13437263505</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09339875191838753</v>
+        <v>0.0938060959324151</v>
       </c>
       <c r="T12">
-        <v>1.099278335297634</v>
+        <v>1.10868581830058</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2315,7 +2315,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>51.03660350999707</v>
+        <v>46.39691228181552</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,22 +2323,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08759291137984944</v>
+        <v>0.08739468603315009</v>
       </c>
       <c r="C13">
-        <v>59827.73232097165</v>
+        <v>59252.12622814385</v>
       </c>
       <c r="D13">
-        <v>30410.79566824532</v>
+        <v>30555.72260698785</v>
       </c>
       <c r="E13">
-        <v>-26731.63980975972</v>
+        <v>-26011.10677818938</v>
       </c>
       <c r="F13">
-        <v>7925.863347273674</v>
+        <v>8646.396378844007</v>
       </c>
       <c r="G13">
         <v>37342.8</v>
@@ -2359,28 +2359,28 @@
         <v>18497.1</v>
       </c>
       <c r="M13">
-        <v>398.6709263678658</v>
+        <v>434.9137378558535</v>
       </c>
       <c r="N13">
-        <v>18098.42907363214</v>
+        <v>18062.18626214415</v>
       </c>
       <c r="O13">
-        <v>4669.394700997092</v>
+        <v>4660.04405563319</v>
       </c>
       <c r="P13">
-        <v>13429.03437263505</v>
+        <v>13402.14220651096</v>
       </c>
       <c r="Q13">
-        <v>18378.13437263505</v>
+        <v>18351.24220651096</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0938060959324151</v>
+        <v>0.0942226977649433</v>
       </c>
       <c r="T13">
-        <v>1.10868581830058</v>
+        <v>1.118307107735412</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2397,7 +2397,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>46.39691228181552</v>
+        <v>42.53050292499756</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,22 +2405,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08739468603315009</v>
+        <v>0.08719646068645077</v>
       </c>
       <c r="C14">
-        <v>59252.12622814385</v>
+        <v>58677.90808936822</v>
       </c>
       <c r="D14">
-        <v>30555.72260698785</v>
+        <v>30702.03749978256</v>
       </c>
       <c r="E14">
-        <v>-26011.10677818938</v>
+        <v>-25290.57374661905</v>
       </c>
       <c r="F14">
-        <v>8646.396378844007</v>
+        <v>9366.929410414343</v>
       </c>
       <c r="G14">
         <v>37342.8</v>
@@ -2441,28 +2441,28 @@
         <v>18497.1</v>
       </c>
       <c r="M14">
-        <v>434.9137378558535</v>
+        <v>471.1565493438414</v>
       </c>
       <c r="N14">
-        <v>18062.18626214415</v>
+        <v>18025.94345065616</v>
       </c>
       <c r="O14">
-        <v>4660.04405563319</v>
+        <v>4650.693410269289</v>
       </c>
       <c r="P14">
-        <v>13402.14220651096</v>
+        <v>13375.25004038687</v>
       </c>
       <c r="Q14">
-        <v>18351.24220651096</v>
+        <v>18324.35004038687</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0942226977649433</v>
+        <v>0.09464887665109284</v>
       </c>
       <c r="T14">
-        <v>1.118307107735412</v>
+        <v>1.12814957623771</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2479,7 +2479,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>42.53050292499756</v>
+        <v>39.25892577692082</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,22 +2487,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08719646068645077</v>
+        <v>0.08699823533975143</v>
       </c>
       <c r="C15">
-        <v>58677.90808936822</v>
+        <v>58105.09793907135</v>
       </c>
       <c r="D15">
-        <v>30702.03749978256</v>
+        <v>30849.76038105603</v>
       </c>
       <c r="E15">
-        <v>-25290.57374661905</v>
+        <v>-24570.04071504871</v>
       </c>
       <c r="F15">
-        <v>9366.929410414343</v>
+        <v>10087.46244198468</v>
       </c>
       <c r="G15">
         <v>37342.8</v>
@@ -2523,28 +2523,28 @@
         <v>18497.1</v>
       </c>
       <c r="M15">
-        <v>471.1565493438414</v>
+        <v>507.3993608318292</v>
       </c>
       <c r="N15">
-        <v>18025.94345065616</v>
+        <v>17989.70063916817</v>
       </c>
       <c r="O15">
-        <v>4650.693410269289</v>
+        <v>4641.342764905388</v>
       </c>
       <c r="P15">
-        <v>13375.25004038687</v>
+        <v>13348.35787426278</v>
       </c>
       <c r="Q15">
-        <v>18324.35004038687</v>
+        <v>18297.45787426278</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09464887665109284</v>
+        <v>0.09508496667412956</v>
       </c>
       <c r="T15">
-        <v>1.12814957623771</v>
+        <v>1.138220939356341</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2561,7 +2561,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>39.25892577692082</v>
+        <v>36.45471679285505</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,22 +2569,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08699823533975143</v>
+        <v>0.08680000999305208</v>
       </c>
       <c r="C16">
-        <v>58105.09793907135</v>
+        <v>57533.71619912663</v>
       </c>
       <c r="D16">
-        <v>30849.76038105603</v>
+        <v>30998.91167268164</v>
       </c>
       <c r="E16">
-        <v>-24570.04071504871</v>
+        <v>-23849.50768347838</v>
       </c>
       <c r="F16">
-        <v>10087.46244198468</v>
+        <v>10807.99547355501</v>
       </c>
       <c r="G16">
         <v>37342.8</v>
@@ -2605,28 +2605,28 @@
         <v>18497.1</v>
       </c>
       <c r="M16">
-        <v>507.3993608318292</v>
+        <v>543.6421723198171</v>
       </c>
       <c r="N16">
-        <v>17989.70063916817</v>
+        <v>17953.45782768018</v>
       </c>
       <c r="O16">
-        <v>4641.342764905388</v>
+        <v>4631.992119541487</v>
       </c>
       <c r="P16">
-        <v>13348.35787426278</v>
+        <v>13321.4657081387</v>
       </c>
       <c r="Q16">
-        <v>18297.45787426278</v>
+        <v>18270.5657081387</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09508496667412956</v>
+        <v>0.09553131763888481</v>
       </c>
       <c r="T16">
-        <v>1.138220939356341</v>
+        <v>1.148529275724823</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>36.45471679285505</v>
+        <v>34.02440233999804</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08680000999305208</v>
+        <v>0.08660178464635275</v>
       </c>
       <c r="C17">
-        <v>57533.71619912663</v>
+        <v>56963.78368826583</v>
       </c>
       <c r="D17">
-        <v>30998.91167268164</v>
+        <v>31149.51219339118</v>
       </c>
       <c r="E17">
-        <v>-23849.50768347838</v>
+        <v>-23128.97465190804</v>
       </c>
       <c r="F17">
-        <v>10807.99547355501</v>
+        <v>11528.52850512534</v>
       </c>
       <c r="G17">
         <v>37342.8</v>
@@ -2687,28 +2687,28 @@
         <v>18497.1</v>
       </c>
       <c r="M17">
-        <v>543.642172319817</v>
+        <v>579.8849838078047</v>
       </c>
       <c r="N17">
-        <v>17953.45782768018</v>
+        <v>17917.2150161922</v>
       </c>
       <c r="O17">
-        <v>4631.992119541487</v>
+        <v>4622.641474177587</v>
       </c>
       <c r="P17">
-        <v>13321.4657081387</v>
+        <v>13294.57354201461</v>
       </c>
       <c r="Q17">
-        <v>18270.5657081387</v>
+        <v>18243.67354201461</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09553131763888481</v>
+        <v>0.0959882960075628</v>
       </c>
       <c r="T17">
-        <v>1.148529275724823</v>
+        <v>1.159083048673506</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>34.02440233999805</v>
+        <v>31.89787719374817</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,22 +2733,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08660178464635275</v>
+        <v>0.0864035592996534</v>
       </c>
       <c r="C18">
-        <v>56963.78368826583</v>
+        <v>56395.32163176648</v>
       </c>
       <c r="D18">
-        <v>31149.51219339118</v>
+        <v>31301.58316846216</v>
       </c>
       <c r="E18">
-        <v>-23128.97465190804</v>
+        <v>-22408.44162033771</v>
       </c>
       <c r="F18">
-        <v>11528.52850512534</v>
+        <v>12249.06153669568</v>
       </c>
       <c r="G18">
         <v>37342.8</v>
@@ -2769,28 +2769,28 @@
         <v>18497.1</v>
       </c>
       <c r="M18">
-        <v>579.8849838078047</v>
+        <v>616.1277952957927</v>
       </c>
       <c r="N18">
-        <v>17917.2150161922</v>
+        <v>17880.97220470421</v>
       </c>
       <c r="O18">
-        <v>4622.641474177587</v>
+        <v>4613.290828813686</v>
       </c>
       <c r="P18">
-        <v>13294.57354201461</v>
+        <v>13267.68137589052</v>
       </c>
       <c r="Q18">
-        <v>18243.67354201461</v>
+        <v>18216.78137589052</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0959882960075628</v>
+        <v>0.09645628590319688</v>
       </c>
       <c r="T18">
-        <v>1.159083048673506</v>
+        <v>1.169891129404085</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.89787719374817</v>
+        <v>30.02153147646886</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,22 +2815,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0864035592996534</v>
+        <v>0.08620533395295407</v>
       </c>
       <c r="C19">
-        <v>56395.32163176648</v>
+        <v>55828.3516714241</v>
       </c>
       <c r="D19">
-        <v>31301.58316846216</v>
+        <v>31455.1462396901</v>
       </c>
       <c r="E19">
-        <v>-22408.44162033771</v>
+        <v>-21687.90858876738</v>
       </c>
       <c r="F19">
-        <v>12249.06153669568</v>
+        <v>12969.59456826601</v>
       </c>
       <c r="G19">
         <v>37342.8</v>
@@ -2851,28 +2851,28 @@
         <v>18497.1</v>
       </c>
       <c r="M19">
-        <v>616.1277952957927</v>
+        <v>652.3706067837804</v>
       </c>
       <c r="N19">
-        <v>17880.97220470421</v>
+        <v>17844.72939321622</v>
       </c>
       <c r="O19">
-        <v>4613.290828813686</v>
+        <v>4603.940183449785</v>
       </c>
       <c r="P19">
-        <v>13267.68137589052</v>
+        <v>13240.78920976644</v>
       </c>
       <c r="Q19">
-        <v>18216.78137589052</v>
+        <v>18189.88920976644</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09645628590319688</v>
+        <v>0.09693569018652935</v>
       </c>
       <c r="T19">
-        <v>1.169891129404085</v>
+        <v>1.180962821859801</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>30.02153147646886</v>
+        <v>28.35366861666504</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,22 +2897,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08620533395295407</v>
+        <v>0.08600710860625474</v>
       </c>
       <c r="C20">
-        <v>55828.3516714241</v>
+        <v>55262.89587581971</v>
       </c>
       <c r="D20">
-        <v>31455.1462396901</v>
+        <v>31610.22347565605</v>
       </c>
       <c r="E20">
-        <v>-21687.90858876738</v>
+        <v>-20967.37555719704</v>
       </c>
       <c r="F20">
-        <v>12969.59456826601</v>
+        <v>13690.12759983635</v>
       </c>
       <c r="G20">
         <v>37342.8</v>
@@ -2933,28 +2933,28 @@
         <v>18497.1</v>
       </c>
       <c r="M20">
-        <v>652.3706067837803</v>
+        <v>688.6134182717682</v>
       </c>
       <c r="N20">
-        <v>17844.72939321622</v>
+        <v>17808.48658172823</v>
       </c>
       <c r="O20">
-        <v>4603.940183449785</v>
+        <v>4594.589538085885</v>
       </c>
       <c r="P20">
-        <v>13240.78920976644</v>
+        <v>13213.89704364235</v>
       </c>
       <c r="Q20">
-        <v>18189.88920976644</v>
+        <v>18162.99704364235</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09693569018652935</v>
+        <v>0.09742693161266017</v>
       </c>
       <c r="T20">
-        <v>1.180962821859801</v>
+        <v>1.19230788943788</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>28.35366861666504</v>
+        <v>26.86137026841951</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,22 +2979,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08600710860625474</v>
+        <v>0.08580888325955541</v>
       </c>
       <c r="C21">
-        <v>55262.89587581971</v>
+        <v>54698.97675089243</v>
       </c>
       <c r="D21">
-        <v>31610.22347565605</v>
+        <v>31766.83738229912</v>
       </c>
       <c r="E21">
-        <v>-20967.37555719704</v>
+        <v>-20246.84252562671</v>
       </c>
       <c r="F21">
-        <v>13690.12759983635</v>
+        <v>14410.66063140668</v>
       </c>
       <c r="G21">
         <v>37342.8</v>
@@ -3015,28 +3015,28 @@
         <v>18497.1</v>
       </c>
       <c r="M21">
-        <v>688.6134182717682</v>
+        <v>724.856229759756</v>
       </c>
       <c r="N21">
-        <v>17808.48658172823</v>
+        <v>17772.24377024025</v>
       </c>
       <c r="O21">
-        <v>4594.589538085885</v>
+        <v>4585.238892721984</v>
       </c>
       <c r="P21">
-        <v>13213.89704364235</v>
+        <v>13187.00487751826</v>
       </c>
       <c r="Q21">
-        <v>18162.99704364235</v>
+        <v>18136.10487751826</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09742693161266017</v>
+        <v>0.09793045407444424</v>
       </c>
       <c r="T21">
-        <v>1.19230788943788</v>
+        <v>1.20393658370541</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3053,7 +3053,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.86137026841951</v>
+        <v>25.51830175499853</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,22 +3061,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08580888325955541</v>
+        <v>0.08561065791285608</v>
       </c>
       <c r="C22">
-        <v>54698.97675089243</v>
+        <v>54136.61725082795</v>
       </c>
       <c r="D22">
-        <v>31766.83738229912</v>
+        <v>31925.01091380496</v>
       </c>
       <c r="E22">
-        <v>-20246.84252562671</v>
+        <v>-19526.30949405638</v>
       </c>
       <c r="F22">
-        <v>14410.66063140668</v>
+        <v>15131.19366297702</v>
       </c>
       <c r="G22">
         <v>37342.8</v>
@@ -3097,28 +3097,28 @@
         <v>18497.1</v>
       </c>
       <c r="M22">
-        <v>724.856229759756</v>
+        <v>761.0990412477438</v>
       </c>
       <c r="N22">
-        <v>17772.24377024025</v>
+        <v>17736.00095875226</v>
       </c>
       <c r="O22">
-        <v>4585.238892721984</v>
+        <v>4575.888247358082</v>
       </c>
       <c r="P22">
-        <v>13187.00487751826</v>
+        <v>13160.11271139418</v>
       </c>
       <c r="Q22">
-        <v>18136.10487751826</v>
+        <v>18109.21271139418</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09793045407444424</v>
+        <v>0.09844672394032414</v>
       </c>
       <c r="T22">
-        <v>1.20393658370541</v>
+        <v>1.21585967529617</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.51830175499853</v>
+        <v>24.30314452857003</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,22 +3143,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08561065791285605</v>
+        <v>0.08541243256615672</v>
       </c>
       <c r="C23">
-        <v>54136.61725082798</v>
+        <v>53575.84078927388</v>
       </c>
       <c r="D23">
-        <v>31925.01091380498</v>
+        <v>32084.76748382123</v>
       </c>
       <c r="E23">
-        <v>-19526.30949405638</v>
+        <v>-18805.77646248604</v>
       </c>
       <c r="F23">
-        <v>15131.19366297701</v>
+        <v>15851.72669454735</v>
       </c>
       <c r="G23">
         <v>37342.8</v>
@@ -3179,28 +3179,28 @@
         <v>18497.1</v>
       </c>
       <c r="M23">
-        <v>761.0990412477437</v>
+        <v>797.3418527357315</v>
       </c>
       <c r="N23">
-        <v>17736.00095875226</v>
+        <v>17699.75814726427</v>
       </c>
       <c r="O23">
-        <v>4575.888247358082</v>
+        <v>4566.537601994182</v>
       </c>
       <c r="P23">
-        <v>13160.11271139418</v>
+        <v>13133.22054527009</v>
       </c>
       <c r="Q23">
-        <v>18109.21271139418</v>
+        <v>18082.32054527009</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09844672394032411</v>
+        <v>0.09897623149507272</v>
       </c>
       <c r="T23">
-        <v>1.215859675296169</v>
+        <v>1.228088487184128</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.30314452857004</v>
+        <v>23.19845614090776</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08541243256615672</v>
+        <v>0.08521420721945738</v>
       </c>
       <c r="C24">
-        <v>53575.84078927388</v>
+        <v>53016.67125089359</v>
       </c>
       <c r="D24">
-        <v>32084.76748382123</v>
+        <v>32246.13097701127</v>
       </c>
       <c r="E24">
-        <v>-18805.77646248604</v>
+        <v>-18085.24343091571</v>
       </c>
       <c r="F24">
-        <v>15851.72669454735</v>
+        <v>16572.25972611768</v>
       </c>
       <c r="G24">
         <v>37342.8</v>
@@ -3261,28 +3261,28 @@
         <v>18497.1</v>
       </c>
       <c r="M24">
-        <v>797.3418527357315</v>
+        <v>833.5846642237193</v>
       </c>
       <c r="N24">
-        <v>17699.75814726427</v>
+        <v>17663.51533577628</v>
       </c>
       <c r="O24">
-        <v>4566.537601994182</v>
+        <v>4557.186956630281</v>
       </c>
       <c r="P24">
-        <v>13133.22054527009</v>
+        <v>13106.328379146</v>
       </c>
       <c r="Q24">
-        <v>18082.32054527009</v>
+        <v>18055.428379146</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09897623149507272</v>
+        <v>0.09951949249280179</v>
       </c>
       <c r="T24">
-        <v>1.228088487184128</v>
+        <v>1.240634930549695</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>23.19845614090776</v>
+        <v>22.1898276130422</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,22 +3307,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08521420721945738</v>
+        <v>0.08501598187275805</v>
       </c>
       <c r="C25">
-        <v>53016.67125089359</v>
+        <v>52459.13300327053</v>
       </c>
       <c r="D25">
-        <v>32246.13097701127</v>
+        <v>32409.12576095854</v>
       </c>
       <c r="E25">
-        <v>-18085.24343091571</v>
+        <v>-17364.71039934537</v>
       </c>
       <c r="F25">
-        <v>16572.25972611768</v>
+        <v>17292.79275768802</v>
       </c>
       <c r="G25">
         <v>37342.8</v>
@@ -3343,28 +3343,28 @@
         <v>18497.1</v>
       </c>
       <c r="M25">
-        <v>833.5846642237193</v>
+        <v>869.8274757117073</v>
       </c>
       <c r="N25">
-        <v>17663.51533577628</v>
+        <v>17627.2725242883</v>
       </c>
       <c r="O25">
-        <v>4557.186956630281</v>
+        <v>4547.83631126638</v>
       </c>
       <c r="P25">
-        <v>13106.328379146</v>
+        <v>13079.43621302192</v>
       </c>
       <c r="Q25">
-        <v>18055.428379146</v>
+        <v>18028.53621302191</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09951949249280179</v>
+        <v>0.1000770498325764</v>
       </c>
       <c r="T25">
-        <v>1.240634930549695</v>
+        <v>1.253511543477515</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>22.1898276130422</v>
+        <v>21.26525146249878</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,22 +3389,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08501598187275805</v>
+        <v>0.08481775652605869</v>
       </c>
       <c r="C26">
-        <v>52459.13300327053</v>
+        <v>51903.25090917526</v>
       </c>
       <c r="D26">
-        <v>32409.12576095854</v>
+        <v>32573.7766984336</v>
       </c>
       <c r="E26">
-        <v>-17364.71039934537</v>
+        <v>-16644.17736777504</v>
       </c>
       <c r="F26">
-        <v>17292.79275768801</v>
+        <v>18013.32578925835</v>
       </c>
       <c r="G26">
         <v>37342.8</v>
@@ -3425,28 +3425,28 @@
         <v>18497.1</v>
       </c>
       <c r="M26">
-        <v>869.8274757117071</v>
+        <v>906.0702871996949</v>
       </c>
       <c r="N26">
-        <v>17627.2725242883</v>
+        <v>17591.02971280031</v>
       </c>
       <c r="O26">
-        <v>4547.83631126638</v>
+        <v>4538.48566590248</v>
       </c>
       <c r="P26">
-        <v>13079.43621302192</v>
+        <v>13052.54404689783</v>
       </c>
       <c r="Q26">
-        <v>18028.53621302191</v>
+        <v>18001.64404689783</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1000770498325764</v>
+        <v>0.1006494753680783</v>
       </c>
       <c r="T26">
-        <v>1.253511543477515</v>
+        <v>1.266731532750076</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.26525146249878</v>
+        <v>20.41464140399883</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,22 +3471,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08481775652605869</v>
+        <v>0.08461953117935936</v>
       </c>
       <c r="C27">
-        <v>51903.25090917526</v>
+        <v>51349.05033920835</v>
       </c>
       <c r="D27">
-        <v>32573.7766984336</v>
+        <v>32740.10916003702</v>
       </c>
       <c r="E27">
-        <v>-16644.17736777504</v>
+        <v>-15923.6443362047</v>
       </c>
       <c r="F27">
-        <v>18013.32578925835</v>
+        <v>18733.85882082869</v>
       </c>
       <c r="G27">
         <v>37342.8</v>
@@ -3507,28 +3507,28 @@
         <v>18497.1</v>
       </c>
       <c r="M27">
-        <v>906.0702871996949</v>
+        <v>942.3130986876828</v>
       </c>
       <c r="N27">
-        <v>17591.02971280031</v>
+        <v>17554.78690131232</v>
       </c>
       <c r="O27">
-        <v>4538.48566590248</v>
+        <v>4529.135020538579</v>
       </c>
       <c r="P27">
-        <v>13052.54404689783</v>
+        <v>13025.65188077374</v>
       </c>
       <c r="Q27">
-        <v>18001.64404689783</v>
+        <v>17974.75188077374</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1006494753680783</v>
+        <v>0.1012373718639991</v>
       </c>
       <c r="T27">
-        <v>1.266731532750076</v>
+        <v>1.280308819030004</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.41464140399883</v>
+        <v>19.62946288846041</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,22 +3553,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08461953117935936</v>
+        <v>0.08442130583266003</v>
       </c>
       <c r="C28">
-        <v>51349.05033920835</v>
+        <v>50796.55718483278</v>
       </c>
       <c r="D28">
-        <v>32740.10916003702</v>
+        <v>32908.1490372318</v>
       </c>
       <c r="E28">
-        <v>-15923.6443362047</v>
+        <v>-15203.11130463437</v>
       </c>
       <c r="F28">
-        <v>18733.85882082869</v>
+        <v>19454.39185239902</v>
       </c>
       <c r="G28">
         <v>37342.8</v>
@@ -3589,28 +3589,28 @@
         <v>18497.1</v>
       </c>
       <c r="M28">
-        <v>942.3130986876828</v>
+        <v>978.5559101756705</v>
       </c>
       <c r="N28">
-        <v>17554.78690131232</v>
+        <v>17518.54408982433</v>
       </c>
       <c r="O28">
-        <v>4529.135020538579</v>
+        <v>4519.784375174678</v>
       </c>
       <c r="P28">
-        <v>13025.65188077374</v>
+        <v>12998.75971464966</v>
       </c>
       <c r="Q28">
-        <v>17974.75188077374</v>
+        <v>17947.85971464965</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1012373718639991</v>
+        <v>0.1018413751132329</v>
       </c>
       <c r="T28">
-        <v>1.280308819030004</v>
+        <v>1.294258085755957</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3627,7 +3627,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.62946288846041</v>
+        <v>18.90244574444336</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,22 +3635,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08442130583266003</v>
+        <v>0.08422308048596068</v>
       </c>
       <c r="C29">
-        <v>50796.55718483278</v>
+        <v>50245.79787180963</v>
       </c>
       <c r="D29">
-        <v>32908.1490372318</v>
+        <v>33077.92275577898</v>
       </c>
       <c r="E29">
-        <v>-15203.11130463437</v>
+        <v>-14482.57827306403</v>
       </c>
       <c r="F29">
-        <v>19454.39185239902</v>
+        <v>20174.92488396935</v>
       </c>
       <c r="G29">
         <v>37342.8</v>
@@ -3671,28 +3671,28 @@
         <v>18497.1</v>
       </c>
       <c r="M29">
-        <v>978.5559101756705</v>
+        <v>1014.798721663658</v>
       </c>
       <c r="N29">
-        <v>17518.54408982433</v>
+        <v>17482.30127833634</v>
       </c>
       <c r="O29">
-        <v>4519.784375174678</v>
+        <v>4510.433729810777</v>
       </c>
       <c r="P29">
-        <v>12998.75971464966</v>
+        <v>12971.86754852557</v>
       </c>
       <c r="Q29">
-        <v>17947.85971464965</v>
+        <v>17920.96754852556</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1018413751132329</v>
+        <v>0.102462156230501</v>
       </c>
       <c r="T29">
-        <v>1.294258085755957</v>
+        <v>1.308594832113186</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3709,7 +3709,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.90244574444336</v>
+        <v>18.22735839642753</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,22 +3717,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08422308048596068</v>
+        <v>0.08402485513926135</v>
       </c>
       <c r="C30">
-        <v>50245.79787180963</v>
+        <v>49696.79937405164</v>
       </c>
       <c r="D30">
-        <v>33077.92275577898</v>
+        <v>33249.45728959134</v>
       </c>
       <c r="E30">
-        <v>-14482.57827306403</v>
+        <v>-13762.0452414937</v>
       </c>
       <c r="F30">
-        <v>20174.92488396935</v>
+        <v>20895.45791553969</v>
       </c>
       <c r="G30">
         <v>37342.8</v>
@@ -3753,28 +3753,28 @@
         <v>18497.1</v>
       </c>
       <c r="M30">
-        <v>1014.798721663658</v>
+        <v>1051.041533151646</v>
       </c>
       <c r="N30">
-        <v>17482.30127833634</v>
+        <v>17446.05846684836</v>
       </c>
       <c r="O30">
-        <v>4510.433729810777</v>
+        <v>4501.083084446876</v>
       </c>
       <c r="P30">
-        <v>12971.86754852557</v>
+        <v>12944.97538240148</v>
       </c>
       <c r="Q30">
-        <v>17920.96754852556</v>
+        <v>17894.07538240148</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.102462156230501</v>
+        <v>0.1031004241398047</v>
       </c>
       <c r="T30">
-        <v>1.308594832113186</v>
+        <v>1.323335430480479</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3791,7 +3791,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.22735839642753</v>
+        <v>17.59882879655071</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,22 +3799,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08402485513926135</v>
+        <v>0.08382662979256202</v>
       </c>
       <c r="C31">
-        <v>49696.79937405165</v>
+        <v>49149.5892279105</v>
       </c>
       <c r="D31">
-        <v>33249.45728959134</v>
+        <v>33422.78017502051</v>
       </c>
       <c r="E31">
-        <v>-13762.0452414937</v>
+        <v>-13041.51220992337</v>
       </c>
       <c r="F31">
-        <v>20895.45791553969</v>
+        <v>21615.99094711002</v>
       </c>
       <c r="G31">
         <v>37342.8</v>
@@ -3835,28 +3835,28 @@
         <v>18497.1</v>
       </c>
       <c r="M31">
-        <v>1051.041533151646</v>
+        <v>1087.284344639634</v>
       </c>
       <c r="N31">
-        <v>17446.05846684836</v>
+        <v>17409.81565536037</v>
       </c>
       <c r="O31">
-        <v>4501.083084446876</v>
+        <v>4491.732439082975</v>
       </c>
       <c r="P31">
-        <v>12944.97538240148</v>
+        <v>12918.08321627739</v>
       </c>
       <c r="Q31">
-        <v>17894.07538240148</v>
+        <v>17867.18321627739</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1031004241398047</v>
+        <v>0.1037569282750886</v>
       </c>
       <c r="T31">
-        <v>1.323335430480479</v>
+        <v>1.338497188801123</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3873,7 +3873,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.59882879655071</v>
+        <v>17.01220116999902</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,22 +3881,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08382662979256202</v>
+        <v>0.08362840444586267</v>
       </c>
       <c r="C32">
-        <v>49149.5892279105</v>
+        <v>48604.19554691284</v>
       </c>
       <c r="D32">
-        <v>33422.78017502051</v>
+        <v>33597.9195255932</v>
       </c>
       <c r="E32">
-        <v>-13041.51220992337</v>
+        <v>-12320.97917835303</v>
       </c>
       <c r="F32">
-        <v>21615.99094711002</v>
+        <v>22336.52397868035</v>
       </c>
       <c r="G32">
         <v>37342.8</v>
@@ -3917,28 +3917,28 @@
         <v>18497.1</v>
       </c>
       <c r="M32">
-        <v>1087.284344639634</v>
+        <v>1123.527156127622</v>
       </c>
       <c r="N32">
-        <v>17409.81565536037</v>
+        <v>17373.57284387238</v>
       </c>
       <c r="O32">
-        <v>4491.732439082975</v>
+        <v>4482.381793719074</v>
       </c>
       <c r="P32">
-        <v>12918.08321627739</v>
+        <v>12891.19105015331</v>
       </c>
       <c r="Q32">
-        <v>17867.18321627739</v>
+        <v>17840.2910501533</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1037569282750886</v>
+        <v>0.104432461515743</v>
       </c>
       <c r="T32">
-        <v>1.338497188801123</v>
+        <v>1.354098418377437</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>17.01220116999902</v>
+        <v>16.46342048709583</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,22 +3963,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08362840444586267</v>
+        <v>0.08343017909916332</v>
       </c>
       <c r="C33">
-        <v>48604.19554691284</v>
+        <v>48060.64703696244</v>
       </c>
       <c r="D33">
-        <v>33597.9195255932</v>
+        <v>33774.90404721312</v>
       </c>
       <c r="E33">
-        <v>-12320.97917835303</v>
+        <v>-11600.4461467827</v>
       </c>
       <c r="F33">
-        <v>22336.52397868035</v>
+        <v>23057.05701025069</v>
       </c>
       <c r="G33">
         <v>37342.8</v>
@@ -3999,28 +3999,28 @@
         <v>18497.1</v>
       </c>
       <c r="M33">
-        <v>1123.527156127622</v>
+        <v>1159.769967615609</v>
       </c>
       <c r="N33">
-        <v>17373.57284387238</v>
+        <v>17337.33003238439</v>
       </c>
       <c r="O33">
-        <v>4482.381793719074</v>
+        <v>4473.031148355174</v>
       </c>
       <c r="P33">
-        <v>12891.19105015331</v>
+        <v>12864.29888402922</v>
       </c>
       <c r="Q33">
-        <v>17840.2910501533</v>
+        <v>17813.39888402922</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.104432461515743</v>
+        <v>0.1051278633811225</v>
       </c>
       <c r="T33">
-        <v>1.354098418377437</v>
+        <v>1.370158507647173</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.46342048709583</v>
+        <v>15.94893859687409</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,22 +4045,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08343017909916332</v>
+        <v>0.08323195375246398</v>
       </c>
       <c r="C34">
-        <v>48060.64703696244</v>
+        <v>47518.97301202505</v>
       </c>
       <c r="D34">
-        <v>33774.90404721312</v>
+        <v>33953.76305384607</v>
       </c>
       <c r="E34">
-        <v>-11600.4461467827</v>
+        <v>-10879.91311521237</v>
       </c>
       <c r="F34">
-        <v>23057.05701025069</v>
+        <v>23777.59004182102</v>
       </c>
       <c r="G34">
         <v>37342.8</v>
@@ -4081,28 +4081,28 @@
         <v>18497.1</v>
       </c>
       <c r="M34">
-        <v>1159.769967615609</v>
+        <v>1196.012779103597</v>
       </c>
       <c r="N34">
-        <v>17337.33003238439</v>
+        <v>17301.08722089641</v>
       </c>
       <c r="O34">
-        <v>4473.031148355174</v>
+        <v>4463.680502991273</v>
       </c>
       <c r="P34">
-        <v>12864.29888402922</v>
+        <v>12837.40671790513</v>
       </c>
       <c r="Q34">
-        <v>17813.39888402922</v>
+        <v>17786.50671790513</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1051278633811225</v>
+        <v>0.1058440235111403</v>
       </c>
       <c r="T34">
-        <v>1.370158507647173</v>
+        <v>1.386698002566751</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.94893859687409</v>
+        <v>15.46563742727184</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,22 +4127,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08323195375246398</v>
+        <v>0.08303372840576465</v>
       </c>
       <c r="C35">
-        <v>47518.97301202505</v>
+        <v>46979.20341031454</v>
       </c>
       <c r="D35">
-        <v>33953.76305384607</v>
+        <v>34134.5264837059</v>
       </c>
       <c r="E35">
-        <v>-10879.91311521237</v>
+        <v>-10159.38008364203</v>
       </c>
       <c r="F35">
-        <v>23777.59004182102</v>
+        <v>24498.12307339136</v>
       </c>
       <c r="G35">
         <v>37342.8</v>
@@ -4163,28 +4163,28 @@
         <v>18497.1</v>
       </c>
       <c r="M35">
-        <v>1196.012779103597</v>
+        <v>1232.255590591585</v>
       </c>
       <c r="N35">
-        <v>17301.08722089641</v>
+        <v>17264.84440940842</v>
       </c>
       <c r="O35">
-        <v>4463.680502991273</v>
+        <v>4454.329857627371</v>
       </c>
       <c r="P35">
-        <v>12837.40671790513</v>
+        <v>12810.51455178105</v>
       </c>
       <c r="Q35">
-        <v>17786.50671790513</v>
+        <v>17759.61455178104</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1058440235111403</v>
+        <v>0.1065818854632798</v>
       </c>
       <c r="T35">
-        <v>1.386698002566751</v>
+        <v>1.403738694302074</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.46563742727184</v>
+        <v>15.01076573823443</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,22 +4209,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08303372840576465</v>
+        <v>0.0828355030590653</v>
       </c>
       <c r="C36">
-        <v>46979.20341031454</v>
+        <v>46441.36881099879</v>
       </c>
       <c r="D36">
-        <v>34134.5264837059</v>
+        <v>34317.22491596048</v>
       </c>
       <c r="E36">
-        <v>-10159.38008364203</v>
+        <v>-9438.847052071698</v>
       </c>
       <c r="F36">
-        <v>24498.12307339136</v>
+        <v>25218.65610496169</v>
       </c>
       <c r="G36">
         <v>37342.8</v>
@@ -4245,28 +4245,28 @@
         <v>18497.1</v>
       </c>
       <c r="M36">
-        <v>1232.255590591585</v>
+        <v>1268.498402079573</v>
       </c>
       <c r="N36">
-        <v>17264.84440940842</v>
+        <v>17228.60159792043</v>
       </c>
       <c r="O36">
-        <v>4454.329857627371</v>
+        <v>4444.979212263471</v>
       </c>
       <c r="P36">
-        <v>12810.51455178105</v>
+        <v>12783.62238565696</v>
       </c>
       <c r="Q36">
-        <v>17759.61455178104</v>
+        <v>17732.72238565695</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1065818854632798</v>
+        <v>0.1073424508601005</v>
       </c>
       <c r="T36">
-        <v>1.403738694302074</v>
+        <v>1.421303715013869</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>15.01076573823443</v>
+        <v>14.58188671714202</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0828355030590653</v>
+        <v>0.08263727771236597</v>
       </c>
       <c r="C37">
-        <v>46441.36881099879</v>
+        <v>45905.5004514447</v>
       </c>
       <c r="D37">
-        <v>34317.22491596048</v>
+        <v>34501.88958797672</v>
       </c>
       <c r="E37">
-        <v>-9438.847052071698</v>
+        <v>-8718.314020501362</v>
       </c>
       <c r="F37">
-        <v>25218.65610496169</v>
+        <v>25939.18913653203</v>
       </c>
       <c r="G37">
         <v>37342.8</v>
@@ -4327,28 +4327,28 @@
         <v>18497.1</v>
       </c>
       <c r="M37">
-        <v>1268.498402079573</v>
+        <v>1304.741213567561</v>
       </c>
       <c r="N37">
-        <v>17228.60159792043</v>
+        <v>17192.35878643244</v>
       </c>
       <c r="O37">
-        <v>4444.979212263471</v>
+        <v>4435.62856689957</v>
       </c>
       <c r="P37">
-        <v>12783.62238565696</v>
+        <v>12756.73021953287</v>
       </c>
       <c r="Q37">
-        <v>17732.72238565695</v>
+        <v>17705.83021953287</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1073424508601005</v>
+        <v>0.1081267839255718</v>
       </c>
       <c r="T37">
-        <v>1.421303715013869</v>
+        <v>1.439417642622907</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.58188671714202</v>
+        <v>14.17683430833252</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,22 +4373,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08263727771236598</v>
+        <v>0.08243905236566662</v>
       </c>
       <c r="C38">
-        <v>45905.50045144468</v>
+        <v>45371.63024502341</v>
       </c>
       <c r="D38">
-        <v>34501.8895879767</v>
+        <v>34688.55241312576</v>
       </c>
       <c r="E38">
-        <v>-8718.314020501366</v>
+        <v>-7997.78098893103</v>
       </c>
       <c r="F38">
-        <v>25939.18913653202</v>
+        <v>26659.72216810236</v>
       </c>
       <c r="G38">
         <v>37342.8</v>
@@ -4409,28 +4409,28 @@
         <v>18497.1</v>
       </c>
       <c r="M38">
-        <v>1304.741213567561</v>
+        <v>1340.984025055548</v>
       </c>
       <c r="N38">
-        <v>17192.35878643244</v>
+        <v>17156.11597494445</v>
       </c>
       <c r="O38">
-        <v>4435.62856689957</v>
+        <v>4426.277921535669</v>
       </c>
       <c r="P38">
-        <v>12756.73021953287</v>
+        <v>12729.83805340878</v>
       </c>
       <c r="Q38">
-        <v>17705.83021953287</v>
+        <v>17678.93805340878</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1081267839255718</v>
+        <v>0.1089360164534391</v>
       </c>
       <c r="T38">
-        <v>1.439417642622907</v>
+        <v>1.458106615552867</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4447,7 +4447,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.17683430833252</v>
+        <v>13.79367662432353</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,22 +4455,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08243905236566662</v>
+        <v>0.08224082701896729</v>
       </c>
       <c r="C39">
-        <v>45371.63024502341</v>
+        <v>44839.79079949631</v>
       </c>
       <c r="D39">
-        <v>34688.55241312576</v>
+        <v>34877.24599916899</v>
       </c>
       <c r="E39">
-        <v>-7997.78098893103</v>
+        <v>-7277.247957360698</v>
       </c>
       <c r="F39">
-        <v>26659.72216810236</v>
+        <v>27380.25519967269</v>
       </c>
       <c r="G39">
         <v>37342.8</v>
@@ -4491,28 +4491,28 @@
         <v>18497.1</v>
       </c>
       <c r="M39">
-        <v>1340.984025055548</v>
+        <v>1377.226836543536</v>
       </c>
       <c r="N39">
-        <v>17156.11597494445</v>
+        <v>17119.87316345646</v>
       </c>
       <c r="O39">
-        <v>4426.277921535669</v>
+        <v>4416.927276171768</v>
       </c>
       <c r="P39">
-        <v>12729.83805340878</v>
+        <v>12702.9458872847</v>
       </c>
       <c r="Q39">
-        <v>17678.93805340878</v>
+        <v>17652.04588728469</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1089360164534391</v>
+        <v>0.1097713532563989</v>
       </c>
       <c r="T39">
-        <v>1.458106615552867</v>
+        <v>1.477398458577341</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.79367662432353</v>
+        <v>13.43068513420975</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,22 +4537,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08224082701896729</v>
+        <v>0.08204260167226796</v>
       </c>
       <c r="C40">
-        <v>44839.79079949631</v>
+        <v>44310.01543600456</v>
       </c>
       <c r="D40">
-        <v>34877.24599916899</v>
+        <v>35068.00366724758</v>
       </c>
       <c r="E40">
-        <v>-7277.247957360698</v>
+        <v>-6556.714925790362</v>
       </c>
       <c r="F40">
-        <v>27380.25519967269</v>
+        <v>28100.78823124303</v>
       </c>
       <c r="G40">
         <v>37342.8</v>
@@ -4573,28 +4573,28 @@
         <v>18497.1</v>
       </c>
       <c r="M40">
-        <v>1377.226836543536</v>
+        <v>1413.469648031524</v>
       </c>
       <c r="N40">
-        <v>17119.87316345646</v>
+        <v>17083.63035196848</v>
       </c>
       <c r="O40">
-        <v>4416.927276171768</v>
+        <v>4407.576630807867</v>
       </c>
       <c r="P40">
-        <v>12702.9458872847</v>
+        <v>12676.05372116061</v>
       </c>
       <c r="Q40">
-        <v>17652.04588728469</v>
+        <v>17625.15372116061</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1097713532563989</v>
+        <v>0.1106340781512589</v>
       </c>
       <c r="T40">
-        <v>1.477398458577341</v>
+        <v>1.497322821045242</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4611,7 +4611,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.43068513420975</v>
+        <v>13.08630859230694</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,22 +4619,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08204260167226796</v>
+        <v>0.08184437632556862</v>
       </c>
       <c r="C41">
-        <v>44310.01543600456</v>
+        <v>43782.33820868524</v>
       </c>
       <c r="D41">
-        <v>35068.00366724758</v>
+        <v>35260.8594714986</v>
       </c>
       <c r="E41">
-        <v>-6556.714925790362</v>
+        <v>-5836.181894220026</v>
       </c>
       <c r="F41">
-        <v>28100.78823124303</v>
+        <v>28821.32126281336</v>
       </c>
       <c r="G41">
         <v>37342.8</v>
@@ -4655,28 +4655,28 @@
         <v>18497.1</v>
       </c>
       <c r="M41">
-        <v>1413.469648031524</v>
+        <v>1449.712459519512</v>
       </c>
       <c r="N41">
-        <v>17083.63035196848</v>
+        <v>17047.38754048049</v>
       </c>
       <c r="O41">
-        <v>4407.576630807867</v>
+        <v>4398.225985443966</v>
       </c>
       <c r="P41">
-        <v>12676.05372116061</v>
+        <v>12649.16155503652</v>
       </c>
       <c r="Q41">
-        <v>17625.15372116061</v>
+        <v>17598.26155503652</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1106340781512589</v>
+        <v>0.1115255605426144</v>
       </c>
       <c r="T41">
-        <v>1.497322821045242</v>
+        <v>1.517911328928739</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4693,7 +4693,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>13.08630859230694</v>
+        <v>12.75915087749927</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,22 +4701,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08184437632556862</v>
+        <v>0.08164615097886926</v>
       </c>
       <c r="C42">
-        <v>43782.33820868524</v>
+        <v>43256.79392493822</v>
       </c>
       <c r="D42">
-        <v>35260.8594714986</v>
+        <v>35455.84821932191</v>
       </c>
       <c r="E42">
-        <v>-5836.181894220026</v>
+        <v>-5115.648862649694</v>
       </c>
       <c r="F42">
-        <v>28821.32126281336</v>
+        <v>29541.85429438369</v>
       </c>
       <c r="G42">
         <v>37342.8</v>
@@ -4737,28 +4737,28 @@
         <v>18497.1</v>
       </c>
       <c r="M42">
-        <v>1449.712459519512</v>
+        <v>1485.9552710075</v>
       </c>
       <c r="N42">
-        <v>17047.38754048049</v>
+        <v>17011.1447289925</v>
       </c>
       <c r="O42">
-        <v>4398.225985443966</v>
+        <v>4388.875340080065</v>
       </c>
       <c r="P42">
-        <v>12649.16155503652</v>
+        <v>12622.26938891244</v>
       </c>
       <c r="Q42">
-        <v>17598.26155503652</v>
+        <v>17571.36938891243</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1115255605426144</v>
+        <v>0.1124472626760496</v>
       </c>
       <c r="T42">
-        <v>1.517911328928739</v>
+        <v>1.53919775233371</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4775,7 +4775,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.75915087749927</v>
+        <v>12.44795207560904</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,22 +4783,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08164615097886926</v>
+        <v>0.08144792563216995</v>
       </c>
       <c r="C43">
-        <v>43256.79392493822</v>
+        <v>42733.41816636924</v>
       </c>
       <c r="D43">
-        <v>35455.84821932191</v>
+        <v>35653.00549232326</v>
       </c>
       <c r="E43">
-        <v>-5115.648862649694</v>
+        <v>-4395.115831079358</v>
       </c>
       <c r="F43">
-        <v>29541.85429438369</v>
+        <v>30262.38732595403</v>
       </c>
       <c r="G43">
         <v>37342.8</v>
@@ -4819,28 +4819,28 @@
         <v>18497.1</v>
       </c>
       <c r="M43">
-        <v>1485.9552710075</v>
+        <v>1522.198082495488</v>
       </c>
       <c r="N43">
-        <v>17011.1447289925</v>
+        <v>16974.90191750451</v>
       </c>
       <c r="O43">
-        <v>4388.875340080065</v>
+        <v>4379.524694716165</v>
       </c>
       <c r="P43">
-        <v>12622.26938891244</v>
+        <v>12595.37722278835</v>
       </c>
       <c r="Q43">
-        <v>17571.36938891243</v>
+        <v>17544.47722278835</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1124472626760496</v>
+        <v>0.1134007476416723</v>
       </c>
       <c r="T43">
-        <v>1.53919775233371</v>
+        <v>1.561218190338853</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>12.44795207560904</v>
+        <v>12.15157226428502</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,22 +4865,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08144792563216996</v>
+        <v>0.0812497002854706</v>
       </c>
       <c r="C44">
-        <v>42733.41816636921</v>
+        <v>42212.24731043587</v>
       </c>
       <c r="D44">
-        <v>35653.00549232324</v>
+        <v>35852.36766796021</v>
       </c>
       <c r="E44">
-        <v>-4395.115831079362</v>
+        <v>-3674.582799509026</v>
       </c>
       <c r="F44">
-        <v>30262.38732595403</v>
+        <v>30982.92035752436</v>
       </c>
       <c r="G44">
         <v>37342.8</v>
@@ -4901,28 +4901,28 @@
         <v>18497.1</v>
       </c>
       <c r="M44">
-        <v>1522.198082495487</v>
+        <v>1558.440893983475</v>
       </c>
       <c r="N44">
-        <v>16974.90191750451</v>
+        <v>16938.65910601653</v>
       </c>
       <c r="O44">
-        <v>4379.524694716165</v>
+        <v>4370.174049352264</v>
       </c>
       <c r="P44">
-        <v>12595.37722278835</v>
+        <v>12568.48505666426</v>
       </c>
       <c r="Q44">
-        <v>17544.47722278835</v>
+        <v>17517.58505666426</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1134007476416723</v>
+        <v>0.1143876882201239</v>
       </c>
       <c r="T44">
-        <v>1.561218190338853</v>
+        <v>1.584011275291545</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4939,7 +4939,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>12.15157226428502</v>
+        <v>11.86897756046443</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,22 +4947,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0812497002854706</v>
+        <v>0.08105147493877127</v>
       </c>
       <c r="C45">
-        <v>42212.24731043587</v>
+        <v>41693.31855282334</v>
       </c>
       <c r="D45">
-        <v>35852.36766796021</v>
+        <v>36053.97194191803</v>
       </c>
       <c r="E45">
-        <v>-3674.582799509026</v>
+        <v>-2954.049767938694</v>
       </c>
       <c r="F45">
-        <v>30982.92035752436</v>
+        <v>31703.4533890947</v>
       </c>
       <c r="G45">
         <v>37342.8</v>
@@ -4983,28 +4983,28 @@
         <v>18497.1</v>
       </c>
       <c r="M45">
-        <v>1558.440893983475</v>
+        <v>1594.683705471463</v>
       </c>
       <c r="N45">
-        <v>16938.65910601653</v>
+        <v>16902.41629452854</v>
       </c>
       <c r="O45">
-        <v>4370.174049352264</v>
+        <v>4360.823403988363</v>
       </c>
       <c r="P45">
-        <v>12568.48505666426</v>
+        <v>12541.59289054018</v>
       </c>
       <c r="Q45">
-        <v>17517.58505666426</v>
+        <v>17490.69289054017</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1143876882201239</v>
+        <v>0.1154098766763773</v>
       </c>
       <c r="T45">
-        <v>1.584011275291545</v>
+        <v>1.607618398992547</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.86897756046443</v>
+        <v>11.59922807045388</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,22 +5029,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08105147493877127</v>
+        <v>0.08085324959207192</v>
       </c>
       <c r="C46">
-        <v>41693.31855282334</v>
+        <v>41176.66993058011</v>
       </c>
       <c r="D46">
-        <v>36053.97194191803</v>
+        <v>36257.85635124514</v>
       </c>
       <c r="E46">
-        <v>-2954.049767938694</v>
+        <v>-2233.516736368358</v>
       </c>
       <c r="F46">
-        <v>31703.4533890947</v>
+        <v>32423.98642066503</v>
       </c>
       <c r="G46">
         <v>37342.8</v>
@@ -5065,28 +5065,28 @@
         <v>18497.1</v>
       </c>
       <c r="M46">
-        <v>1594.683705471463</v>
+        <v>1630.926516959451</v>
       </c>
       <c r="N46">
-        <v>16902.41629452854</v>
+        <v>16866.17348304055</v>
       </c>
       <c r="O46">
-        <v>4360.823403988363</v>
+        <v>4351.472758624463</v>
       </c>
       <c r="P46">
-        <v>12541.59289054018</v>
+        <v>12514.70072441609</v>
       </c>
       <c r="Q46">
-        <v>17490.69289054017</v>
+        <v>17463.80072441609</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1154098766763773</v>
+        <v>0.1164692356219489</v>
       </c>
       <c r="T46">
-        <v>1.607618398992547</v>
+        <v>1.632083963555404</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.59922807045388</v>
+        <v>11.34146744666602</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,22 +5111,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08085324959207192</v>
+        <v>0.08065502424537259</v>
       </c>
       <c r="C47">
-        <v>41176.66993058011</v>
+        <v>40662.34034604237</v>
       </c>
       <c r="D47">
-        <v>36257.85635124514</v>
+        <v>36464.05979827773</v>
       </c>
       <c r="E47">
-        <v>-2233.516736368358</v>
+        <v>-1512.983704798025</v>
       </c>
       <c r="F47">
-        <v>32423.98642066503</v>
+        <v>33144.51945223536</v>
       </c>
       <c r="G47">
         <v>37342.8</v>
@@ -5147,28 +5147,28 @@
         <v>18497.1</v>
       </c>
       <c r="M47">
-        <v>1630.926516959451</v>
+        <v>1667.169328447439</v>
       </c>
       <c r="N47">
-        <v>16866.17348304055</v>
+        <v>16829.93067155256</v>
       </c>
       <c r="O47">
-        <v>4351.472758624463</v>
+        <v>4342.122113260561</v>
       </c>
       <c r="P47">
-        <v>12514.70072441609</v>
+        <v>12487.808558292</v>
       </c>
       <c r="Q47">
-        <v>17463.80072441609</v>
+        <v>17436.908558292</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1164692356219489</v>
+        <v>0.1175678300840233</v>
       </c>
       <c r="T47">
-        <v>1.632083963555404</v>
+        <v>1.657455660139107</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5185,7 +5185,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>11.34146744666602</v>
+        <v>11.0949138065211</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,22 +5193,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08065502424537259</v>
+        <v>0.08045679889867324</v>
       </c>
       <c r="C48">
-        <v>40662.34034604237</v>
+        <v>40150.36959157996</v>
       </c>
       <c r="D48">
-        <v>36464.05979827773</v>
+        <v>36672.62207538567</v>
       </c>
       <c r="E48">
-        <v>-1512.983704798025</v>
+        <v>-792.4506732276859</v>
       </c>
       <c r="F48">
-        <v>33144.51945223536</v>
+        <v>33865.0524838057</v>
       </c>
       <c r="G48">
         <v>37342.8</v>
@@ -5229,28 +5229,28 @@
         <v>18497.1</v>
       </c>
       <c r="M48">
-        <v>1667.169328447439</v>
+        <v>1703.412139935427</v>
       </c>
       <c r="N48">
-        <v>16829.93067155256</v>
+        <v>16793.68786006458</v>
       </c>
       <c r="O48">
-        <v>4342.122113260561</v>
+        <v>4332.77146789666</v>
       </c>
       <c r="P48">
-        <v>12487.808558292</v>
+        <v>12460.91639216792</v>
       </c>
       <c r="Q48">
-        <v>17436.908558292</v>
+        <v>17410.01639216791</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1175678300840233</v>
+        <v>0.1187078809408929</v>
       </c>
       <c r="T48">
-        <v>1.657455660139107</v>
+        <v>1.683784779235403</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5267,7 +5267,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>11.0949138065211</v>
+        <v>10.85885181063767</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08045679889867324</v>
+        <v>0.08025857355197391</v>
       </c>
       <c r="C49">
-        <v>40150.36959157996</v>
+        <v>39640.79837519627</v>
       </c>
       <c r="D49">
-        <v>36672.62207538567</v>
+        <v>36883.58389057231</v>
       </c>
       <c r="E49">
-        <v>-792.4506732276859</v>
+        <v>-71.91764165735367</v>
       </c>
       <c r="F49">
-        <v>33865.0524838057</v>
+        <v>34585.58551537603</v>
       </c>
       <c r="G49">
         <v>37342.8</v>
@@ -5311,28 +5311,28 @@
         <v>18497.1</v>
       </c>
       <c r="M49">
-        <v>1703.412139935427</v>
+        <v>1739.654951423415</v>
       </c>
       <c r="N49">
-        <v>16793.68786006458</v>
+        <v>16757.44504857659</v>
       </c>
       <c r="O49">
-        <v>4332.77146789666</v>
+        <v>4323.42082253276</v>
       </c>
       <c r="P49">
-        <v>12460.91639216792</v>
+        <v>12434.02422604383</v>
       </c>
       <c r="Q49">
-        <v>17410.01639216791</v>
+        <v>17383.12422604383</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1187078809408929</v>
+        <v>0.1198917799076421</v>
       </c>
       <c r="T49">
-        <v>1.683784779235403</v>
+        <v>1.711126556758479</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5349,7 +5349,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.85885181063767</v>
+        <v>10.63262573124939</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08025857355197391</v>
+        <v>0.08006034820527456</v>
       </c>
       <c r="C50">
-        <v>39640.79837519628</v>
+        <v>39133.66834701684</v>
       </c>
       <c r="D50">
-        <v>36883.58389057231</v>
+        <v>37096.9868939632</v>
       </c>
       <c r="E50">
-        <v>-71.91764165736095</v>
+        <v>648.6153899129786</v>
       </c>
       <c r="F50">
-        <v>34585.58551537603</v>
+        <v>35306.11854694637</v>
       </c>
       <c r="G50">
         <v>37342.8</v>
@@ -5393,28 +5393,28 @@
         <v>18497.1</v>
       </c>
       <c r="M50">
-        <v>1739.654951423414</v>
+        <v>1775.897762911402</v>
       </c>
       <c r="N50">
-        <v>16757.44504857659</v>
+        <v>16721.2022370886</v>
       </c>
       <c r="O50">
-        <v>4323.42082253276</v>
+        <v>4314.070177168859</v>
       </c>
       <c r="P50">
-        <v>12434.02422604383</v>
+        <v>12407.13205991974</v>
       </c>
       <c r="Q50">
-        <v>17383.12422604383</v>
+        <v>17356.23205991974</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1198917799076421</v>
+        <v>0.1211221062848521</v>
       </c>
       <c r="T50">
-        <v>1.711126556758479</v>
+        <v>1.739540560851088</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.63262573124939</v>
+        <v>10.41563336938716</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,22 +5439,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08006034820527456</v>
+        <v>0.07986212285857522</v>
       </c>
       <c r="C51">
-        <v>39133.66834701684</v>
+        <v>38629.02212670277</v>
       </c>
       <c r="D51">
-        <v>37096.9868939632</v>
+        <v>37312.87370521946</v>
       </c>
       <c r="E51">
-        <v>648.6153899129786</v>
+        <v>1369.148421483311</v>
       </c>
       <c r="F51">
-        <v>35306.11854694637</v>
+        <v>36026.6515785167</v>
       </c>
       <c r="G51">
         <v>37342.8</v>
@@ -5475,28 +5475,28 @@
         <v>18497.1</v>
       </c>
       <c r="M51">
-        <v>1775.897762911402</v>
+        <v>1812.14057439939</v>
       </c>
       <c r="N51">
-        <v>16721.2022370886</v>
+        <v>16684.95942560061</v>
       </c>
       <c r="O51">
-        <v>4314.070177168859</v>
+        <v>4304.719531804958</v>
       </c>
       <c r="P51">
-        <v>12407.13205991974</v>
+        <v>12380.23989379566</v>
       </c>
       <c r="Q51">
-        <v>17356.23205991974</v>
+        <v>17329.33989379565</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1211221062848521</v>
+        <v>0.1224016457171505</v>
       </c>
       <c r="T51">
-        <v>1.739540560851088</v>
+        <v>1.769091125107402</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5513,7 +5513,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>10.41563336938716</v>
+        <v>10.20732070199941</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,22 +5521,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07986212285857522</v>
+        <v>0.07966389751187589</v>
       </c>
       <c r="C52">
-        <v>38629.02212670277</v>
+        <v>38126.90333182718</v>
       </c>
       <c r="D52">
-        <v>37312.87370521946</v>
+        <v>37531.28794191421</v>
       </c>
       <c r="E52">
-        <v>1369.148421483311</v>
+        <v>2089.681453053643</v>
       </c>
       <c r="F52">
-        <v>36026.6515785167</v>
+        <v>36747.18461008703</v>
       </c>
       <c r="G52">
         <v>37342.8</v>
@@ -5557,28 +5557,28 @@
         <v>18497.1</v>
       </c>
       <c r="M52">
-        <v>1812.14057439939</v>
+        <v>1848.383385887378</v>
       </c>
       <c r="N52">
-        <v>16684.95942560061</v>
+        <v>16648.71661411263</v>
       </c>
       <c r="O52">
-        <v>4304.719531804958</v>
+        <v>4295.368886441058</v>
       </c>
       <c r="P52">
-        <v>12380.23989379566</v>
+        <v>12353.34772767157</v>
       </c>
       <c r="Q52">
-        <v>17329.33989379565</v>
+        <v>17302.44772767157</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1224016457171505</v>
+        <v>0.1237334112487263</v>
       </c>
       <c r="T52">
-        <v>1.769091125107402</v>
+        <v>1.799847834843564</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5595,7 +5595,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>10.20732070199941</v>
+        <v>10.00717715882296</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,22 +5603,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07966389751187589</v>
+        <v>0.07946567216517655</v>
       </c>
       <c r="C53">
-        <v>38126.90333182718</v>
+        <v>37627.35660725398</v>
       </c>
       <c r="D53">
-        <v>37531.28794191421</v>
+        <v>37752.27424891134</v>
       </c>
       <c r="E53">
-        <v>2089.681453053643</v>
+        <v>2810.214484623983</v>
       </c>
       <c r="F53">
-        <v>36747.18461008703</v>
+        <v>37467.71764165737</v>
       </c>
       <c r="G53">
         <v>37342.8</v>
@@ -5639,28 +5639,28 @@
         <v>18497.1</v>
       </c>
       <c r="M53">
-        <v>1848.383385887378</v>
+        <v>1884.626197375366</v>
       </c>
       <c r="N53">
-        <v>16648.71661411263</v>
+        <v>16612.47380262464</v>
       </c>
       <c r="O53">
-        <v>4295.368886441058</v>
+        <v>4286.018241077157</v>
       </c>
       <c r="P53">
-        <v>12353.34772767157</v>
+        <v>12326.45556154748</v>
       </c>
       <c r="Q53">
-        <v>17302.44772767157</v>
+        <v>17275.55556154748</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1237334112487263</v>
+        <v>0.1251206670107845</v>
       </c>
       <c r="T53">
-        <v>1.799847834843564</v>
+        <v>1.831886074152067</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5677,7 +5677,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>10.00717715882296</v>
+        <v>9.814731444230206</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,22 +5685,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07946567216517655</v>
+        <v>0.07926744681847721</v>
       </c>
       <c r="C54">
-        <v>37627.35660725398</v>
+        <v>37130.42765556067</v>
       </c>
       <c r="D54">
-        <v>37752.27424891134</v>
+        <v>37975.87832878837</v>
       </c>
       <c r="E54">
-        <v>2810.214484623983</v>
+        <v>3530.747516194315</v>
       </c>
       <c r="F54">
-        <v>37467.71764165737</v>
+        <v>38188.2506732277</v>
       </c>
       <c r="G54">
         <v>37342.8</v>
@@ -5721,28 +5721,28 @@
         <v>18497.1</v>
       </c>
       <c r="M54">
-        <v>1884.626197375366</v>
+        <v>1920.869008863353</v>
       </c>
       <c r="N54">
-        <v>16612.47380262464</v>
+        <v>16576.23099113665</v>
       </c>
       <c r="O54">
-        <v>4286.018241077157</v>
+        <v>4276.667595713256</v>
       </c>
       <c r="P54">
-        <v>12326.45556154748</v>
+        <v>12299.56339542339</v>
       </c>
       <c r="Q54">
-        <v>17275.55556154748</v>
+        <v>17248.66339542339</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1251206670107845</v>
+        <v>0.1265669549329302</v>
       </c>
       <c r="T54">
-        <v>1.831886074152067</v>
+        <v>1.865287642792847</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5759,7 +5759,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.814731444230206</v>
+        <v>9.62954783207492</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,22 +5767,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07926744681847721</v>
+        <v>0.07906922147177788</v>
       </c>
       <c r="C55">
-        <v>37130.42765556067</v>
+        <v>36636.16326854884</v>
       </c>
       <c r="D55">
-        <v>37975.87832878837</v>
+        <v>38202.14697334688</v>
       </c>
       <c r="E55">
-        <v>3530.747516194315</v>
+        <v>4251.280547764647</v>
       </c>
       <c r="F55">
-        <v>38188.2506732277</v>
+        <v>38908.78370479804</v>
       </c>
       <c r="G55">
         <v>37342.8</v>
@@ -5803,28 +5803,28 @@
         <v>18497.1</v>
       </c>
       <c r="M55">
-        <v>1920.869008863353</v>
+        <v>1957.111820351341</v>
       </c>
       <c r="N55">
-        <v>16576.23099113665</v>
+        <v>16539.98817964866</v>
       </c>
       <c r="O55">
-        <v>4276.667595713256</v>
+        <v>4267.316950349355</v>
       </c>
       <c r="P55">
-        <v>12299.56339542339</v>
+        <v>12272.67122929931</v>
       </c>
       <c r="Q55">
-        <v>17248.66339542339</v>
+        <v>17221.77122929931</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1265669549329302</v>
+        <v>0.1280761249386476</v>
       </c>
       <c r="T55">
-        <v>1.865287642792847</v>
+        <v>1.900141453548443</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5841,7 +5841,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>9.62954783207492</v>
+        <v>9.451222872221681</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,22 +5849,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07906922147177788</v>
+        <v>0.07887099612507853</v>
       </c>
       <c r="C56">
-        <v>36636.16326854884</v>
+        <v>36144.61135988784</v>
       </c>
       <c r="D56">
-        <v>38202.14697334688</v>
+        <v>38431.12809625622</v>
       </c>
       <c r="E56">
-        <v>4251.280547764647</v>
+        <v>4971.813579334987</v>
       </c>
       <c r="F56">
-        <v>38908.78370479804</v>
+        <v>39629.31673636838</v>
       </c>
       <c r="G56">
         <v>37342.8</v>
@@ -5885,28 +5885,28 @@
         <v>18497.1</v>
       </c>
       <c r="M56">
-        <v>1957.111820351341</v>
+        <v>1993.354631839329</v>
       </c>
       <c r="N56">
-        <v>16539.98817964866</v>
+        <v>16503.74536816067</v>
       </c>
       <c r="O56">
-        <v>4267.316950349355</v>
+        <v>4257.966304985453</v>
       </c>
       <c r="P56">
-        <v>12272.67122929931</v>
+        <v>12245.77906317522</v>
       </c>
       <c r="Q56">
-        <v>17221.77122929931</v>
+        <v>17194.87906317522</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1280761249386476</v>
+        <v>0.1296523691668412</v>
       </c>
       <c r="T56">
-        <v>1.900141453548443</v>
+        <v>1.936544322559844</v>
       </c>
       <c r="U56">
         <v>0.0503</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>9.451222872221681</v>
+        <v>9.279382456363102</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,22 +5931,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07887099612507853</v>
+        <v>0.0786727707783792</v>
       </c>
       <c r="C57">
-        <v>36144.61135988784</v>
+        <v>35655.82099893953</v>
       </c>
       <c r="D57">
-        <v>38431.12809625622</v>
+        <v>38662.87076687824</v>
       </c>
       <c r="E57">
-        <v>4971.813579334987</v>
+        <v>5692.346610905319</v>
       </c>
       <c r="F57">
-        <v>39629.31673636838</v>
+        <v>40349.84976793871</v>
       </c>
       <c r="G57">
         <v>37342.8</v>
@@ -5967,28 +5967,28 @@
         <v>18497.1</v>
       </c>
       <c r="M57">
-        <v>1993.354631839329</v>
+        <v>2029.597443327317</v>
       </c>
       <c r="N57">
-        <v>16503.74536816067</v>
+        <v>16467.50255667268</v>
       </c>
       <c r="O57">
-        <v>4257.966304985453</v>
+        <v>4248.615659621552</v>
       </c>
       <c r="P57">
-        <v>12245.77906317522</v>
+        <v>12218.88689705113</v>
       </c>
       <c r="Q57">
-        <v>17194.87906317522</v>
+        <v>17167.98689705113</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1296523691668412</v>
+        <v>0.1313002608599527</v>
       </c>
       <c r="T57">
-        <v>1.936544322559844</v>
+        <v>1.974601867435399</v>
       </c>
       <c r="U57">
         <v>0.0503</v>
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>9.279382456363102</v>
+        <v>9.113679198213761</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,22 +6013,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0786727707783792</v>
+        <v>0.07847454543167985</v>
       </c>
       <c r="C58">
-        <v>35655.82099893953</v>
+        <v>35169.84244581424</v>
       </c>
       <c r="D58">
-        <v>38662.87076687824</v>
+        <v>38897.42524532328</v>
       </c>
       <c r="E58">
-        <v>5692.346610905319</v>
+        <v>6412.879642475651</v>
       </c>
       <c r="F58">
-        <v>40349.84976793871</v>
+        <v>41070.38279950904</v>
       </c>
       <c r="G58">
         <v>37342.8</v>
@@ -6049,28 +6049,28 @@
         <v>18497.1</v>
       </c>
       <c r="M58">
-        <v>2029.597443327317</v>
+        <v>2065.840254815304</v>
       </c>
       <c r="N58">
-        <v>16467.50255667268</v>
+        <v>16431.2597451847</v>
       </c>
       <c r="O58">
-        <v>4248.615659621552</v>
+        <v>4239.265014257651</v>
       </c>
       <c r="P58">
-        <v>12218.88689705113</v>
+        <v>12191.99473092704</v>
       </c>
       <c r="Q58">
-        <v>17167.98689705113</v>
+        <v>17141.09473092704</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1313002608599527</v>
+        <v>0.1330247986783253</v>
       </c>
       <c r="T58">
-        <v>1.974601867435399</v>
+        <v>2.014429530677258</v>
       </c>
       <c r="U58">
         <v>0.0503</v>
@@ -6087,7 +6087,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>9.113679198213761</v>
+        <v>8.95379008947317</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,22 +6095,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07847454543167985</v>
+        <v>0.07827632008498052</v>
       </c>
       <c r="C59">
-        <v>35169.84244581424</v>
+        <v>34686.72718771053</v>
       </c>
       <c r="D59">
-        <v>38897.42524532328</v>
+        <v>39134.8430187899</v>
       </c>
       <c r="E59">
-        <v>6412.879642475651</v>
+        <v>7133.412674045991</v>
       </c>
       <c r="F59">
-        <v>41070.38279950904</v>
+        <v>41790.91583107938</v>
       </c>
       <c r="G59">
         <v>37342.8</v>
@@ -6131,28 +6131,28 @@
         <v>18497.1</v>
       </c>
       <c r="M59">
-        <v>2065.840254815304</v>
+        <v>2102.083066303293</v>
       </c>
       <c r="N59">
-        <v>16431.2597451847</v>
+        <v>16395.01693369671</v>
       </c>
       <c r="O59">
-        <v>4239.265014257651</v>
+        <v>4229.914368893751</v>
       </c>
       <c r="P59">
-        <v>12191.99473092704</v>
+        <v>12165.10256480296</v>
       </c>
       <c r="Q59">
-        <v>17141.09473092704</v>
+        <v>17114.20256480296</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1330247986783253</v>
+        <v>0.1348314573451917</v>
       </c>
       <c r="T59">
-        <v>2.014429530677258</v>
+        <v>2.056153749311588</v>
       </c>
       <c r="U59">
         <v>0.0503</v>
@@ -6169,7 +6169,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.95379008947317</v>
+        <v>8.799414398275356</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,22 +6177,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07827632008498052</v>
+        <v>0.07873476473828117</v>
       </c>
       <c r="C60">
-        <v>34686.72718771054</v>
+        <v>33421.44578212583</v>
       </c>
       <c r="D60">
-        <v>39134.8430187899</v>
+        <v>38590.09464477553</v>
       </c>
       <c r="E60">
-        <v>7133.412674045983</v>
+        <v>7853.945705616316</v>
       </c>
       <c r="F60">
-        <v>41790.91583107937</v>
+        <v>42511.4488626497</v>
       </c>
       <c r="G60">
         <v>37342.8</v>
@@ -6213,45 +6213,45 @@
         <v>18497.1</v>
       </c>
       <c r="M60">
-        <v>2102.083066303293</v>
+        <v>2202.093051085255</v>
       </c>
       <c r="N60">
-        <v>16395.01693369671</v>
+        <v>16295.00694891475</v>
       </c>
       <c r="O60">
-        <v>4229.914368893751</v>
+        <v>4204.111792820006</v>
       </c>
       <c r="P60">
-        <v>12165.10256480296</v>
+        <v>12090.89515609474</v>
       </c>
       <c r="Q60">
-        <v>17114.20256480296</v>
+        <v>17039.99515609474</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1348314573451917</v>
+        <v>0.1367262457031248</v>
       </c>
       <c r="T60">
-        <v>2.056153749311588</v>
+        <v>2.099913295684177</v>
       </c>
       <c r="U60">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V60">
         <v>0.258</v>
       </c>
       <c r="W60">
-        <v>0.0373226</v>
+        <v>0.0384356</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y60">
-        <v>8.799414398275356</v>
+        <v>8.39978128575634</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,22 +6259,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07873476473828117</v>
+        <v>0.07854766939158184</v>
       </c>
       <c r="C61">
-        <v>33421.44578212583</v>
+        <v>32921.38728418994</v>
       </c>
       <c r="D61">
-        <v>38590.09464477553</v>
+        <v>38810.56917840998</v>
       </c>
       <c r="E61">
-        <v>7853.945705616316</v>
+        <v>8574.478737186648</v>
       </c>
       <c r="F61">
-        <v>42511.4488626497</v>
+        <v>43231.98189422004</v>
       </c>
       <c r="G61">
         <v>37342.8</v>
@@ -6295,28 +6295,28 @@
         <v>18497.1</v>
       </c>
       <c r="M61">
-        <v>2202.093051085255</v>
+        <v>2239.416662120598</v>
       </c>
       <c r="N61">
-        <v>16295.00694891475</v>
+        <v>16257.6833378794</v>
       </c>
       <c r="O61">
-        <v>4204.111792820006</v>
+        <v>4194.482301172886</v>
       </c>
       <c r="P61">
-        <v>12090.89515609474</v>
+        <v>12063.20103670652</v>
       </c>
       <c r="Q61">
-        <v>17039.99515609474</v>
+        <v>17012.30103670651</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1367262457031248</v>
+        <v>0.1387157734789546</v>
       </c>
       <c r="T61">
-        <v>2.099913295684177</v>
+        <v>2.145860819375395</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.39978128575634</v>
+        <v>8.259784930993735</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,22 +6341,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07854766939158184</v>
+        <v>0.0783605740448825</v>
       </c>
       <c r="C62">
-        <v>32921.38728418994</v>
+        <v>32423.86251058288</v>
       </c>
       <c r="D62">
-        <v>38810.56917840998</v>
+        <v>39033.57743637325</v>
       </c>
       <c r="E62">
-        <v>8574.478737186648</v>
+        <v>9295.011768756987</v>
       </c>
       <c r="F62">
-        <v>43231.98189422004</v>
+        <v>43952.51492579038</v>
       </c>
       <c r="G62">
         <v>37342.8</v>
@@ -6377,28 +6377,28 @@
         <v>18497.1</v>
       </c>
       <c r="M62">
-        <v>2239.416662120598</v>
+        <v>2276.740273155941</v>
       </c>
       <c r="N62">
-        <v>16257.6833378794</v>
+        <v>16220.35972684406</v>
       </c>
       <c r="O62">
-        <v>4194.482301172886</v>
+        <v>4184.852809525768</v>
       </c>
       <c r="P62">
-        <v>12063.20103670652</v>
+        <v>12035.50691731829</v>
       </c>
       <c r="Q62">
-        <v>17012.30103670651</v>
+        <v>16984.60691731829</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1387157734789546</v>
+        <v>0.1408073283202115</v>
       </c>
       <c r="T62">
-        <v>2.145860819375395</v>
+        <v>2.194164626332831</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6415,7 +6415,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>8.259784930993735</v>
+        <v>8.124378620649575</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0783605740448825</v>
+        <v>0.07817347869818317</v>
       </c>
       <c r="C63">
-        <v>32423.86251058288</v>
+        <v>31928.91539059958</v>
       </c>
       <c r="D63">
-        <v>39033.57743637325</v>
+        <v>39259.1633479603</v>
       </c>
       <c r="E63">
-        <v>9295.011768756987</v>
+        <v>10015.54480032732</v>
       </c>
       <c r="F63">
-        <v>43952.51492579038</v>
+        <v>44673.04795736071</v>
       </c>
       <c r="G63">
         <v>37342.8</v>
@@ -6459,28 +6459,28 @@
         <v>18497.1</v>
       </c>
       <c r="M63">
-        <v>2276.740273155941</v>
+        <v>2314.063884191285</v>
       </c>
       <c r="N63">
-        <v>16220.35972684406</v>
+        <v>16183.03611580872</v>
       </c>
       <c r="O63">
-        <v>4184.852809525768</v>
+        <v>4175.223317878649</v>
       </c>
       <c r="P63">
-        <v>12035.50691731829</v>
+        <v>12007.81279793007</v>
       </c>
       <c r="Q63">
-        <v>16984.60691731829</v>
+        <v>16956.91279793007</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1408073283202115</v>
+        <v>0.1430089649952188</v>
       </c>
       <c r="T63">
-        <v>2.194164626332831</v>
+        <v>2.245010738919605</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6497,7 +6497,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>8.124378620649575</v>
+        <v>7.993340255800388</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,22 +6505,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07817347869818317</v>
+        <v>0.07798638335148383</v>
       </c>
       <c r="C64">
-        <v>31928.91539059958</v>
+        <v>31436.59087495665</v>
       </c>
       <c r="D64">
-        <v>39259.1633479603</v>
+        <v>39487.37186388769</v>
       </c>
       <c r="E64">
-        <v>10015.54480032732</v>
+        <v>10736.07783189765</v>
       </c>
       <c r="F64">
-        <v>44673.04795736071</v>
+        <v>45393.58098893104</v>
       </c>
       <c r="G64">
         <v>37342.8</v>
@@ -6541,28 +6541,28 @@
         <v>18497.1</v>
       </c>
       <c r="M64">
-        <v>2314.063884191285</v>
+        <v>2351.387495226628</v>
       </c>
       <c r="N64">
-        <v>16183.03611580872</v>
+        <v>16145.71250477338</v>
       </c>
       <c r="O64">
-        <v>4175.223317878649</v>
+        <v>4165.593826231531</v>
       </c>
       <c r="P64">
-        <v>12007.81279793007</v>
+        <v>11980.11867854184</v>
       </c>
       <c r="Q64">
-        <v>16956.91279793007</v>
+        <v>16929.21867854184</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1430089649952188</v>
+        <v>0.1453296090580644</v>
       </c>
       <c r="T64">
-        <v>2.245010738919605</v>
+        <v>2.298605290024583</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>7.993340255800388</v>
+        <v>7.866461839041652</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,22 +6587,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07798638335148383</v>
+        <v>0.07779928800478449</v>
       </c>
       <c r="C65">
-        <v>31436.59087495665</v>
+        <v>30946.93496565277</v>
       </c>
       <c r="D65">
-        <v>39487.37186388769</v>
+        <v>39718.24898615415</v>
       </c>
       <c r="E65">
-        <v>10736.07783189765</v>
+        <v>11456.61086346798</v>
       </c>
       <c r="F65">
-        <v>45393.58098893104</v>
+        <v>46114.11402050137</v>
       </c>
       <c r="G65">
         <v>37342.8</v>
@@ -6623,28 +6623,28 @@
         <v>18497.1</v>
       </c>
       <c r="M65">
-        <v>2351.387495226628</v>
+        <v>2388.711106261971</v>
       </c>
       <c r="N65">
-        <v>16145.71250477338</v>
+        <v>16108.38889373803</v>
       </c>
       <c r="O65">
-        <v>4165.593826231531</v>
+        <v>4155.964334584412</v>
       </c>
       <c r="P65">
-        <v>11980.11867854184</v>
+        <v>11952.42455915362</v>
       </c>
       <c r="Q65">
-        <v>16929.21867854184</v>
+        <v>16901.52455915361</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1453296090580644</v>
+        <v>0.147779177791068</v>
       </c>
       <c r="T65">
-        <v>2.298605290024583</v>
+        <v>2.355177316190948</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6661,7 +6661,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.866461839041652</v>
+        <v>7.743548372806626</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,22 +6669,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07779928800478449</v>
+        <v>0.07761219265808514</v>
       </c>
       <c r="C66">
-        <v>30946.93496565277</v>
+        <v>30459.99474688301</v>
       </c>
       <c r="D66">
-        <v>39718.24898615415</v>
+        <v>39951.84179895472</v>
       </c>
       <c r="E66">
-        <v>11456.61086346798</v>
+        <v>12177.14389503832</v>
       </c>
       <c r="F66">
-        <v>46114.11402050137</v>
+        <v>46834.64705207171</v>
       </c>
       <c r="G66">
         <v>37342.8</v>
@@ -6705,28 +6705,28 @@
         <v>18497.1</v>
       </c>
       <c r="M66">
-        <v>2388.711106261971</v>
+        <v>2426.034717297315</v>
       </c>
       <c r="N66">
-        <v>16108.38889373803</v>
+        <v>16071.06528270269</v>
       </c>
       <c r="O66">
-        <v>4155.964334584412</v>
+        <v>4146.334842937294</v>
       </c>
       <c r="P66">
-        <v>11952.42455915362</v>
+        <v>11924.73043976539</v>
       </c>
       <c r="Q66">
-        <v>16901.52455915361</v>
+        <v>16873.83043976539</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.147779177791068</v>
+        <v>0.1503687218802433</v>
       </c>
       <c r="T66">
-        <v>2.355177316190948</v>
+        <v>2.41498202956682</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6743,7 +6743,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.743548372806626</v>
+        <v>7.624416859378831</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,22 +6751,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07761219265808514</v>
+        <v>0.0774250973113858</v>
       </c>
       <c r="C67">
-        <v>30459.99474688301</v>
+        <v>29975.81841705035</v>
       </c>
       <c r="D67">
-        <v>39951.84179895472</v>
+        <v>40188.19850069239</v>
       </c>
       <c r="E67">
-        <v>12177.14389503832</v>
+        <v>12897.67692660866</v>
       </c>
       <c r="F67">
-        <v>46834.64705207171</v>
+        <v>47555.18008364204</v>
       </c>
       <c r="G67">
         <v>37342.8</v>
@@ -6787,28 +6787,28 @@
         <v>18497.1</v>
       </c>
       <c r="M67">
-        <v>2426.034717297315</v>
+        <v>2463.358328332658</v>
       </c>
       <c r="N67">
-        <v>16071.06528270269</v>
+        <v>16033.74167166734</v>
       </c>
       <c r="O67">
-        <v>4146.334842937294</v>
+        <v>4136.705351290175</v>
       </c>
       <c r="P67">
-        <v>11924.73043976539</v>
+        <v>11897.03632037717</v>
       </c>
       <c r="Q67">
-        <v>16873.83043976539</v>
+        <v>16846.13632037717</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1503687218802433</v>
+        <v>0.1531105920923112</v>
       </c>
       <c r="T67">
-        <v>2.41498202956682</v>
+        <v>2.47830466725892</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6825,7 +6825,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.624416859378831</v>
+        <v>7.508895391812485</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,22 +6833,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0774250973113858</v>
+        <v>0.07723800196468647</v>
       </c>
       <c r="C68">
-        <v>29975.81841705035</v>
+        <v>29494.45532192047</v>
       </c>
       <c r="D68">
-        <v>40188.19850069239</v>
+        <v>40427.36843713283</v>
       </c>
       <c r="E68">
-        <v>12897.67692660866</v>
+        <v>13618.20995817899</v>
       </c>
       <c r="F68">
-        <v>47555.18008364204</v>
+        <v>48275.71311521238</v>
       </c>
       <c r="G68">
         <v>37342.8</v>
@@ -6869,28 +6869,28 @@
         <v>18497.1</v>
       </c>
       <c r="M68">
-        <v>2463.358328332658</v>
+        <v>2500.681939368001</v>
       </c>
       <c r="N68">
-        <v>16033.74167166734</v>
+        <v>15996.418060632</v>
       </c>
       <c r="O68">
-        <v>4136.705351290175</v>
+        <v>4127.075859643056</v>
       </c>
       <c r="P68">
-        <v>11897.03632037717</v>
+        <v>11869.34220098894</v>
       </c>
       <c r="Q68">
-        <v>16846.13632037717</v>
+        <v>16818.44220098894</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1531105920923112</v>
+        <v>0.1560186362566257</v>
       </c>
       <c r="T68">
-        <v>2.47830466725892</v>
+        <v>2.545465040568724</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6907,7 +6907,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.508895391812485</v>
+        <v>7.396822326263045</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,22 +6915,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07723800196468647</v>
+        <v>0.07705090661798714</v>
       </c>
       <c r="C69">
-        <v>29494.45532192047</v>
+        <v>29015.95598896717</v>
       </c>
       <c r="D69">
-        <v>40427.36843713283</v>
+        <v>40669.40213574988</v>
       </c>
       <c r="E69">
-        <v>13618.20995817899</v>
+        <v>14338.74298974933</v>
       </c>
       <c r="F69">
-        <v>48275.71311521238</v>
+        <v>48996.24614678272</v>
       </c>
       <c r="G69">
         <v>37342.8</v>
@@ -6951,28 +6951,28 @@
         <v>18497.1</v>
       </c>
       <c r="M69">
-        <v>2500.681939368001</v>
+        <v>2538.005550403345</v>
       </c>
       <c r="N69">
-        <v>15996.418060632</v>
+        <v>15959.09444959666</v>
       </c>
       <c r="O69">
-        <v>4127.075859643056</v>
+        <v>4117.446367995938</v>
       </c>
       <c r="P69">
-        <v>11869.34220098894</v>
+        <v>11841.64808160072</v>
       </c>
       <c r="Q69">
-        <v>16818.44220098894</v>
+        <v>16790.74808160072</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1560186362566257</v>
+        <v>0.1591084331812098</v>
       </c>
       <c r="T69">
-        <v>2.545465040568724</v>
+        <v>2.616822937210389</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6989,7 +6989,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>7.396822326263045</v>
+        <v>7.288045527347411</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,22 +6997,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07705090661798714</v>
+        <v>0.0768638112712878</v>
       </c>
       <c r="C70">
-        <v>29015.95598896717</v>
+        <v>28540.37216295925</v>
       </c>
       <c r="D70">
-        <v>40669.40213574988</v>
+        <v>40914.3513413123</v>
       </c>
       <c r="E70">
-        <v>14338.74298974933</v>
+        <v>15059.27602131966</v>
       </c>
       <c r="F70">
-        <v>48996.24614678272</v>
+        <v>49716.77917835305</v>
       </c>
       <c r="G70">
         <v>37342.8</v>
@@ -7033,28 +7033,28 @@
         <v>18497.1</v>
       </c>
       <c r="M70">
-        <v>2538.005550403345</v>
+        <v>2575.329161438688</v>
       </c>
       <c r="N70">
-        <v>15959.09444959666</v>
+        <v>15921.77083856132</v>
       </c>
       <c r="O70">
-        <v>4117.446367995938</v>
+        <v>4107.816876348819</v>
       </c>
       <c r="P70">
-        <v>11841.64808160072</v>
+        <v>11813.9539622125</v>
       </c>
       <c r="Q70">
-        <v>16790.74808160072</v>
+        <v>16763.05396221249</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1591084331812098</v>
+        <v>0.1623975718428639</v>
       </c>
       <c r="T70">
-        <v>2.616822937210389</v>
+        <v>2.692784569119259</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>7.288045527347411</v>
+        <v>7.182421679124985</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,22 +7079,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.0768638112712878</v>
+        <v>0.07667671592458845</v>
       </c>
       <c r="C71">
-        <v>28540.37216295925</v>
+        <v>28067.75684284107</v>
       </c>
       <c r="D71">
-        <v>40914.3513413123</v>
+        <v>41162.26905276444</v>
       </c>
       <c r="E71">
-        <v>15059.27602131966</v>
+        <v>15779.80905288999</v>
       </c>
       <c r="F71">
-        <v>49716.77917835305</v>
+        <v>50437.31220992338</v>
       </c>
       <c r="G71">
         <v>37342.8</v>
@@ -7115,28 +7115,28 @@
         <v>18497.1</v>
       </c>
       <c r="M71">
-        <v>2575.329161438688</v>
+        <v>2612.652772474031</v>
       </c>
       <c r="N71">
-        <v>15921.77083856132</v>
+        <v>15884.44722752597</v>
       </c>
       <c r="O71">
-        <v>4107.816876348819</v>
+        <v>4098.1873847017</v>
       </c>
       <c r="P71">
-        <v>11813.9539622125</v>
+        <v>11786.25984282427</v>
       </c>
       <c r="Q71">
-        <v>16763.05396221249</v>
+        <v>16735.35984282427</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1623975718428639</v>
+        <v>0.1659059864152949</v>
       </c>
       <c r="T71">
-        <v>2.692784569119259</v>
+        <v>2.773810309822053</v>
       </c>
       <c r="U71">
         <v>0.0518</v>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>7.182421679124985</v>
+        <v>7.079815655137486</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,22 +7161,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07667671592458845</v>
+        <v>0.07648962057788912</v>
       </c>
       <c r="C72">
-        <v>28067.75684284107</v>
+        <v>27598.164319962</v>
       </c>
       <c r="D72">
-        <v>41162.26905276444</v>
+        <v>41413.20956145573</v>
       </c>
       <c r="E72">
-        <v>15779.80905288999</v>
+        <v>16500.34208446033</v>
       </c>
       <c r="F72">
-        <v>50437.31220992338</v>
+        <v>51157.84524149372</v>
       </c>
       <c r="G72">
         <v>37342.8</v>
@@ -7197,28 +7197,28 @@
         <v>18497.1</v>
       </c>
       <c r="M72">
-        <v>2612.652772474031</v>
+        <v>2649.976383509375</v>
       </c>
       <c r="N72">
-        <v>15884.44722752597</v>
+        <v>15847.12361649063</v>
       </c>
       <c r="O72">
-        <v>4098.1873847017</v>
+        <v>4088.557893054582</v>
       </c>
       <c r="P72">
-        <v>11786.25984282427</v>
+        <v>11758.56572343605</v>
       </c>
       <c r="Q72">
-        <v>16735.35984282427</v>
+        <v>16707.66572343605</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1659059864152949</v>
+        <v>0.1696563606134108</v>
       </c>
       <c r="T72">
-        <v>2.773810309822053</v>
+        <v>2.860424032642282</v>
       </c>
       <c r="U72">
         <v>0.0518</v>
@@ -7235,7 +7235,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>7.079815655137486</v>
+        <v>6.980099941684846</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,22 +7243,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07648962057788912</v>
+        <v>0.07630252523118977</v>
       </c>
       <c r="C73">
-        <v>27598.16431996201</v>
+        <v>27131.65021771333</v>
       </c>
       <c r="D73">
-        <v>41413.20956145573</v>
+        <v>41667.22849077737</v>
       </c>
       <c r="E73">
-        <v>16500.34208446032</v>
+        <v>17220.87511603066</v>
       </c>
       <c r="F73">
-        <v>51157.84524149371</v>
+        <v>51878.37827306405</v>
       </c>
       <c r="G73">
         <v>37342.8</v>
@@ -7279,28 +7279,28 @@
         <v>18497.1</v>
       </c>
       <c r="M73">
-        <v>2649.976383509374</v>
+        <v>2687.299994544717</v>
       </c>
       <c r="N73">
-        <v>15847.12361649063</v>
+        <v>15809.80000545528</v>
       </c>
       <c r="O73">
-        <v>4088.557893054582</v>
+        <v>4078.928401407464</v>
       </c>
       <c r="P73">
-        <v>11758.56572343605</v>
+        <v>11730.87160404782</v>
       </c>
       <c r="Q73">
-        <v>16707.66572343605</v>
+        <v>16679.97160404782</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1696563606134107</v>
+        <v>0.1736746186828206</v>
       </c>
       <c r="T73">
-        <v>2.860424032642281</v>
+        <v>2.953224449949669</v>
       </c>
       <c r="U73">
         <v>0.0518</v>
@@ -7317,7 +7317,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.980099941684847</v>
+        <v>6.883154109161446</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,22 +7325,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07630252523118977</v>
+        <v>0.07611542988449044</v>
       </c>
       <c r="C74">
-        <v>27131.65021771333</v>
+        <v>26668.2715326321</v>
       </c>
       <c r="D74">
-        <v>41667.22849077737</v>
+        <v>41924.38283726647</v>
       </c>
       <c r="E74">
-        <v>17220.87511603066</v>
+        <v>17941.40814760099</v>
       </c>
       <c r="F74">
-        <v>51878.37827306405</v>
+        <v>52598.91130463438</v>
       </c>
       <c r="G74">
         <v>37342.8</v>
@@ -7361,28 +7361,28 @@
         <v>18497.1</v>
       </c>
       <c r="M74">
-        <v>2687.299994544717</v>
+        <v>2724.62360558006</v>
       </c>
       <c r="N74">
-        <v>15809.80000545528</v>
+        <v>15772.47639441994</v>
       </c>
       <c r="O74">
-        <v>4078.928401407464</v>
+        <v>4069.298909760345</v>
       </c>
       <c r="P74">
-        <v>11730.87160404782</v>
+        <v>11703.1774846596</v>
       </c>
       <c r="Q74">
-        <v>16679.97160404782</v>
+        <v>16652.27748465959</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1736746186828206</v>
+        <v>0.1779905254981127</v>
       </c>
       <c r="T74">
-        <v>2.953224449949669</v>
+        <v>3.052898972242789</v>
       </c>
       <c r="U74">
         <v>0.0518</v>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.883154109161446</v>
+        <v>6.788864326844166</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,22 +7407,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07611542988449044</v>
+        <v>0.07686177053779109</v>
       </c>
       <c r="C75">
-        <v>26668.2715326321</v>
+        <v>24940.39504528795</v>
       </c>
       <c r="D75">
-        <v>41924.38283726647</v>
+        <v>40917.03938149266</v>
       </c>
       <c r="E75">
-        <v>17941.40814760099</v>
+        <v>18661.94117917133</v>
       </c>
       <c r="F75">
-        <v>52598.91130463438</v>
+        <v>53319.44433620472</v>
       </c>
       <c r="G75">
         <v>37342.8</v>
@@ -7443,45 +7443,45 @@
         <v>18497.1</v>
       </c>
       <c r="M75">
-        <v>2724.62360558006</v>
+        <v>2852.590271986952</v>
       </c>
       <c r="N75">
-        <v>15772.47639441994</v>
+        <v>15644.50972801305</v>
       </c>
       <c r="O75">
-        <v>4069.298909760345</v>
+        <v>4036.283509827367</v>
       </c>
       <c r="P75">
-        <v>11703.1774846596</v>
+        <v>11608.22621818568</v>
       </c>
       <c r="Q75">
-        <v>16652.27748465959</v>
+        <v>16557.32621818568</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1779905254981127</v>
+        <v>0.1826384251453504</v>
       </c>
       <c r="T75">
-        <v>3.052898972242789</v>
+        <v>3.160240765481534</v>
       </c>
       <c r="U75">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V75">
         <v>0.258</v>
       </c>
       <c r="W75">
-        <v>0.0384356</v>
+        <v>0.039697</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y75">
-        <v>6.788864326844166</v>
+        <v>6.484317142088539</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,22 +7489,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07686177053779109</v>
+        <v>0.07668728919109176</v>
       </c>
       <c r="C76">
-        <v>24940.39504528795</v>
+        <v>24451.00111077671</v>
       </c>
       <c r="D76">
-        <v>40917.03938149266</v>
+        <v>41148.17847855174</v>
       </c>
       <c r="E76">
-        <v>18661.94117917133</v>
+        <v>19382.47421074166</v>
       </c>
       <c r="F76">
-        <v>53319.44433620472</v>
+        <v>54039.97736777505</v>
       </c>
       <c r="G76">
         <v>37342.8</v>
@@ -7525,28 +7525,28 @@
         <v>18497.1</v>
       </c>
       <c r="M76">
-        <v>2852.590271986952</v>
+        <v>2891.138789175965</v>
       </c>
       <c r="N76">
-        <v>15644.50972801305</v>
+        <v>15605.96121082404</v>
       </c>
       <c r="O76">
-        <v>4036.283509827367</v>
+        <v>4026.337992392601</v>
       </c>
       <c r="P76">
-        <v>11608.22621818568</v>
+        <v>11579.62321843144</v>
       </c>
       <c r="Q76">
-        <v>16557.32621818568</v>
+        <v>16528.72321843143</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1826384251453504</v>
+        <v>0.1876581567643671</v>
       </c>
       <c r="T76">
-        <v>3.160240765481534</v>
+        <v>3.276169902179379</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7563,7 +7563,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.484317142088539</v>
+        <v>6.397859580194025</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,22 +7571,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07668728919109176</v>
+        <v>0.07651280784439242</v>
       </c>
       <c r="C77">
-        <v>24451.00111077671</v>
+        <v>23964.23340706366</v>
       </c>
       <c r="D77">
-        <v>41148.17847855174</v>
+        <v>41381.94380640904</v>
       </c>
       <c r="E77">
-        <v>19382.47421074166</v>
+        <v>20103.00724231199</v>
       </c>
       <c r="F77">
-        <v>54039.97736777505</v>
+        <v>54760.51039934538</v>
       </c>
       <c r="G77">
         <v>37342.8</v>
@@ -7607,28 +7607,28 @@
         <v>18497.1</v>
       </c>
       <c r="M77">
-        <v>2891.138789175965</v>
+        <v>2929.687306364978</v>
       </c>
       <c r="N77">
-        <v>15605.96121082404</v>
+        <v>15567.41269363502</v>
       </c>
       <c r="O77">
-        <v>4026.337992392601</v>
+        <v>4016.392474957836</v>
       </c>
       <c r="P77">
-        <v>11579.62321843144</v>
+        <v>11551.02021867719</v>
       </c>
       <c r="Q77">
-        <v>16528.72321843143</v>
+        <v>16500.12021867718</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1876581567643671</v>
+        <v>0.1930961993516351</v>
       </c>
       <c r="T77">
-        <v>3.276169902179379</v>
+        <v>3.40175980026871</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.397859580194025</v>
+        <v>6.313677217296735</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,22 +7653,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07651280784439242</v>
+        <v>0.07633832649769308</v>
       </c>
       <c r="C78">
-        <v>23964.23340706366</v>
+        <v>23480.1369492173</v>
       </c>
       <c r="D78">
-        <v>41381.94380640904</v>
+        <v>41618.38038013302</v>
       </c>
       <c r="E78">
-        <v>20103.00724231199</v>
+        <v>20823.54027388233</v>
       </c>
       <c r="F78">
-        <v>54760.51039934538</v>
+        <v>55481.04343091572</v>
       </c>
       <c r="G78">
         <v>37342.8</v>
@@ -7689,28 +7689,28 @@
         <v>18497.1</v>
       </c>
       <c r="M78">
-        <v>2929.687306364978</v>
+        <v>2968.235823553991</v>
       </c>
       <c r="N78">
-        <v>15567.41269363502</v>
+        <v>15528.86417644601</v>
       </c>
       <c r="O78">
-        <v>4016.392474957836</v>
+        <v>4006.446957523071</v>
       </c>
       <c r="P78">
-        <v>11551.02021867719</v>
+        <v>11522.41721892294</v>
       </c>
       <c r="Q78">
-        <v>16500.12021867718</v>
+        <v>16471.51721892294</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1930961993516351</v>
+        <v>0.1990071152073612</v>
       </c>
       <c r="T78">
-        <v>3.40175980026871</v>
+        <v>3.538270559061461</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7727,7 +7727,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>6.313677217296735</v>
+        <v>6.231681409279894</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,22 +7735,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07633832649769308</v>
+        <v>0.07616384515099374</v>
       </c>
       <c r="C79">
-        <v>23480.1369492173</v>
+        <v>22998.75778699588</v>
       </c>
       <c r="D79">
-        <v>41618.38038013302</v>
+        <v>41857.53424948193</v>
       </c>
       <c r="E79">
-        <v>20823.54027388233</v>
+        <v>21544.07330545266</v>
       </c>
       <c r="F79">
-        <v>55481.04343091572</v>
+        <v>56201.57646248605</v>
       </c>
       <c r="G79">
         <v>37342.8</v>
@@ -7771,28 +7771,28 @@
         <v>18497.1</v>
       </c>
       <c r="M79">
-        <v>2968.235823553991</v>
+        <v>3006.784340743004</v>
       </c>
       <c r="N79">
-        <v>15528.86417644601</v>
+        <v>15490.315659257</v>
       </c>
       <c r="O79">
-        <v>4006.446957523071</v>
+        <v>3996.501440088306</v>
       </c>
       <c r="P79">
-        <v>11522.41721892294</v>
+        <v>11493.81421916869</v>
       </c>
       <c r="Q79">
-        <v>16471.51721892294</v>
+        <v>16442.91421916869</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1990071152073612</v>
+        <v>0.2054553870499716</v>
       </c>
       <c r="T79">
-        <v>3.538270559061461</v>
+        <v>3.687191386835373</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>6.231681409279894</v>
+        <v>6.15178805787887</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,22 +7817,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07616384515099374</v>
+        <v>0.07598936380429441</v>
       </c>
       <c r="C80">
-        <v>22998.75778699588</v>
+        <v>22520.14303474761</v>
       </c>
       <c r="D80">
-        <v>41857.53424948193</v>
+        <v>42099.45252880399</v>
       </c>
       <c r="E80">
-        <v>21544.07330545266</v>
+        <v>22264.606337023</v>
       </c>
       <c r="F80">
-        <v>56201.57646248605</v>
+        <v>56922.10949405639</v>
       </c>
       <c r="G80">
         <v>37342.8</v>
@@ -7853,28 +7853,28 @@
         <v>18497.1</v>
       </c>
       <c r="M80">
-        <v>3006.784340743004</v>
+        <v>3045.332857932016</v>
       </c>
       <c r="N80">
-        <v>15490.315659257</v>
+        <v>15451.76714206799</v>
       </c>
       <c r="O80">
-        <v>3996.501440088306</v>
+        <v>3986.55592265354</v>
       </c>
       <c r="P80">
-        <v>11493.81421916869</v>
+        <v>11465.21121941444</v>
       </c>
       <c r="Q80">
-        <v>16442.91421916869</v>
+        <v>16414.31121941444</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2054553870499716</v>
+        <v>0.2125177800204496</v>
       </c>
       <c r="T80">
-        <v>3.687191386835373</v>
+        <v>3.850295150587752</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>6.15178805787887</v>
+        <v>6.073917322969011</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,22 +7899,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07598936380429441</v>
+        <v>0.07581488245759507</v>
       </c>
       <c r="C81">
-        <v>22520.14303474761</v>
+        <v>22044.34090235399</v>
       </c>
       <c r="D81">
-        <v>42099.45252880399</v>
+        <v>42344.18342798071</v>
       </c>
       <c r="E81">
-        <v>22264.606337023</v>
+        <v>22985.13936859334</v>
       </c>
       <c r="F81">
-        <v>56922.10949405639</v>
+        <v>57642.64252562672</v>
       </c>
       <c r="G81">
         <v>37342.8</v>
@@ -7935,28 +7935,28 @@
         <v>18497.1</v>
       </c>
       <c r="M81">
-        <v>3045.332857932016</v>
+        <v>3083.88137512103</v>
       </c>
       <c r="N81">
-        <v>15451.76714206799</v>
+        <v>15413.21862487897</v>
       </c>
       <c r="O81">
-        <v>3986.55592265354</v>
+        <v>3976.610405218775</v>
       </c>
       <c r="P81">
-        <v>11465.21121941444</v>
+        <v>11436.6082196602</v>
       </c>
       <c r="Q81">
-        <v>16414.31121941444</v>
+        <v>16385.7082196602</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2125177800204496</v>
+        <v>0.2202864122879754</v>
       </c>
       <c r="T81">
-        <v>3.850295150587752</v>
+        <v>4.029709290715368</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7973,7 +7973,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>6.073917322969011</v>
+        <v>5.997993356431898</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,22 +7981,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07581488245759507</v>
+        <v>0.07564040111089573</v>
       </c>
       <c r="C82">
-        <v>22044.34090235399</v>
+        <v>21571.40072725837</v>
       </c>
       <c r="D82">
-        <v>42344.18342798071</v>
+        <v>42591.77628445542</v>
       </c>
       <c r="E82">
-        <v>22985.13936859334</v>
+        <v>23705.67240016367</v>
       </c>
       <c r="F82">
-        <v>57642.64252562672</v>
+        <v>58363.17555719706</v>
       </c>
       <c r="G82">
         <v>37342.8</v>
@@ -8017,28 +8017,28 @@
         <v>18497.1</v>
       </c>
       <c r="M82">
-        <v>3083.88137512103</v>
+        <v>3122.429892310042</v>
       </c>
       <c r="N82">
-        <v>15413.21862487897</v>
+        <v>15374.67010768996</v>
       </c>
       <c r="O82">
-        <v>3976.610405218775</v>
+        <v>3966.664887784009</v>
       </c>
       <c r="P82">
-        <v>11436.6082196602</v>
+        <v>11408.00521990595</v>
       </c>
       <c r="Q82">
-        <v>16385.7082196602</v>
+        <v>16357.10521990595</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2202864122879754</v>
+        <v>0.2288727953205039</v>
       </c>
       <c r="T82">
-        <v>4.029709290715368</v>
+        <v>4.228009129803787</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.997993356431898</v>
+        <v>5.923944055735208</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,22 +8063,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07564040111089573</v>
+        <v>0.07546591976419638</v>
       </c>
       <c r="C83">
-        <v>21571.40072725837</v>
+        <v>21101.37300762508</v>
       </c>
       <c r="D83">
-        <v>42591.77628445542</v>
+        <v>42842.28159639246</v>
       </c>
       <c r="E83">
-        <v>23705.67240016367</v>
+        <v>24426.205431734</v>
       </c>
       <c r="F83">
-        <v>58363.17555719706</v>
+        <v>59083.70858876739</v>
       </c>
       <c r="G83">
         <v>37342.8</v>
@@ -8099,28 +8099,28 @@
         <v>18497.1</v>
       </c>
       <c r="M83">
-        <v>3122.429892310042</v>
+        <v>3160.978409499055</v>
       </c>
       <c r="N83">
-        <v>15374.67010768996</v>
+        <v>15336.12159050095</v>
       </c>
       <c r="O83">
-        <v>3966.664887784009</v>
+        <v>3956.719370349244</v>
       </c>
       <c r="P83">
-        <v>11408.00521990595</v>
+        <v>11379.4022201517</v>
       </c>
       <c r="Q83">
-        <v>16357.10521990595</v>
+        <v>16328.5022201517</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2288727953205039</v>
+        <v>0.2384132209122022</v>
       </c>
       <c r="T83">
-        <v>4.228009129803787</v>
+        <v>4.448342284346473</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8137,7 +8137,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.923944055735208</v>
+        <v>5.851700835543315</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,22 +8145,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07546591976419638</v>
+        <v>0.07529143841749705</v>
       </c>
       <c r="C84">
-        <v>21101.37300762508</v>
+        <v>20634.3094366754</v>
       </c>
       <c r="D84">
-        <v>42842.28159639246</v>
+        <v>43095.75105701313</v>
       </c>
       <c r="E84">
-        <v>24426.205431734</v>
+        <v>25146.73846330434</v>
       </c>
       <c r="F84">
-        <v>59083.70858876739</v>
+        <v>59804.24162033773</v>
       </c>
       <c r="G84">
         <v>37342.8</v>
@@ -8181,28 +8181,28 @@
         <v>18497.1</v>
       </c>
       <c r="M84">
-        <v>3160.978409499055</v>
+        <v>3199.526926688068</v>
       </c>
       <c r="N84">
-        <v>15336.12159050095</v>
+        <v>15297.57307331193</v>
       </c>
       <c r="O84">
-        <v>3956.719370349244</v>
+        <v>3946.773852914479</v>
       </c>
       <c r="P84">
-        <v>11379.4022201517</v>
+        <v>11350.79922039746</v>
       </c>
       <c r="Q84">
-        <v>16328.5022201517</v>
+        <v>16299.89922039745</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2384132209122022</v>
+        <v>0.2490760495146886</v>
       </c>
       <c r="T84">
-        <v>4.448342284346473</v>
+        <v>4.694596986482417</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8219,7 +8219,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.851700835543315</v>
+        <v>5.781198415837975</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,22 +8227,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07529143841749705</v>
+        <v>0.0751169570707977</v>
       </c>
       <c r="C85">
-        <v>20634.3094366754</v>
+        <v>20170.26293824999</v>
       </c>
       <c r="D85">
-        <v>43095.75105701313</v>
+        <v>43352.23759015805</v>
       </c>
       <c r="E85">
-        <v>25146.73846330434</v>
+        <v>25867.27149487467</v>
       </c>
       <c r="F85">
-        <v>59804.24162033773</v>
+        <v>60524.77465190806</v>
       </c>
       <c r="G85">
         <v>37342.8</v>
@@ -8263,28 +8263,28 @@
         <v>18497.1</v>
       </c>
       <c r="M85">
-        <v>3199.526926688068</v>
+        <v>3238.075443877081</v>
       </c>
       <c r="N85">
-        <v>15297.57307331193</v>
+        <v>15259.02455612292</v>
       </c>
       <c r="O85">
-        <v>3946.773852914479</v>
+        <v>3936.828335479714</v>
       </c>
       <c r="P85">
-        <v>11350.79922039746</v>
+        <v>11322.19622064321</v>
       </c>
       <c r="Q85">
-        <v>16299.89922039745</v>
+        <v>16271.29622064321</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2490760495146886</v>
+        <v>0.2610717316924858</v>
       </c>
       <c r="T85">
-        <v>4.694596986482417</v>
+        <v>4.971633526385355</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8301,7 +8301,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.781198415837975</v>
+        <v>5.712374625173235</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,22 +8309,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07511695707079771</v>
+        <v>0.07494247572409837</v>
       </c>
       <c r="C86">
-        <v>20170.26293824999</v>
+        <v>19709.28770364834</v>
       </c>
       <c r="D86">
-        <v>43352.23759015804</v>
+        <v>43611.79538712672</v>
       </c>
       <c r="E86">
-        <v>25867.27149487467</v>
+        <v>26587.804526445</v>
       </c>
       <c r="F86">
-        <v>60524.77465190805</v>
+        <v>61245.30768347839</v>
       </c>
       <c r="G86">
         <v>37342.8</v>
@@ -8345,28 +8345,28 @@
         <v>18497.1</v>
       </c>
       <c r="M86">
-        <v>3238.075443877081</v>
+        <v>3276.623961066094</v>
       </c>
       <c r="N86">
-        <v>15259.02455612292</v>
+        <v>15220.47603893391</v>
       </c>
       <c r="O86">
-        <v>3936.828335479714</v>
+        <v>3926.882818044948</v>
       </c>
       <c r="P86">
-        <v>11322.19622064321</v>
+        <v>11293.59322088896</v>
       </c>
       <c r="Q86">
-        <v>16271.29622064321</v>
+        <v>16242.69322088896</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2610717316924857</v>
+        <v>0.2746668381606558</v>
       </c>
       <c r="T86">
-        <v>4.971633526385352</v>
+        <v>5.285608271608681</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8383,7 +8383,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.712374625173236</v>
+        <v>5.645170217818258</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,22 +8391,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07494247572409837</v>
+        <v>0.07527849037739903</v>
       </c>
       <c r="C87">
-        <v>19709.28770364834</v>
+        <v>18491.63958513787</v>
       </c>
       <c r="D87">
-        <v>43611.79538712672</v>
+        <v>43114.68030018659</v>
       </c>
       <c r="E87">
-        <v>26587.804526445</v>
+        <v>27308.33755801534</v>
       </c>
       <c r="F87">
-        <v>61245.30768347839</v>
+        <v>61965.84071504873</v>
       </c>
       <c r="G87">
         <v>37342.8</v>
@@ -8427,45 +8427,45 @@
         <v>18497.1</v>
       </c>
       <c r="M87">
-        <v>3276.623961066094</v>
+        <v>3364.745150827146</v>
       </c>
       <c r="N87">
-        <v>15220.47603893391</v>
+        <v>15132.35484917286</v>
       </c>
       <c r="O87">
-        <v>3926.882818044948</v>
+        <v>3904.147551086597</v>
       </c>
       <c r="P87">
-        <v>11293.59322088896</v>
+        <v>11228.20729808626</v>
       </c>
       <c r="Q87">
-        <v>16242.69322088896</v>
+        <v>16177.30729808626</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2746668381606558</v>
+        <v>0.2902041026957073</v>
       </c>
       <c r="T87">
-        <v>5.285608271608681</v>
+        <v>5.644436551863913</v>
       </c>
       <c r="U87">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V87">
         <v>0.258</v>
       </c>
       <c r="W87">
-        <v>0.039697</v>
+        <v>0.0402906</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y87">
-        <v>5.645170217818258</v>
+        <v>5.49732570249872</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,22 +8473,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07527849037739903</v>
+        <v>0.0751099450306997</v>
       </c>
       <c r="C88">
-        <v>18491.63958513787</v>
+        <v>18019.03532762065</v>
       </c>
       <c r="D88">
-        <v>43114.68030018659</v>
+        <v>43362.60907423971</v>
       </c>
       <c r="E88">
-        <v>27308.33755801534</v>
+        <v>28028.87058958567</v>
       </c>
       <c r="F88">
-        <v>61965.84071504873</v>
+        <v>62686.37374661906</v>
       </c>
       <c r="G88">
         <v>37342.8</v>
@@ -8509,28 +8509,28 @@
         <v>18497.1</v>
       </c>
       <c r="M88">
-        <v>3364.745150827146</v>
+        <v>3403.870094441415</v>
       </c>
       <c r="N88">
-        <v>15132.35484917286</v>
+        <v>15093.22990555859</v>
       </c>
       <c r="O88">
-        <v>3904.147551086597</v>
+        <v>3894.053315634115</v>
       </c>
       <c r="P88">
-        <v>11228.20729808626</v>
+        <v>11199.17658992447</v>
       </c>
       <c r="Q88">
-        <v>16177.30729808626</v>
+        <v>16148.27658992447</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2902041026957073</v>
+        <v>0.3081317156207669</v>
       </c>
       <c r="T88">
-        <v>5.644436551863913</v>
+        <v>6.058469182927643</v>
       </c>
       <c r="U88">
         <v>0.0543</v>
@@ -8547,7 +8547,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.49732570249872</v>
+        <v>5.434138050745862</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,22 +8555,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.0751099450306997</v>
+        <v>0.07494139968400035</v>
       </c>
       <c r="C89">
-        <v>18019.03532762065</v>
+        <v>17549.29896537499</v>
       </c>
       <c r="D89">
-        <v>43362.60907423971</v>
+        <v>43613.40574356438</v>
       </c>
       <c r="E89">
-        <v>28028.87058958567</v>
+        <v>28749.403621156</v>
       </c>
       <c r="F89">
-        <v>62686.37374661906</v>
+        <v>63406.90677818939</v>
       </c>
       <c r="G89">
         <v>37342.8</v>
@@ -8591,28 +8591,28 @@
         <v>18497.1</v>
       </c>
       <c r="M89">
-        <v>3403.870094441415</v>
+        <v>3442.995038055684</v>
       </c>
       <c r="N89">
-        <v>15093.22990555859</v>
+        <v>15054.10496194432</v>
       </c>
       <c r="O89">
-        <v>3894.053315634115</v>
+        <v>3883.959080181634</v>
       </c>
       <c r="P89">
-        <v>11199.17658992447</v>
+        <v>11170.14588176268</v>
       </c>
       <c r="Q89">
-        <v>16148.27658992447</v>
+        <v>16119.24588176268</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3081317156207669</v>
+        <v>0.3290472640333363</v>
       </c>
       <c r="T89">
-        <v>6.058469182927643</v>
+        <v>6.541507252501995</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8629,7 +8629,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.434138050745862</v>
+        <v>5.372386481987387</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,22 +8637,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07494139968400035</v>
+        <v>0.07477285433730102</v>
       </c>
       <c r="C90">
-        <v>17549.29896537499</v>
+        <v>17082.48054908589</v>
       </c>
       <c r="D90">
-        <v>43613.40574356438</v>
+        <v>43867.12035884561</v>
       </c>
       <c r="E90">
-        <v>28749.403621156</v>
+        <v>29469.93665272633</v>
       </c>
       <c r="F90">
-        <v>63406.90677818939</v>
+        <v>64127.43980975972</v>
       </c>
       <c r="G90">
         <v>37342.8</v>
@@ -8673,28 +8673,28 @@
         <v>18497.1</v>
       </c>
       <c r="M90">
-        <v>3442.995038055684</v>
+        <v>3482.119981669953</v>
       </c>
       <c r="N90">
-        <v>15054.10496194432</v>
+        <v>15014.98001833005</v>
       </c>
       <c r="O90">
-        <v>3883.959080181634</v>
+        <v>3873.864844729153</v>
       </c>
       <c r="P90">
-        <v>11170.14588176268</v>
+        <v>11141.1151736009</v>
       </c>
       <c r="Q90">
-        <v>16119.24588176268</v>
+        <v>16090.21517360089</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3290472640333363</v>
+        <v>0.3537656394300093</v>
       </c>
       <c r="T90">
-        <v>6.541507252501995</v>
+        <v>7.11237042563532</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.372386481987387</v>
+        <v>5.312022588931348</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,22 +8719,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07477285433730102</v>
+        <v>0.07460430899060168</v>
       </c>
       <c r="C91">
-        <v>17082.48054908589</v>
+        <v>16618.63130090352</v>
       </c>
       <c r="D91">
-        <v>43867.12035884561</v>
+        <v>44123.80414223357</v>
       </c>
       <c r="E91">
-        <v>29469.93665272633</v>
+        <v>30190.46968429667</v>
       </c>
       <c r="F91">
-        <v>64127.43980975972</v>
+        <v>64847.97284133006</v>
       </c>
       <c r="G91">
         <v>37342.8</v>
@@ -8755,28 +8755,28 @@
         <v>18497.1</v>
       </c>
       <c r="M91">
-        <v>3482.119981669953</v>
+        <v>3521.244925284223</v>
       </c>
       <c r="N91">
-        <v>15014.98001833005</v>
+        <v>14975.85507471578</v>
       </c>
       <c r="O91">
-        <v>3873.864844729153</v>
+        <v>3863.770609276671</v>
       </c>
       <c r="P91">
-        <v>11141.1151736009</v>
+        <v>11112.08446543911</v>
       </c>
       <c r="Q91">
-        <v>16090.21517360089</v>
+        <v>16061.18446543911</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3537656394300093</v>
+        <v>0.3834276899060168</v>
       </c>
       <c r="T91">
-        <v>7.11237042563532</v>
+        <v>7.797406233395311</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8793,7 +8793,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.312022588931348</v>
+        <v>5.253000115720999</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,22 +8801,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07460430899060168</v>
+        <v>0.07443576364390234</v>
       </c>
       <c r="C92">
-        <v>16618.63130090352</v>
+        <v>16157.8036489182</v>
       </c>
       <c r="D92">
-        <v>44123.80414223357</v>
+        <v>44383.5095218186</v>
       </c>
       <c r="E92">
-        <v>30190.46968429667</v>
+        <v>30911.00271586701</v>
       </c>
       <c r="F92">
-        <v>64847.97284133006</v>
+        <v>65568.50587290039</v>
       </c>
       <c r="G92">
         <v>37342.8</v>
@@ -8837,28 +8837,28 @@
         <v>18497.1</v>
       </c>
       <c r="M92">
-        <v>3521.244925284223</v>
+        <v>3560.369868898491</v>
       </c>
       <c r="N92">
-        <v>14975.85507471578</v>
+        <v>14936.73013110151</v>
       </c>
       <c r="O92">
-        <v>3863.770609276671</v>
+        <v>3853.67637382419</v>
       </c>
       <c r="P92">
-        <v>11112.08446543911</v>
+        <v>11083.05375727732</v>
       </c>
       <c r="Q92">
-        <v>16061.18446543911</v>
+        <v>16032.15375727732</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3834276899060168</v>
+        <v>0.4196813071544706</v>
       </c>
       <c r="T92">
-        <v>7.797406233395311</v>
+        <v>8.634672220657521</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8875,7 +8875,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.253000115720999</v>
+        <v>5.195274839724066</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,22 +8883,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07443576364390234</v>
+        <v>0.07426721829720301</v>
       </c>
       <c r="C93">
-        <v>16157.8036489182</v>
+        <v>15700.05126286049</v>
       </c>
       <c r="D93">
-        <v>44383.5095218186</v>
+        <v>44646.29016733122</v>
       </c>
       <c r="E93">
-        <v>30911.00271586701</v>
+        <v>31631.53574743734</v>
       </c>
       <c r="F93">
-        <v>65568.50587290039</v>
+        <v>66289.03890447073</v>
       </c>
       <c r="G93">
         <v>37342.8</v>
@@ -8919,28 +8919,28 @@
         <v>18497.1</v>
       </c>
       <c r="M93">
-        <v>3560.369868898491</v>
+        <v>3599.49481251276</v>
       </c>
       <c r="N93">
-        <v>14936.73013110151</v>
+        <v>14897.60518748724</v>
       </c>
       <c r="O93">
-        <v>3853.67637382419</v>
+        <v>3843.582138371709</v>
       </c>
       <c r="P93">
-        <v>11083.05375727732</v>
+        <v>11054.02304911553</v>
       </c>
       <c r="Q93">
-        <v>16032.15375727732</v>
+        <v>16003.12304911553</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4196813071544706</v>
+        <v>0.4649983287150378</v>
       </c>
       <c r="T93">
-        <v>8.634672220657521</v>
+        <v>9.681254704735286</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.195274839724066</v>
+        <v>5.138804461031413</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,22 +8965,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07426721829720301</v>
+        <v>0.07409867295050365</v>
       </c>
       <c r="C94">
-        <v>15700.05126286049</v>
+        <v>15245.42909107692</v>
       </c>
       <c r="D94">
-        <v>44646.29016733122</v>
+        <v>44912.20102711798</v>
       </c>
       <c r="E94">
-        <v>31631.53574743734</v>
+        <v>32352.06877900767</v>
       </c>
       <c r="F94">
-        <v>66289.03890447073</v>
+        <v>67009.57193604106</v>
       </c>
       <c r="G94">
         <v>37342.8</v>
@@ -9001,28 +9001,28 @@
         <v>18497.1</v>
       </c>
       <c r="M94">
-        <v>3599.49481251276</v>
+        <v>3638.61975612703</v>
       </c>
       <c r="N94">
-        <v>14897.60518748724</v>
+        <v>14858.48024387297</v>
       </c>
       <c r="O94">
-        <v>3843.582138371709</v>
+        <v>3833.487902919227</v>
       </c>
       <c r="P94">
-        <v>11054.02304911553</v>
+        <v>11024.99234095375</v>
       </c>
       <c r="Q94">
-        <v>16003.12304911553</v>
+        <v>15974.09234095374</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4649983287150378</v>
+        <v>0.5232630707214811</v>
       </c>
       <c r="T94">
-        <v>9.681254704735286</v>
+        <v>11.02686075569241</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9039,7 +9039,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>5.138804461031413</v>
+        <v>5.083548499084839</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,22 +9047,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07409867295050365</v>
+        <v>0.07393012760380432</v>
       </c>
       <c r="C95">
-        <v>15245.42909107692</v>
+        <v>14793.99339883475</v>
       </c>
       <c r="D95">
-        <v>44912.20102711798</v>
+        <v>45181.29836644614</v>
       </c>
       <c r="E95">
-        <v>32352.06877900767</v>
+        <v>33072.60181057802</v>
       </c>
       <c r="F95">
-        <v>67009.57193604106</v>
+        <v>67730.10496761141</v>
       </c>
       <c r="G95">
         <v>37342.8</v>
@@ -9083,28 +9083,28 @@
         <v>18497.1</v>
       </c>
       <c r="M95">
-        <v>3638.61975612703</v>
+        <v>3677.744699741299</v>
       </c>
       <c r="N95">
-        <v>14858.48024387297</v>
+        <v>14819.3553002587</v>
       </c>
       <c r="O95">
-        <v>3833.487902919227</v>
+        <v>3823.393667466746</v>
       </c>
       <c r="P95">
-        <v>11024.99234095375</v>
+        <v>10995.96163279196</v>
       </c>
       <c r="Q95">
-        <v>15974.09234095374</v>
+        <v>15945.06163279196</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5232630707214811</v>
+        <v>0.6009493933967393</v>
       </c>
       <c r="T95">
-        <v>11.02686075569241</v>
+        <v>12.82100215696858</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9121,7 +9121,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>5.083548499084839</v>
+        <v>5.029468195903084</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,22 +9129,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07393012760380432</v>
+        <v>0.07376158225710497</v>
       </c>
       <c r="C96">
-        <v>14793.99339883475</v>
+        <v>14345.80180801263</v>
       </c>
       <c r="D96">
-        <v>45181.29836644614</v>
+        <v>45453.63980719436</v>
       </c>
       <c r="E96">
-        <v>33072.60181057802</v>
+        <v>33793.13484214835</v>
       </c>
       <c r="F96">
-        <v>67730.10496761141</v>
+        <v>68450.63799918174</v>
       </c>
       <c r="G96">
         <v>37342.8</v>
@@ -9165,28 +9165,28 @@
         <v>18497.1</v>
       </c>
       <c r="M96">
-        <v>3677.744699741299</v>
+        <v>3716.869643355568</v>
       </c>
       <c r="N96">
-        <v>14819.3553002587</v>
+        <v>14780.23035664443</v>
       </c>
       <c r="O96">
-        <v>3823.393667466746</v>
+        <v>3813.299432014264</v>
       </c>
       <c r="P96">
-        <v>10995.96163279196</v>
+        <v>10966.93092463017</v>
       </c>
       <c r="Q96">
-        <v>15945.06163279196</v>
+        <v>15916.03092463017</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6009493933967393</v>
+        <v>0.7097102451421005</v>
       </c>
       <c r="T96">
-        <v>12.82100215696858</v>
+        <v>15.33280011875521</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>5.029468195903084</v>
+        <v>4.976526425419894</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,22 +9211,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07376158225710497</v>
+        <v>0.07359303691040564</v>
       </c>
       <c r="C97">
-        <v>14345.80180801263</v>
+        <v>13900.91333823474</v>
       </c>
       <c r="D97">
-        <v>45453.63980719436</v>
+        <v>45729.28436898681</v>
       </c>
       <c r="E97">
-        <v>33793.13484214835</v>
+        <v>34513.66787371868</v>
       </c>
       <c r="F97">
-        <v>68450.63799918174</v>
+        <v>69171.17103075207</v>
       </c>
       <c r="G97">
         <v>37342.8</v>
@@ -9247,28 +9247,28 @@
         <v>18497.1</v>
       </c>
       <c r="M97">
-        <v>3716.869643355568</v>
+        <v>3755.994586969838</v>
       </c>
       <c r="N97">
-        <v>14780.23035664443</v>
+        <v>14741.10541303016</v>
       </c>
       <c r="O97">
-        <v>3813.299432014264</v>
+        <v>3803.205196561782</v>
       </c>
       <c r="P97">
-        <v>10966.93092463017</v>
+        <v>10937.90021646838</v>
       </c>
       <c r="Q97">
-        <v>15916.03092463017</v>
+        <v>15887.00021646838</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7097102451421005</v>
+        <v>0.8728515227601427</v>
       </c>
       <c r="T97">
-        <v>15.33280011875521</v>
+        <v>19.10049706143517</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9285,7 +9285,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.976526425419894</v>
+        <v>4.924687608488436</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,22 +9293,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07359303691040564</v>
+        <v>0.07342449156370631</v>
       </c>
       <c r="C98">
-        <v>13900.91333823475</v>
+        <v>13459.38844951143</v>
       </c>
       <c r="D98">
-        <v>45729.28436898681</v>
+        <v>46008.29251183383</v>
       </c>
       <c r="E98">
-        <v>34513.66787371867</v>
+        <v>35234.20090528901</v>
       </c>
       <c r="F98">
-        <v>69171.17103075206</v>
+        <v>69891.7040623224</v>
       </c>
       <c r="G98">
         <v>37342.8</v>
@@ -9329,28 +9329,28 @@
         <v>18497.1</v>
       </c>
       <c r="M98">
-        <v>3755.994586969837</v>
+        <v>3795.119530584107</v>
       </c>
       <c r="N98">
-        <v>14741.10541303017</v>
+        <v>14701.9804694159</v>
       </c>
       <c r="O98">
-        <v>3803.205196561783</v>
+        <v>3793.110961109301</v>
       </c>
       <c r="P98">
-        <v>10937.90021646838</v>
+        <v>10908.86950830659</v>
       </c>
       <c r="Q98">
-        <v>15887.00021646838</v>
+        <v>15857.96950830659</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8728515227601403</v>
+        <v>1.144753652123543</v>
       </c>
       <c r="T98">
-        <v>19.10049706143512</v>
+        <v>25.37999196590169</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.924687608488437</v>
+        <v>4.873917633143195</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,22 +9375,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07342449156370631</v>
+        <v>0.07325594621700697</v>
       </c>
       <c r="C99">
-        <v>13459.38844951143</v>
+        <v>13021.28908644998</v>
       </c>
       <c r="D99">
-        <v>46008.29251183383</v>
+        <v>46290.72618034271</v>
       </c>
       <c r="E99">
-        <v>35234.20090528901</v>
+        <v>35954.73393685935</v>
       </c>
       <c r="F99">
-        <v>69891.7040623224</v>
+        <v>70612.23709389273</v>
       </c>
       <c r="G99">
         <v>37342.8</v>
@@ -9411,28 +9411,28 @@
         <v>18497.1</v>
       </c>
       <c r="M99">
-        <v>3795.119530584107</v>
+        <v>3834.244474198375</v>
       </c>
       <c r="N99">
-        <v>14701.9804694159</v>
+        <v>14662.85552580163</v>
       </c>
       <c r="O99">
-        <v>3793.110961109301</v>
+        <v>3783.01672565682</v>
       </c>
       <c r="P99">
-        <v>10908.86950830659</v>
+        <v>10879.83880014481</v>
       </c>
       <c r="Q99">
-        <v>15857.96950830659</v>
+        <v>15828.93880014481</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.144753652123543</v>
+        <v>1.688557910850347</v>
       </c>
       <c r="T99">
-        <v>25.37999196590169</v>
+        <v>37.93898177483482</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9449,7 +9449,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.873917633143195</v>
+        <v>4.824183779743775</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,22 +9457,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07325594621700697</v>
+        <v>0.07308740087030763</v>
       </c>
       <c r="C100">
-        <v>13021.28908644998</v>
+        <v>12586.67872410388</v>
       </c>
       <c r="D100">
-        <v>46290.72618034271</v>
+        <v>46576.64884956695</v>
       </c>
       <c r="E100">
-        <v>35954.73393685935</v>
+        <v>36675.26696842968</v>
       </c>
       <c r="F100">
-        <v>70612.23709389273</v>
+        <v>71332.77012546307</v>
       </c>
       <c r="G100">
         <v>37342.8</v>
@@ -9493,28 +9493,28 @@
         <v>18497.1</v>
       </c>
       <c r="M100">
-        <v>3834.244474198375</v>
+        <v>3873.369417812645</v>
       </c>
       <c r="N100">
-        <v>14662.85552580163</v>
+        <v>14623.73058218736</v>
       </c>
       <c r="O100">
-        <v>3783.01672565682</v>
+        <v>3772.922490204338</v>
       </c>
       <c r="P100">
-        <v>10879.83880014481</v>
+        <v>10850.80809198302</v>
       </c>
       <c r="Q100">
-        <v>15828.93880014481</v>
+        <v>15799.90809198302</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.688557910850347</v>
+        <v>3.31997068703076</v>
       </c>
       <c r="T100">
-        <v>37.93898177483482</v>
+        <v>75.61595120163422</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9531,91 +9531,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.824183779743775</v>
+        <v>4.775454650655454</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07308740087030763</v>
-      </c>
-      <c r="C101">
-        <v>12586.67872410388</v>
-      </c>
-      <c r="D101">
-        <v>46576.64884956695</v>
-      </c>
-      <c r="E101">
-        <v>36675.26696842968</v>
-      </c>
-      <c r="F101">
-        <v>71332.77012546307</v>
-      </c>
-      <c r="G101">
-        <v>37342.8</v>
-      </c>
-      <c r="H101">
-        <v>37395.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>23446.2</v>
-      </c>
-      <c r="K101">
-        <v>4949.099999999999</v>
-      </c>
-      <c r="L101">
-        <v>18497.1</v>
-      </c>
-      <c r="M101">
-        <v>3873.369417812645</v>
-      </c>
-      <c r="N101">
-        <v>14623.73058218736</v>
-      </c>
-      <c r="O101">
-        <v>3772.922490204338</v>
-      </c>
-      <c r="P101">
-        <v>10850.80809198302</v>
-      </c>
-      <c r="Q101">
-        <v>15799.90809198302</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.31997068703076</v>
-      </c>
-      <c r="T101">
-        <v>75.61595120163422</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.258</v>
-      </c>
-      <c r="W101">
-        <v>0.0402906</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.775454650655454</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
